--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 01:51:31</t>
+          <t>2026-06-03 03:58:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 03:58:27</t>
+          <t>2026-06-03 06:05:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,254 +833,1016 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>South Korean K2 League</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>07:30:00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Busan IPark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Chungnam Asan</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>75</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>22</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>24</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>27</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>34</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>2026-06-03 08:12:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>South Korean K2 League</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>07:30:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Daegu Fc</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Paju Citizen</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="X3" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>300</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>70</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>90</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2026-06-03 08:12:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>South Korean K2 League</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>07:30:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Seongnam FC</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Gimhae City</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>100</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>90</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>22</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>22</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>36</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>44</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-06-03 08:12:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Swedish Division 1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>FBK Karlstad</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>IF Karlstad</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="F5" t="n">
         <v>1.04</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G5" t="n">
         <v>1000</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H5" t="n">
         <v>1.04</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I5" t="n">
         <v>1000</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J5" t="n">
         <v>1.01</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K5" t="n">
         <v>950</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q5" t="n">
         <v>1.01</v>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>2026-06-03 06:05:17</t>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-06-03 08:12:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB5"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G2" t="n">
         <v>2.04</v>
@@ -869,7 +869,7 @@
         <v>5.1</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
         <v>4</v>
@@ -905,7 +905,7 @@
         <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W2" t="n">
         <v>1.96</v>
@@ -971,13 +971,13 @@
         <v>11.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU2" t="n">
         <v>6.2</v>
@@ -986,19 +986,19 @@
         <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AZ2" t="n">
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
         <v>16</v>
@@ -1007,70 +1007,70 @@
         <v>15</v>
       </c>
       <c r="BD2" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>75</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
         <v>10.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
         <v>3.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.7</v>
+        <v>2.98</v>
       </c>
       <c r="BJ2" t="n">
         <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>22</v>
+        <v>9.6</v>
       </c>
       <c r="BN2" t="n">
         <v>4.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="BP2" t="n">
         <v>14.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BR2" t="n">
         <v>30</v>
       </c>
       <c r="BS2" t="n">
-        <v>24</v>
+        <v>7.6</v>
       </c>
       <c r="BT2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU2" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV2" t="n">
         <v>40</v>
       </c>
       <c r="BW2" t="n">
-        <v>27</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>34</v>
+        <v>8.6</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 08:12:38</t>
+          <t>2026-06-03 10:20:28</t>
         </is>
       </c>
     </row>
@@ -1114,19 +1114,19 @@
         <v>1.51</v>
       </c>
       <c r="G3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L3" t="n">
         <v>1.34</v>
@@ -1144,7 +1144,7 @@
         <v>2.06</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="R3" t="n">
         <v>1.41</v>
@@ -1153,16 +1153,16 @@
         <v>2.92</v>
       </c>
       <c r="T3" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="U3" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="V3" t="n">
         <v>1.12</v>
       </c>
       <c r="W3" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="X3" t="n">
         <v>22</v>
@@ -1225,10 +1225,10 @@
         <v>18.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>170</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
         <v>6.4</v>
@@ -1237,40 +1237,40 @@
         <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AW3" t="n">
-        <v>80</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
         <v>6.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
         <v>17</v>
       </c>
       <c r="BA3" t="n">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC3" t="n">
         <v>11.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>90</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
         <v>3.9</v>
@@ -1282,49 +1282,49 @@
         <v>11.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>9.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="BN3" t="n">
         <v>4.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="BP3" t="n">
         <v>9.6</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>20</v>
+        <v>7.8</v>
       </c>
       <c r="BT3" t="n">
         <v>11.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>9.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>21</v>
+        <v>9.6</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>21</v>
+        <v>9.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 08:12:38</t>
+          <t>2026-06-03 10:20:28</t>
         </is>
       </c>
     </row>
@@ -1365,31 +1365,31 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="G4" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.4</v>
@@ -1398,46 +1398,46 @@
         <v>1.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="T4" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U4" t="n">
         <v>1.84</v>
       </c>
       <c r="V4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="X4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y4" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z4" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AA4" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE4" t="n">
         <v>110</v>
@@ -1449,136 +1449,136 @@
         <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AI4" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL4" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
         <v>190</v>
       </c>
       <c r="AN4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO4" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF4" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>100</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>11</v>
-      </c>
       <c r="BG4" t="n">
-        <v>90</v>
+        <v>4.4</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="BJ4" t="n">
         <v>11.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9.4</v>
+        <v>6</v>
       </c>
       <c r="BR4" t="n">
         <v>34</v>
       </c>
       <c r="BS4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="BT4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BU4" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>36</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-03 08:12:38</t>
+          <t>2026-06-03 10:20:28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,17 +1605,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FBK Karlstad</t>
+          <t>Lanzhou Longyuan Athletic</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IF Karlstad</t>
+          <t>Dalian Kewei</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1637,212 +1637,466 @@
         <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:20:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FBK Karlstad</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>IF Karlstad</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K6" t="n">
+        <v>950</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>2026-06-03 08:12:38</t>
+      <c r="Q6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:20:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="G2" t="n">
         <v>2.04</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I2" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="n">
         <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L2" t="n">
         <v>1.34</v>
@@ -884,28 +884,28 @@
         <v>3.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q2" t="n">
         <v>1.94</v>
       </c>
       <c r="R2" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
         <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U2" t="n">
         <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
         <v>1.96</v>
@@ -914,10 +914,10 @@
         <v>17</v>
       </c>
       <c r="Y2" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA2" t="n">
         <v>130</v>
@@ -944,7 +944,7 @@
         <v>24</v>
       </c>
       <c r="AI2" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ2" t="n">
         <v>27</v>
@@ -956,10 +956,10 @@
         <v>46</v>
       </c>
       <c r="AM2" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO2" t="n">
         <v>85</v>
@@ -992,7 +992,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AY2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ2" t="n">
         <v>14</v>
@@ -1013,7 +1013,7 @@
         <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG2" t="n">
         <v>1.01</v>
@@ -1022,13 +1022,13 @@
         <v>3.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="BJ2" t="n">
         <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1046,7 +1046,7 @@
         <v>14.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BR2" t="n">
         <v>30</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
         <v>5.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
@@ -1147,10 +1147,10 @@
         <v>1.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="T3" t="n">
         <v>1.9</v>
@@ -1159,7 +1159,7 @@
         <v>1.89</v>
       </c>
       <c r="V3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W3" t="n">
         <v>2.74</v>
@@ -1246,7 +1246,7 @@
         <v>6.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AZ3" t="n">
         <v>17</v>
@@ -1276,7 +1276,7 @@
         <v>3.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ3" t="n">
         <v>11.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G4" t="n">
         <v>1.96</v>
@@ -1374,13 +1374,13 @@
         <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.39</v>
@@ -1404,10 +1404,10 @@
         <v>1.26</v>
       </c>
       <c r="S4" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U4" t="n">
         <v>1.84</v>
@@ -1422,7 +1422,7 @@
         <v>14</v>
       </c>
       <c r="Y4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z4" t="n">
         <v>50</v>
@@ -1434,7 +1434,7 @@
         <v>9</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD4" t="n">
         <v>23</v>
@@ -1464,7 +1464,7 @@
         <v>55</v>
       </c>
       <c r="AM4" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN4" t="n">
         <v>19</v>
@@ -1479,10 +1479,10 @@
         <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AT4" t="n">
         <v>5.6</v>
@@ -1494,7 +1494,7 @@
         <v>15.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AX4" t="n">
         <v>7.8</v>
@@ -1506,7 +1506,7 @@
         <v>18.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BB4" t="n">
         <v>14.5</v>
@@ -1515,22 +1515,22 @@
         <v>16</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BF4" t="n">
         <v>11.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BH4" t="n">
         <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BJ4" t="n">
         <v>11.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>
@@ -1622,16 +1622,16 @@
         <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H5" t="n">
         <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
         <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R5" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1784,65 +1784,65 @@
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G2" t="n">
         <v>2.04</v>
@@ -866,16 +866,16 @@
         <v>4.3</v>
       </c>
       <c r="I2" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="J2" t="n">
         <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -890,7 +890,7 @@
         <v>1.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R2" t="n">
         <v>1.33</v>
@@ -905,7 +905,7 @@
         <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="W2" t="n">
         <v>1.96</v>
@@ -917,7 +917,7 @@
         <v>19.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AA2" t="n">
         <v>130</v>
@@ -971,13 +971,13 @@
         <v>11.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AU2" t="n">
         <v>6.2</v>
@@ -986,19 +986,19 @@
         <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY2" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>7.8</v>
       </c>
       <c r="AZ2" t="n">
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB2" t="n">
         <v>16</v>
@@ -1007,16 +1007,16 @@
         <v>15</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF2" t="n">
         <v>10</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH2" t="n">
         <v>3.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 12:28:17</t>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G3" t="n">
         <v>1.57</v>
@@ -1120,13 +1120,13 @@
         <v>7.2</v>
       </c>
       <c r="I3" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J3" t="n">
         <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
         <v>1.29</v>
@@ -1144,13 +1144,13 @@
         <v>2.06</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>2.68</v>
+        <v>2.92</v>
       </c>
       <c r="T3" t="n">
         <v>1.9</v>
@@ -1159,7 +1159,7 @@
         <v>1.89</v>
       </c>
       <c r="V3" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W3" t="n">
         <v>2.74</v>
@@ -1276,7 +1276,7 @@
         <v>3.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="BJ3" t="n">
         <v>11.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 12:28:17</t>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G4" t="n">
         <v>1.96</v>
@@ -1374,7 +1374,7 @@
         <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J4" t="n">
         <v>3.35</v>
@@ -1383,7 +1383,7 @@
         <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1395,13 +1395,13 @@
         <v>1.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q4" t="n">
         <v>2.16</v>
       </c>
       <c r="R4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1422,52 +1422,52 @@
         <v>14</v>
       </c>
       <c r="Y4" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA4" t="n">
         <v>180</v>
       </c>
       <c r="AB4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH4" t="n">
         <v>23</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>27</v>
       </c>
       <c r="AI4" t="n">
         <v>110</v>
       </c>
       <c r="AJ4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM4" t="n">
         <v>180</v>
       </c>
       <c r="AN4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO4" t="n">
         <v>150</v>
@@ -1479,13 +1479,13 @@
         <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU4" t="n">
         <v>7</v>
@@ -1494,7 +1494,7 @@
         <v>15.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AX4" t="n">
         <v>7.8</v>
@@ -1506,7 +1506,7 @@
         <v>18.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BB4" t="n">
         <v>14.5</v>
@@ -1515,16 +1515,16 @@
         <v>16</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BF4" t="n">
         <v>11.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BH4" t="n">
         <v>3.2</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-03 12:28:17</t>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>110</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P5" t="n">
         <v>1.25</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.24</v>
       </c>
       <c r="Q5" t="n">
         <v>1.02</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,261 +1842,769 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-03 12:28:17</t>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Finnish Ykkosliiga</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>12:30:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Haka</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>JaPS</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X6" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>260</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>15</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-06-03 14:36:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Finnish Ykkosliiga</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>KaPa</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>KTP</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X7" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>140</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>25</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>19</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-06-03 14:36:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Swedish Division 1</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>FBK Karlstad</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>IF Karlstad</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F8" t="n">
         <v>1.04</v>
       </c>
-      <c r="G6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H6" t="n">
+      <c r="G8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H8" t="n">
         <v>1.04</v>
       </c>
-      <c r="I6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K6" t="n">
+      <c r="I8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K8" t="n">
         <v>950</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R8" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-06-03 12:28:17</t>
+      <c r="S8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,7 +860,7 @@
         <v>1.85</v>
       </c>
       <c r="G2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H2" t="n">
         <v>4.3</v>
@@ -875,7 +875,7 @@
         <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -887,7 +887,7 @@
         <v>1.32</v>
       </c>
       <c r="P2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q2" t="n">
         <v>1.95</v>
@@ -899,22 +899,22 @@
         <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V2" t="n">
         <v>1.24</v>
       </c>
       <c r="W2" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X2" t="n">
         <v>17</v>
       </c>
       <c r="Y2" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="Z2" t="n">
         <v>38</v>
@@ -926,43 +926,43 @@
         <v>10.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH2" t="n">
         <v>23</v>
       </c>
-      <c r="AE2" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>24</v>
-      </c>
       <c r="AI2" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
         <v>130</v>
       </c>
       <c r="AN2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AO2" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AP2" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
         <v>11.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="AT2" t="n">
         <v>6.4</v>
@@ -986,7 +986,7 @@
         <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="AX2" t="n">
         <v>10</v>
@@ -998,7 +998,7 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="BB2" t="n">
         <v>16</v>
@@ -1007,16 +1007,16 @@
         <v>15</v>
       </c>
       <c r="BD2" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF2" t="n">
         <v>10</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="BH2" t="n">
         <v>3.5</v>
@@ -1034,19 +1034,19 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO2" t="n">
         <v>3.55</v>
       </c>
       <c r="BP2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR2" t="n">
         <v>30</v>
@@ -1055,22 +1055,22 @@
         <v>7.6</v>
       </c>
       <c r="BT2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 14:36:03</t>
+          <t>2026-06-03 16:43:36</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
         <v>1.89</v>
       </c>
       <c r="V3" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W3" t="n">
         <v>2.74</v>
@@ -1222,7 +1222,7 @@
         <v>13</v>
       </c>
       <c r="AQ3" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
         <v>1.01</v>
@@ -1237,13 +1237,13 @@
         <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
         <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
         <v>7.4</v>
@@ -1255,19 +1255,19 @@
         <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
         <v>11.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
         <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG3" t="n">
         <v>1.01</v>
@@ -1294,7 +1294,7 @@
         <v>4.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BP3" t="n">
         <v>9.6</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 14:36:03</t>
+          <t>2026-06-03 16:43:36</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H4" t="n">
         <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J4" t="n">
         <v>3.35</v>
@@ -1425,13 +1425,13 @@
         <v>16.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AA4" t="n">
         <v>180</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC4" t="n">
         <v>8.4</v>
@@ -1455,7 +1455,7 @@
         <v>110</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK4" t="n">
         <v>24</v>
@@ -1467,7 +1467,7 @@
         <v>180</v>
       </c>
       <c r="AN4" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AO4" t="n">
         <v>150</v>
@@ -1479,10 +1479,10 @@
         <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT4" t="n">
         <v>5.7</v>
@@ -1494,7 +1494,7 @@
         <v>15.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AX4" t="n">
         <v>7.8</v>
@@ -1506,7 +1506,7 @@
         <v>18.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BB4" t="n">
         <v>14.5</v>
@@ -1515,16 +1515,16 @@
         <v>16</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF4" t="n">
         <v>11.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH4" t="n">
         <v>3.2</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-03 14:36:03</t>
+          <t>2026-06-03 16:43:36</t>
         </is>
       </c>
     </row>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
         <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q5" t="n">
         <v>1.02</v>
@@ -1784,65 +1784,65 @@
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-03 14:36:03</t>
+          <t>2026-06-03 16:43:36</t>
         </is>
       </c>
     </row>
@@ -1987,10 +1987,10 @@
         <v>18.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT6" t="n">
         <v>7</v>
@@ -2002,7 +2002,7 @@
         <v>19.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX6" t="n">
         <v>7.2</v>
@@ -2014,7 +2014,7 @@
         <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB6" t="n">
         <v>10</v>
@@ -2023,80 +2023,80 @@
         <v>11.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF6" t="n">
         <v>5.3</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH6" t="n">
         <v>3.95</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ6" t="n">
         <v>11</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BN6" t="n">
         <v>4.1</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BP6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BT6" t="n">
         <v>11</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BZ6" t="n">
         <v>15</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-03 14:36:03</t>
+          <t>2026-06-03 16:43:36</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>6.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="I7" t="n">
         <v>1.88</v>
@@ -2142,7 +2142,7 @@
         <v>3.8</v>
       </c>
       <c r="K7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.29</v>
@@ -2151,7 +2151,7 @@
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
         <v>1.25</v>
@@ -2163,10 +2163,10 @@
         <v>1.73</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S7" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="T7" t="n">
         <v>1.71</v>
@@ -2178,7 +2178,7 @@
         <v>2.12</v>
       </c>
       <c r="W7" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="X7" t="n">
         <v>23</v>
@@ -2292,7 +2292,7 @@
         <v>3.95</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="BJ7" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-03 14:36:03</t>
+          <t>2026-06-03 16:43:36</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -2405,206 +2405,968 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1.25</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.02</v>
       </c>
       <c r="R8" t="n">
         <v>1.24</v>
       </c>
       <c r="S8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-06-03 16:43:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Icelandic 1 Deild</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>HK Kopavogur</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Afturelding</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K9" t="n">
+        <v>950</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
         <v>1.25</v>
       </c>
-      <c r="T8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>2026-06-03 14:36:03</t>
+      <c r="O9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-03 16:43:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Icelandic 1 Deild</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Aegir</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Leiknir R</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-06-03 16:43:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Icelandic 1 Deild</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Njardvik</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K11" t="n">
+        <v>950</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-06-03 16:43:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
@@ -869,7 +869,7 @@
         <v>5.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K2" t="n">
         <v>4</v>
@@ -887,7 +887,7 @@
         <v>1.32</v>
       </c>
       <c r="P2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q2" t="n">
         <v>1.95</v>
@@ -902,7 +902,7 @@
         <v>1.82</v>
       </c>
       <c r="U2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
         <v>1.24</v>
@@ -923,16 +923,16 @@
         <v>130</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
         <v>22</v>
       </c>
       <c r="AE2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF2" t="n">
         <v>12.5</v>
@@ -944,7 +944,7 @@
         <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ2" t="n">
         <v>26</v>
@@ -971,13 +971,13 @@
         <v>11.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AU2" t="n">
         <v>6.2</v>
@@ -986,7 +986,7 @@
         <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AX2" t="n">
         <v>10</v>
@@ -998,7 +998,7 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BB2" t="n">
         <v>16</v>
@@ -1007,16 +1007,16 @@
         <v>15</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BF2" t="n">
         <v>10</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BH2" t="n">
         <v>3.5</v>
@@ -1040,13 +1040,13 @@
         <v>4.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP2" t="n">
         <v>14</v>
       </c>
       <c r="BQ2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BR2" t="n">
         <v>30</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 16:43:36</t>
+          <t>2026-06-03 18:51:00</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
         <v>7.2</v>
       </c>
       <c r="I3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J3" t="n">
         <v>4.3</v>
@@ -1222,7 +1222,7 @@
         <v>13</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AR3" t="n">
         <v>1.01</v>
@@ -1237,7 +1237,7 @@
         <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AW3" t="n">
         <v>1.01</v>
@@ -1255,13 +1255,13 @@
         <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC3" t="n">
         <v>11.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 16:43:36</t>
+          <t>2026-06-03 18:51:00</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
         <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1410,7 +1410,7 @@
         <v>1.99</v>
       </c>
       <c r="U4" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V4" t="n">
         <v>1.2</v>
@@ -1431,7 +1431,7 @@
         <v>180</v>
       </c>
       <c r="AB4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC4" t="n">
         <v>8.4</v>
@@ -1455,10 +1455,10 @@
         <v>110</v>
       </c>
       <c r="AJ4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL4" t="n">
         <v>48</v>
@@ -1467,7 +1467,7 @@
         <v>180</v>
       </c>
       <c r="AN4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO4" t="n">
         <v>150</v>
@@ -1479,13 +1479,13 @@
         <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AU4" t="n">
         <v>7</v>
@@ -1494,7 +1494,7 @@
         <v>15.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX4" t="n">
         <v>7.8</v>
@@ -1506,7 +1506,7 @@
         <v>18.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB4" t="n">
         <v>14.5</v>
@@ -1515,22 +1515,22 @@
         <v>16</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF4" t="n">
         <v>11.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH4" t="n">
         <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BJ4" t="n">
         <v>11.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-03 16:43:36</t>
+          <t>2026-06-03 18:51:00</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-03 16:43:36</t>
+          <t>2026-06-03 18:51:00</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-03 16:43:36</t>
+          <t>2026-06-03 18:51:00</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>4.7</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="H7" t="n">
         <v>1.7</v>
@@ -2151,7 +2151,7 @@
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O7" t="n">
         <v>1.25</v>
@@ -2160,13 +2160,13 @@
         <v>2.14</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="R7" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="T7" t="n">
         <v>1.71</v>
@@ -2178,7 +2178,7 @@
         <v>2.12</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="X7" t="n">
         <v>23</v>
@@ -2292,7 +2292,7 @@
         <v>3.95</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="BJ7" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-03 16:43:36</t>
+          <t>2026-06-03 18:51:00</t>
         </is>
       </c>
     </row>
@@ -2405,13 +2405,13 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q8" t="n">
         <v>1.25</v>
@@ -2420,7 +2420,7 @@
         <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>2.44</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-03 16:43:36</t>
+          <t>2026-06-03 18:51:00</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>2.46</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2659,79 +2659,79 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>3.15</v>
       </c>
       <c r="O9" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25</v>
+        <v>3.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="S9" t="n">
-        <v>1.09</v>
+        <v>1.78</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ9" t="n">
         <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
@@ -2740,125 +2740,125 @@
         <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-03 16:43:36</t>
+          <t>2026-06-03 18:51:00</t>
         </is>
       </c>
     </row>
@@ -2889,230 +2889,230 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="G10" t="n">
-        <v>3.35</v>
+        <v>2.74</v>
       </c>
       <c r="H10" t="n">
-        <v>2.28</v>
+        <v>2.54</v>
       </c>
       <c r="I10" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J10" t="n">
         <v>3.4</v>
       </c>
-      <c r="J10" t="n">
-        <v>3.05</v>
-      </c>
       <c r="K10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X10" t="n">
+        <v>38</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BN10" t="n">
         <v>8.6</v>
       </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1000</v>
-      </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-03 16:43:36</t>
+          <t>2026-06-03 18:51:00</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>1.68</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>1.82</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="J11" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>5.1</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3167,40 +3167,40 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>2.54</v>
       </c>
       <c r="O11" t="n">
         <v>1.13</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>2.52</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.54</v>
       </c>
       <c r="S11" t="n">
-        <v>1.13</v>
+        <v>2.06</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z11" t="n">
         <v>1000</v>
@@ -3209,164 +3209,164 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE11" t="n">
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-03 16:43:36</t>
+          <t>2026-06-03 18:51:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB11"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -896,7 +896,7 @@
         <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T2" t="n">
         <v>1.82</v>
@@ -1028,34 +1028,34 @@
         <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN2" t="n">
         <v>4.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP2" t="n">
         <v>14</v>
       </c>
       <c r="BQ2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BR2" t="n">
         <v>30</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU2" t="n">
         <v>4.6</v>
@@ -1064,13 +1064,13 @@
         <v>42</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX2" t="n">
         <v>55</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 18:51:00</t>
+          <t>2026-06-03 20:58:44</t>
         </is>
       </c>
     </row>
@@ -1120,10 +1120,10 @@
         <v>7.2</v>
       </c>
       <c r="I3" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K3" t="n">
         <v>5</v>
@@ -1138,28 +1138,28 @@
         <v>4.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P3" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U3" t="n">
         <v>1.89</v>
       </c>
       <c r="V3" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W3" t="n">
         <v>2.74</v>
@@ -1186,7 +1186,7 @@
         <v>36</v>
       </c>
       <c r="AE3" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AF3" t="n">
         <v>11</v>
@@ -1273,7 +1273,7 @@
         <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI3" t="n">
         <v>3.35</v>
@@ -1282,49 +1282,49 @@
         <v>11.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN3" t="n">
         <v>4.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="BP3" t="n">
         <v>9.6</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT3" t="n">
         <v>11.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 18:51:00</t>
+          <t>2026-06-03 20:58:44</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
         <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1530,7 +1530,7 @@
         <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BJ4" t="n">
         <v>11.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-03 18:51:00</t>
+          <t>2026-06-03 20:58:44</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G5" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I5" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="J5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-03 18:51:00</t>
+          <t>2026-06-03 20:58:44</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-03 18:51:00</t>
+          <t>2026-06-03 20:58:44</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>5.7</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="I7" t="n">
         <v>1.88</v>
@@ -2154,7 +2154,7 @@
         <v>4.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P7" t="n">
         <v>2.14</v>
@@ -2166,19 +2166,19 @@
         <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="T7" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U7" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V7" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="W7" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="X7" t="n">
         <v>23</v>
@@ -2292,7 +2292,7 @@
         <v>3.95</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="BJ7" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-03 18:51:00</t>
+          <t>2026-06-03 20:58:44</t>
         </is>
       </c>
     </row>
@@ -2405,13 +2405,13 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.23</v>
+        <v>1.02</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
         <v>1.25</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-03 18:51:00</t>
+          <t>2026-06-03 20:58:44</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-03 18:51:00</t>
+          <t>2026-06-03 20:58:44</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
         <v>2.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="P10" t="n">
         <v>2.48</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-03 18:51:00</t>
+          <t>2026-06-03 20:58:44</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="G11" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
         <v>5.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K11" t="n">
         <v>5.1</v>
@@ -3167,16 +3167,16 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
         <v>1.13</v>
       </c>
       <c r="P11" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="R11" t="n">
         <v>1.54</v>
@@ -3185,16 +3185,16 @@
         <v>2.06</v>
       </c>
       <c r="T11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V11" t="n">
         <v>1.22</v>
       </c>
       <c r="W11" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="X11" t="n">
         <v>40</v>
@@ -3239,70 +3239,70 @@
         <v>23</v>
       </c>
       <c r="AL11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>2.16</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>2.1</v>
-      </c>
       <c r="BA11" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="BB11" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="BH11" t="n">
         <v>6.2</v>
@@ -3314,7 +3314,7 @@
         <v>13</v>
       </c>
       <c r="BK11" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3332,13 +3332,13 @@
         <v>15.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="BR11" t="n">
         <v>30</v>
       </c>
       <c r="BS11" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="BT11" t="n">
         <v>12.5</v>
@@ -3347,26 +3347,534 @@
         <v>5.4</v>
       </c>
       <c r="BV11" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BW11" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="BX11" t="n">
         <v>50</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="BZ11" t="n">
         <v>20</v>
       </c>
       <c r="CA11" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-03 18:51:00</t>
+          <t>2026-06-03 20:58:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Wanderers (Uru)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Danubio</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>22</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>28</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>22</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>22</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>22</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>22</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-06-03 20:58:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Operario PR</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X13" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-06-03 20:58:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
@@ -1040,7 +1040,7 @@
         <v>4.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="BP2" t="n">
         <v>14</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 20:58:44</t>
+          <t>2026-06-03 23:05:53</t>
         </is>
       </c>
     </row>
@@ -1114,13 +1114,13 @@
         <v>1.52</v>
       </c>
       <c r="G3" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H3" t="n">
         <v>7.2</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J3" t="n">
         <v>4.4</v>
@@ -1144,13 +1144,13 @@
         <v>2.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="R3" t="n">
         <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="T3" t="n">
         <v>1.92</v>
@@ -1162,7 +1162,7 @@
         <v>1.12</v>
       </c>
       <c r="W3" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="X3" t="n">
         <v>22</v>
@@ -1243,7 +1243,7 @@
         <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AY3" t="n">
         <v>7.4</v>
@@ -1267,7 +1267,7 @@
         <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BG3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 20:58:44</t>
+          <t>2026-06-03 23:05:53</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
         <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1398,7 +1398,7 @@
         <v>1.73</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R4" t="n">
         <v>1.27</v>
@@ -1530,7 +1530,7 @@
         <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.52</v>
+        <v>2.76</v>
       </c>
       <c r="BJ4" t="n">
         <v>11.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-03 20:58:44</t>
+          <t>2026-06-03 23:05:53</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-03 20:58:44</t>
+          <t>2026-06-03 23:05:53</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
         <v>130</v>
       </c>
       <c r="AF6" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG6" t="n">
         <v>12.5</v>
@@ -1987,10 +1987,10 @@
         <v>18.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AT6" t="n">
         <v>7</v>
@@ -2002,7 +2002,7 @@
         <v>19.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AX6" t="n">
         <v>7.2</v>
@@ -2014,7 +2014,7 @@
         <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BB6" t="n">
         <v>10</v>
@@ -2023,16 +2023,16 @@
         <v>11.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BF6" t="n">
         <v>5.3</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BH6" t="n">
         <v>3.95</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-03 20:58:44</t>
+          <t>2026-06-03 23:05:53</t>
         </is>
       </c>
     </row>
@@ -2130,10 +2130,10 @@
         <v>4.7</v>
       </c>
       <c r="G7" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="I7" t="n">
         <v>1.88</v>
@@ -2142,7 +2142,7 @@
         <v>3.8</v>
       </c>
       <c r="K7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L7" t="n">
         <v>1.29</v>
@@ -2160,7 +2160,7 @@
         <v>2.14</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R7" t="n">
         <v>1.44</v>
@@ -2169,16 +2169,16 @@
         <v>2.8</v>
       </c>
       <c r="T7" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="U7" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V7" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="X7" t="n">
         <v>23</v>
@@ -2292,7 +2292,7 @@
         <v>3.95</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="BJ7" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-03 20:58:44</t>
+          <t>2026-06-03 23:05:53</t>
         </is>
       </c>
     </row>
@@ -2384,13 +2384,13 @@
         <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H8" t="n">
         <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J8" t="n">
         <v>1.02</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-03 20:58:44</t>
+          <t>2026-06-03 23:05:53</t>
         </is>
       </c>
     </row>
@@ -2677,10 +2677,10 @@
         <v>1.78</v>
       </c>
       <c r="T9" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="U9" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="V9" t="n">
         <v>1.68</v>
@@ -2689,112 +2689,112 @@
         <v>1.47</v>
       </c>
       <c r="X9" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>55</v>
       </c>
-      <c r="Y9" t="n">
-        <v>30</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA9" t="n">
+      <c r="AK9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM9" t="n">
         <v>48</v>
       </c>
-      <c r="AB9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO9" t="n">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.14</v>
+        <v>7.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.08</v>
+        <v>6.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.1</v>
+        <v>6.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.14</v>
+        <v>7.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.1</v>
+        <v>6.8</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.99</v>
+        <v>5.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.08</v>
+        <v>6.4</v>
       </c>
       <c r="AX9" t="n">
-        <v>2.12</v>
+        <v>7.2</v>
       </c>
       <c r="AY9" t="n">
-        <v>2.02</v>
+        <v>5.9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2</v>
+        <v>5.7</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.1</v>
+        <v>6.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>2.24</v>
+        <v>8</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.1</v>
+        <v>7</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.12</v>
+        <v>7</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.24</v>
+        <v>8</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.24</v>
+        <v>5.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="BH9" t="n">
         <v>7.8</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-03 20:58:44</t>
+          <t>2026-06-03 23:05:53</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-03 20:58:44</t>
+          <t>2026-06-03 23:05:53</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-03 20:58:44</t>
+          <t>2026-06-03 23:05:53</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G12" t="n">
         <v>2.6</v>
       </c>
       <c r="H12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I12" t="n">
         <v>4.1</v>
@@ -3418,31 +3418,31 @@
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="O12" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="P12" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q12" t="n">
         <v>2.44</v>
       </c>
       <c r="R12" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="V12" t="n">
         <v>1.32</v>
@@ -3451,106 +3451,106 @@
         <v>1.62</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX12" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG12" t="n">
+      <c r="AY12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>17</v>
       </c>
-      <c r="AH12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>14</v>
-      </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
         <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
         <v>1.01</v>
@@ -3562,7 +3562,7 @@
         <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BJ12" t="n">
         <v>14.5</v>
@@ -3574,7 +3574,7 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>22</v>
+        <v>1.81</v>
       </c>
       <c r="BN12" t="n">
         <v>6.4</v>
@@ -3586,13 +3586,13 @@
         <v>28</v>
       </c>
       <c r="BQ12" t="n">
-        <v>13.5</v>
+        <v>1.7</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>22</v>
+        <v>1.76</v>
       </c>
       <c r="BT12" t="n">
         <v>8.6</v>
@@ -3604,23 +3604,23 @@
         <v>46</v>
       </c>
       <c r="BW12" t="n">
-        <v>22</v>
+        <v>1.74</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>22</v>
+        <v>1.77</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>22</v>
+        <v>1.76</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-03 20:58:44</t>
+          <t>2026-06-03 23:05:53</t>
         </is>
       </c>
     </row>
@@ -3669,34 +3669,34 @@
         <v>3.25</v>
       </c>
       <c r="L13" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>1.47</v>
+        <v>2.64</v>
       </c>
       <c r="O13" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="P13" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.02</v>
+        <v>2.56</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S13" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="V13" t="n">
         <v>1.32</v>
@@ -3705,112 +3705,112 @@
         <v>1.66</v>
       </c>
       <c r="X13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y13" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX13" t="n">
         <v>12</v>
       </c>
-      <c r="Z13" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>10</v>
-      </c>
       <c r="AY13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC13" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ13" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB13" t="n">
+      <c r="BD13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF13" t="n">
         <v>25</v>
       </c>
-      <c r="BC13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BG13" t="n">
-        <v>4.1</v>
+        <v>11</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-03 20:58:44</t>
+          <t>2026-06-03 23:05:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB13"/>
+  <dimension ref="A1:CB15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -902,7 +902,7 @@
         <v>1.82</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V2" t="n">
         <v>1.24</v>
@@ -917,7 +917,7 @@
         <v>17</v>
       </c>
       <c r="Z2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA2" t="n">
         <v>130</v>
@@ -941,13 +941,13 @@
         <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AI2" t="n">
         <v>70</v>
       </c>
       <c r="AJ2" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AK2" t="n">
         <v>25</v>
@@ -971,10 +971,10 @@
         <v>11.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT2" t="n">
         <v>7.4</v>
@@ -986,7 +986,7 @@
         <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX2" t="n">
         <v>10</v>
@@ -998,7 +998,7 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB2" t="n">
         <v>16</v>
@@ -1007,16 +1007,16 @@
         <v>15</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF2" t="n">
         <v>10</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH2" t="n">
         <v>3.5</v>
@@ -1040,7 +1040,7 @@
         <v>4.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="BP2" t="n">
         <v>14</v>
@@ -1052,13 +1052,13 @@
         <v>30</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV2" t="n">
         <v>42</v>
@@ -1067,7 +1067,7 @@
         <v>8.6</v>
       </c>
       <c r="BX2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
         <v>9</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 23:05:53</t>
+          <t>2026-06-04 01:13:30</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
         <v>7.2</v>
       </c>
       <c r="I3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J3" t="n">
         <v>4.4</v>
@@ -1138,13 +1138,13 @@
         <v>4.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
         <v>2.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="R3" t="n">
         <v>1.42</v>
@@ -1153,7 +1153,7 @@
         <v>2.92</v>
       </c>
       <c r="T3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U3" t="n">
         <v>1.89</v>
@@ -1165,7 +1165,7 @@
         <v>2.78</v>
       </c>
       <c r="X3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y3" t="n">
         <v>32</v>
@@ -1174,7 +1174,7 @@
         <v>85</v>
       </c>
       <c r="AA3" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="AB3" t="n">
         <v>10.5</v>
@@ -1201,7 +1201,7 @@
         <v>130</v>
       </c>
       <c r="AJ3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK3" t="n">
         <v>19.5</v>
@@ -1213,13 +1213,13 @@
         <v>160</v>
       </c>
       <c r="AN3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO3" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AP3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>18.5</v>
@@ -1249,7 +1249,7 @@
         <v>7.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA3" t="n">
         <v>1.01</v>
@@ -1267,22 +1267,22 @@
         <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BG3" t="n">
         <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ3" t="n">
         <v>11.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1297,10 +1297,10 @@
         <v>3.15</v>
       </c>
       <c r="BP3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
@@ -1312,7 +1312,7 @@
         <v>11.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 23:05:53</t>
+          <t>2026-06-04 01:13:30</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
         <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1530,7 +1530,7 @@
         <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.76</v>
+        <v>2.52</v>
       </c>
       <c r="BJ4" t="n">
         <v>11.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-03 23:05:53</t>
+          <t>2026-06-04 01:13:30</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="G5" t="n">
         <v>970</v>
       </c>
       <c r="H5" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="I5" t="n">
         <v>970</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-03 23:05:53</t>
+          <t>2026-06-04 01:13:30</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>1.5</v>
       </c>
       <c r="G6" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H6" t="n">
         <v>7</v>
@@ -1921,7 +1921,7 @@
         <v>2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W6" t="n">
         <v>2.8</v>
@@ -1933,10 +1933,10 @@
         <v>32</v>
       </c>
       <c r="Z6" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AA6" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AB6" t="n">
         <v>11.5</v>
@@ -1945,10 +1945,10 @@
         <v>13</v>
       </c>
       <c r="AD6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE6" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF6" t="n">
         <v>9.800000000000001</v>
@@ -1978,7 +1978,7 @@
         <v>8.4</v>
       </c>
       <c r="AO6" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP6" t="n">
         <v>14.5</v>
@@ -1990,7 +1990,7 @@
         <v>4.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT6" t="n">
         <v>7</v>
@@ -2002,7 +2002,7 @@
         <v>19.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AX6" t="n">
         <v>7.2</v>
@@ -2014,7 +2014,7 @@
         <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB6" t="n">
         <v>10</v>
@@ -2023,13 +2023,13 @@
         <v>11.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG6" t="n">
         <v>4.6</v>
@@ -2038,10 +2038,10 @@
         <v>3.95</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK6" t="n">
         <v>6.4</v>
@@ -2050,53 +2050,53 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN6" t="n">
         <v>4.1</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BP6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT6" t="n">
         <v>11</v>
       </c>
       <c r="BU6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ6" t="n">
         <v>15</v>
       </c>
       <c r="CA6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-03 23:05:53</t>
+          <t>2026-06-04 01:13:30</t>
         </is>
       </c>
     </row>
@@ -2133,10 +2133,10 @@
         <v>6.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="I7" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="J7" t="n">
         <v>3.8</v>
@@ -2154,37 +2154,37 @@
         <v>4.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="T7" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="U7" t="n">
         <v>2.12</v>
       </c>
       <c r="V7" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="W7" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="X7" t="n">
         <v>23</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
         <v>14.5</v>
@@ -2298,13 +2298,13 @@
         <v>10</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN7" t="n">
         <v>8.800000000000001</v>
@@ -2334,7 +2334,7 @@
         <v>12.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BX7" t="n">
         <v>25</v>
@@ -2343,14 +2343,14 @@
         <v>7.4</v>
       </c>
       <c r="BZ7" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="CA7" t="n">
         <v>6.8</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-03 23:05:53</t>
+          <t>2026-06-04 01:13:30</t>
         </is>
       </c>
     </row>
@@ -2384,13 +2384,13 @@
         <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H8" t="n">
         <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="J8" t="n">
         <v>1.02</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-03 23:05:53</t>
+          <t>2026-06-04 01:13:30</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-03 23:05:53</t>
+          <t>2026-06-04 01:13:30</t>
         </is>
       </c>
     </row>
@@ -2913,10 +2913,10 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="O10" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P10" t="n">
         <v>2.48</v>
@@ -2925,16 +2925,16 @@
         <v>1.56</v>
       </c>
       <c r="R10" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="S10" t="n">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="T10" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="U10" t="n">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="V10" t="n">
         <v>1.52</v>
@@ -2943,112 +2943,112 @@
         <v>1.57</v>
       </c>
       <c r="X10" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>38</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AK10" t="n">
         <v>25</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AL10" t="n">
         <v>32</v>
       </c>
-      <c r="AA10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AC10" t="n">
+      <c r="AM10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN10" t="n">
         <v>14.5</v>
       </c>
-      <c r="AD10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1000</v>
-      </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.95</v>
+        <v>6.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.9</v>
+        <v>6</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.94</v>
+        <v>6.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.06</v>
+        <v>7.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.9</v>
+        <v>5.9</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.8</v>
+        <v>4.9</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.86</v>
+        <v>5.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.95</v>
+        <v>6.8</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.93</v>
+        <v>6.4</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.85</v>
+        <v>5.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.88</v>
+        <v>5.7</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.97</v>
+        <v>7</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.98</v>
+        <v>7.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.94</v>
+        <v>6.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.97</v>
+        <v>7</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.06</v>
+        <v>7.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.06</v>
+        <v>5.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.06</v>
+        <v>5.8</v>
       </c>
       <c r="BH10" t="n">
         <v>5.9</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-03 23:05:53</t>
+          <t>2026-06-04 01:13:30</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-03 23:05:53</t>
+          <t>2026-06-04 01:13:30</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G12" t="n">
         <v>2.6</v>
       </c>
       <c r="H12" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K12" t="n">
         <v>3.4</v>
@@ -3421,16 +3421,16 @@
         <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O12" t="n">
         <v>1.48</v>
       </c>
       <c r="P12" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R12" t="n">
         <v>1.2</v>
@@ -3442,16 +3442,16 @@
         <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
         <v>1.62</v>
       </c>
       <c r="X12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y12" t="n">
         <v>12.5</v>
@@ -3463,25 +3463,25 @@
         <v>95</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD12" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AE12" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AF12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG12" t="n">
         <v>14</v>
       </c>
       <c r="AH12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI12" t="n">
         <v>90</v>
@@ -3493,7 +3493,7 @@
         <v>38</v>
       </c>
       <c r="AL12" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AM12" t="n">
         <v>190</v>
@@ -3502,43 +3502,43 @@
         <v>40</v>
       </c>
       <c r="AO12" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AP12" t="n">
         <v>7.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AR12" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
         <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AV12" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
         <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
         <v>1.01</v>
@@ -3559,22 +3559,22 @@
         <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.81</v>
+        <v>2.28</v>
       </c>
       <c r="BJ12" t="n">
         <v>14.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>7.4</v>
+        <v>3.2</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.81</v>
+        <v>4</v>
       </c>
       <c r="BN12" t="n">
         <v>6.4</v>
@@ -3586,13 +3586,13 @@
         <v>28</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.7</v>
+        <v>3.55</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.76</v>
+        <v>3.8</v>
       </c>
       <c r="BT12" t="n">
         <v>8.6</v>
@@ -3604,23 +3604,23 @@
         <v>46</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.74</v>
+        <v>3.75</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.77</v>
+        <v>3.85</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.76</v>
+        <v>3.8</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-03 23:05:53</t>
+          <t>2026-06-04 01:13:30</t>
         </is>
       </c>
     </row>
@@ -3675,13 +3675,13 @@
         <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O13" t="n">
         <v>1.51</v>
       </c>
       <c r="P13" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q13" t="n">
         <v>2.56</v>
@@ -3693,16 +3693,16 @@
         <v>5.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U13" t="n">
         <v>1.8</v>
       </c>
       <c r="V13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X13" t="n">
         <v>9</v>
@@ -3723,7 +3723,7 @@
         <v>7.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AE13" t="n">
         <v>65</v>
@@ -3750,7 +3750,7 @@
         <v>60</v>
       </c>
       <c r="AM13" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN13" t="n">
         <v>34</v>
@@ -3874,7 +3874,515 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-03 23:05:53</t>
+          <t>2026-06-04 01:13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>San Marcos</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-06-04 01:13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>23:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Vancouver FC</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Atletico Ottawa</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="X15" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-06-04 01:13:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="G2" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I2" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L2" t="n">
         <v>1.34</v>
@@ -896,19 +896,19 @@
         <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="U2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V2" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W2" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="X2" t="n">
         <v>17</v>
@@ -920,7 +920,7 @@
         <v>36</v>
       </c>
       <c r="AA2" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB2" t="n">
         <v>9.199999999999999</v>
@@ -932,7 +932,7 @@
         <v>22</v>
       </c>
       <c r="AE2" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF2" t="n">
         <v>12.5</v>
@@ -950,7 +950,7 @@
         <v>23</v>
       </c>
       <c r="AK2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL2" t="n">
         <v>40</v>
@@ -962,61 +962,61 @@
         <v>15</v>
       </c>
       <c r="AO2" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP2" t="n">
         <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="AS2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA2" t="n">
         <v>7.2</v>
       </c>
-      <c r="AT2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BB2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG2" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>6.8</v>
       </c>
       <c r="BH2" t="n">
         <v>3.5</v>
@@ -1028,7 +1028,7 @@
         <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1037,13 +1037,13 @@
         <v>10</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ2" t="n">
         <v>6</v>
@@ -1052,25 +1052,25 @@
         <v>30</v>
       </c>
       <c r="BS2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT2" t="n">
         <v>8</v>
       </c>
-      <c r="BT2" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BU2" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -1114,16 +1114,16 @@
         <v>1.52</v>
       </c>
       <c r="G3" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="H3" t="n">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="I3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="K3" t="n">
         <v>5</v>
@@ -1138,13 +1138,13 @@
         <v>4.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P3" t="n">
         <v>2.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="R3" t="n">
         <v>1.42</v>
@@ -1153,55 +1153,55 @@
         <v>2.92</v>
       </c>
       <c r="T3" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="U3" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="V3" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="X3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y3" t="n">
         <v>32</v>
       </c>
       <c r="Z3" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AA3" t="n">
-        <v>310</v>
+        <v>270</v>
       </c>
       <c r="AB3" t="n">
         <v>10.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE3" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AF3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK3" t="n">
         <v>19.5</v>
@@ -1210,19 +1210,19 @@
         <v>44</v>
       </c>
       <c r="AM3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO3" t="n">
         <v>160</v>
       </c>
-      <c r="AN3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>190</v>
-      </c>
       <c r="AP3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ3" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR3" t="n">
         <v>1.01</v>
@@ -1231,31 +1231,31 @@
         <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AW3" t="n">
         <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY3" t="n">
         <v>7.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA3" t="n">
         <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC3" t="n">
         <v>11.5</v>
@@ -1267,7 +1267,7 @@
         <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BG3" t="n">
         <v>1.01</v>
@@ -1276,31 +1276,31 @@
         <v>3.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BP3" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
@@ -1309,22 +1309,22 @@
         <v>8</v>
       </c>
       <c r="BT3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G4" t="n">
         <v>1.95</v>
@@ -1377,13 +1377,13 @@
         <v>5.9</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
         <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1488,10 +1488,10 @@
         <v>6.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW4" t="n">
         <v>6.4</v>
@@ -1500,16 +1500,16 @@
         <v>7.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18.5</v>
+        <v>5.3</v>
       </c>
       <c r="BA4" t="n">
         <v>6.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC4" t="n">
         <v>16</v>
@@ -1530,7 +1530,7 @@
         <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BJ4" t="n">
         <v>11.5</v>
@@ -1545,10 +1545,10 @@
         <v>10</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BP4" t="n">
         <v>14</v>
@@ -1560,25 +1560,25 @@
         <v>34</v>
       </c>
       <c r="BS4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT4" t="n">
         <v>9</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="G5" t="n">
         <v>970</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="I5" t="n">
         <v>970</v>
       </c>
       <c r="J5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -1879,13 +1879,13 @@
         <v>1.55</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="I6" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K6" t="n">
         <v>5</v>
@@ -1897,13 +1897,13 @@
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
         <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
         <v>1.72</v>
@@ -1915,7 +1915,7 @@
         <v>2.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U6" t="n">
         <v>2</v>
@@ -1924,7 +1924,7 @@
         <v>1.15</v>
       </c>
       <c r="W6" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="X6" t="n">
         <v>24</v>
@@ -1936,7 +1936,7 @@
         <v>65</v>
       </c>
       <c r="AA6" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AB6" t="n">
         <v>11.5</v>
@@ -1951,7 +1951,7 @@
         <v>120</v>
       </c>
       <c r="AF6" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AG6" t="n">
         <v>12.5</v>
@@ -1969,7 +1969,7 @@
         <v>19</v>
       </c>
       <c r="AL6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM6" t="n">
         <v>140</v>
@@ -1987,10 +1987,10 @@
         <v>18.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="AT6" t="n">
         <v>7</v>
@@ -2002,7 +2002,7 @@
         <v>19.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AX6" t="n">
         <v>7.2</v>
@@ -2014,7 +2014,7 @@
         <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BB6" t="n">
         <v>10</v>
@@ -2023,80 +2023,80 @@
         <v>11.5</v>
       </c>
       <c r="BD6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE6" t="n">
         <v>4.3</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>4.6</v>
       </c>
       <c r="BF6" t="n">
         <v>5.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BO6" t="n">
         <v>3.2</v>
       </c>
-      <c r="BJ6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>3.3</v>
-      </c>
       <c r="BP6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BR6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BT6" t="n">
         <v>11</v>
       </c>
       <c r="BU6" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -2130,13 +2130,13 @@
         <v>4.7</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
         <v>1.7</v>
       </c>
       <c r="I7" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="J7" t="n">
         <v>3.8</v>
@@ -2151,7 +2151,7 @@
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O7" t="n">
         <v>1.25</v>
@@ -2160,13 +2160,13 @@
         <v>2.12</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R7" t="n">
         <v>1.43</v>
       </c>
       <c r="S7" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T7" t="n">
         <v>1.74</v>
@@ -2175,37 +2175,37 @@
         <v>2.12</v>
       </c>
       <c r="V7" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y7" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA7" t="n">
         <v>23</v>
       </c>
       <c r="AB7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AC7" t="n">
         <v>11.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
         <v>22</v>
       </c>
       <c r="AF7" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AG7" t="n">
         <v>24</v>
@@ -2214,7 +2214,7 @@
         <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ7" t="n">
         <v>140</v>
@@ -2223,7 +2223,7 @@
         <v>75</v>
       </c>
       <c r="AL7" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -2232,7 +2232,7 @@
         <v>75</v>
       </c>
       <c r="AO7" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AP7" t="n">
         <v>13.5</v>
@@ -2241,7 +2241,7 @@
         <v>7.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AS7" t="n">
         <v>13.5</v>
@@ -2259,7 +2259,7 @@
         <v>13</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AY7" t="n">
         <v>14</v>
@@ -2268,7 +2268,7 @@
         <v>13.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="BB7" t="n">
         <v>1.01</v>
@@ -2289,13 +2289,13 @@
         <v>7.2</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK7" t="n">
         <v>5.1</v>
@@ -2304,53 +2304,53 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT7" t="n">
         <v>4.7</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BV7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ7" t="n">
         <v>19.5</v>
       </c>
       <c r="CA7" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G8" t="n">
         <v>970</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I8" t="n">
         <v>970</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -2408,19 +2408,19 @@
         <v>1.05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P8" t="n">
         <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="R8" t="n">
         <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2429,10 +2429,10 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -2635,58 +2635,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="G9" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H9" t="n">
         <v>2.22</v>
       </c>
       <c r="I9" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J9" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="K9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="P9" t="n">
-        <v>3.15</v>
+        <v>2.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R9" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="S9" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="T9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="U9" t="n">
         <v>3.05</v>
       </c>
       <c r="V9" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W9" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X9" t="n">
         <v>40</v>
@@ -2716,7 +2716,7 @@
         <v>29</v>
       </c>
       <c r="AG9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH9" t="n">
         <v>14</v>
@@ -2737,128 +2737,128 @@
         <v>48</v>
       </c>
       <c r="AN9" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AO9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE9" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>8</v>
       </c>
       <c r="BF9" t="n">
         <v>5.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BH9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.6</v>
+        <v>2.12</v>
       </c>
       <c r="BJ9" t="n">
         <v>11.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.1</v>
+        <v>2.36</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="BN9" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.5</v>
+        <v>2.28</v>
       </c>
       <c r="BP9" t="n">
         <v>26</v>
       </c>
       <c r="BQ9" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BR9" t="n">
         <v>30</v>
       </c>
       <c r="BS9" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="BT9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.1</v>
+        <v>2.22</v>
       </c>
       <c r="BV9" t="n">
         <v>21</v>
       </c>
       <c r="BW9" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BX9" t="n">
         <v>29</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="BZ9" t="n">
         <v>16</v>
       </c>
       <c r="CA9" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -2889,28 +2889,28 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="G10" t="n">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="H10" t="n">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="I10" t="n">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K10" t="n">
         <v>4.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N10" t="n">
         <v>1.01</v>
@@ -2919,16 +2919,16 @@
         <v>1.18</v>
       </c>
       <c r="P10" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="R10" t="n">
         <v>1.59</v>
       </c>
       <c r="S10" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T10" t="n">
         <v>1.51</v>
@@ -2937,40 +2937,40 @@
         <v>2.56</v>
       </c>
       <c r="V10" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="W10" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="X10" t="n">
         <v>26</v>
       </c>
       <c r="Y10" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA10" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AB10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AC10" t="n">
         <v>10.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AF10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH10" t="n">
         <v>15.5</v>
@@ -2979,58 +2979,58 @@
         <v>32</v>
       </c>
       <c r="AJ10" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AK10" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AL10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM10" t="n">
         <v>65</v>
       </c>
       <c r="AN10" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AO10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AP10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR10" t="n">
         <v>6</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="AS10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW10" t="n">
         <v>6.4</v>
       </c>
-      <c r="AS10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AW10" t="n">
+      <c r="AX10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA10" t="n">
         <v>6.8</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>7</v>
       </c>
       <c r="BB10" t="n">
         <v>7.4</v>
@@ -3039,80 +3039,80 @@
         <v>6.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BH10" t="n">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ10" t="n">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>2.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN10" t="n">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BP10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>27</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BX10" t="n">
         <v>25</v>
       </c>
-      <c r="BQ10" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>26</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>36</v>
-      </c>
       <c r="BY10" t="n">
-        <v>2.76</v>
+        <v>7.2</v>
       </c>
       <c r="BZ10" t="n">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>2.64</v>
+        <v>6.2</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -3143,230 +3143,230 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="G11" t="n">
-        <v>1.79</v>
+        <v>2.02</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="I11" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="J11" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="K11" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="O11" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="S11" t="n">
         <v>2.06</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="U11" t="n">
-        <v>2.02</v>
+        <v>2.54</v>
       </c>
       <c r="V11" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
-        <v>2.26</v>
+        <v>1.98</v>
       </c>
       <c r="X11" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE11" t="n">
         <v>40</v>
       </c>
-      <c r="Y11" t="n">
-        <v>36</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC11" t="n">
+      <c r="AF11" t="n">
         <v>16</v>
       </c>
-      <c r="AD11" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>19</v>
-      </c>
       <c r="AG11" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>25</v>
+        <v>16.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO11" t="n">
         <v>28</v>
       </c>
-      <c r="AK11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP11" t="n">
-        <v>2.22</v>
+        <v>7.2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2.22</v>
+        <v>6.8</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.36</v>
+        <v>7.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.36</v>
+        <v>8.4</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.06</v>
+        <v>5.3</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.18</v>
+        <v>6.2</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.36</v>
+        <v>7.8</v>
       </c>
       <c r="AX11" t="n">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="AY11" t="n">
-        <v>2.04</v>
+        <v>5.2</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2.16</v>
+        <v>6</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.36</v>
+        <v>7.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>2.18</v>
+        <v>6.8</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.14</v>
+        <v>6.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.22</v>
+        <v>7</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.36</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.87</v>
+        <v>4.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.36</v>
+        <v>7.2</v>
       </c>
       <c r="BH11" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.05</v>
+        <v>2</v>
       </c>
       <c r="BJ11" t="n">
         <v>13</v>
       </c>
       <c r="BK11" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BQ11" t="n">
         <v>2.44</v>
       </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>2.52</v>
-      </c>
       <c r="BR11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BS11" t="n">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="BT11" t="n">
         <v>12.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.4</v>
+        <v>2.32</v>
       </c>
       <c r="BV11" t="n">
         <v>48</v>
       </c>
       <c r="BW11" t="n">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="BX11" t="n">
         <v>50</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="BZ11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="CA11" t="n">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -3400,10 +3400,10 @@
         <v>2.3</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I12" t="n">
         <v>4</v>
@@ -3415,22 +3415,22 @@
         <v>3.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M12" t="n">
         <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="O12" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P12" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="R12" t="n">
         <v>1.2</v>
@@ -3439,7 +3439,7 @@
         <v>4.8</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U12" t="n">
         <v>1.8</v>
@@ -3448,10 +3448,10 @@
         <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y12" t="n">
         <v>12.5</v>
@@ -3463,7 +3463,7 @@
         <v>95</v>
       </c>
       <c r="AB12" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AC12" t="n">
         <v>8.199999999999999</v>
@@ -3472,10 +3472,10 @@
         <v>970</v>
       </c>
       <c r="AE12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG12" t="n">
         <v>14</v>
@@ -3487,7 +3487,7 @@
         <v>90</v>
       </c>
       <c r="AJ12" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK12" t="n">
         <v>38</v>
@@ -3499,22 +3499,22 @@
         <v>190</v>
       </c>
       <c r="AN12" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AO12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ12" t="n">
         <v>9</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AT12" t="n">
         <v>6.6</v>
@@ -3523,104 +3523,104 @@
         <v>5.7</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="BJ12" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>3.2</v>
+        <v>8.6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO12" t="n">
         <v>4</v>
       </c>
-      <c r="BN12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>3.55</v>
-      </c>
       <c r="BP12" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>3.55</v>
+        <v>7.2</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
         <v>8.6</v>
       </c>
-      <c r="BU12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>46</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>3.75</v>
-      </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.85</v>
+        <v>9.4</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -3654,37 +3654,37 @@
         <v>2.3</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H13" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I13" t="n">
         <v>4.1</v>
       </c>
       <c r="J13" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="K13" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M13" t="n">
         <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="O13" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P13" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="R13" t="n">
         <v>1.2</v>
@@ -3696,13 +3696,13 @@
         <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V13" t="n">
         <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="X13" t="n">
         <v>9</v>
@@ -3723,7 +3723,7 @@
         <v>7.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AE13" t="n">
         <v>65</v>
@@ -3741,7 +3741,7 @@
         <v>85</v>
       </c>
       <c r="AJ13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK13" t="n">
         <v>34</v>
@@ -3762,25 +3762,25 @@
         <v>7.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR13" t="n">
-        <v>8.4</v>
+        <v>21</v>
       </c>
       <c r="AS13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT13" t="n">
         <v>6.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV13" t="n">
         <v>7.2</v>
       </c>
       <c r="AW13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AX13" t="n">
         <v>12</v>
@@ -3789,37 +3789,37 @@
         <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BA13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC13" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BD13" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG13" t="n">
         <v>10.5</v>
       </c>
-      <c r="BE13" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>25</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>11</v>
-      </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK13" t="n">
         <v>1.01</v>
@@ -3831,13 +3831,13 @@
         <v>1.01</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ13" t="n">
         <v>1.01</v>
@@ -3849,10 +3849,10 @@
         <v>1.01</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -3908,22 +3908,22 @@
         <v>2.28</v>
       </c>
       <c r="G14" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="H14" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="I14" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L14" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M14" t="n">
         <v>1.09</v>
@@ -3935,145 +3935,145 @@
         <v>1.4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="R14" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X14" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU14" t="n">
         <v>3.2</v>
       </c>
-      <c r="T14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK14" t="n">
         <v>1.01</v>
@@ -4085,13 +4085,13 @@
         <v>1.01</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO14" t="n">
         <v>1.01</v>
       </c>
       <c r="BP14" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ14" t="n">
         <v>1.01</v>
@@ -4103,7 +4103,7 @@
         <v>1.01</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU14" t="n">
         <v>1.01</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -4162,16 +4162,16 @@
         <v>2.06</v>
       </c>
       <c r="G15" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H15" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="I15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J15" t="n">
         <v>3.75</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.3</v>
       </c>
       <c r="K15" t="n">
         <v>4.3</v>
@@ -4180,136 +4180,136 @@
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="O15" t="n">
         <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.52</v>
+        <v>2.96</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="V15" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W15" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
         <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
         <v>1.03</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB15"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,10 +860,10 @@
         <v>1.89</v>
       </c>
       <c r="G2" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I2" t="n">
         <v>4.9</v>
@@ -899,7 +899,7 @@
         <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U2" t="n">
         <v>2.04</v>
@@ -908,7 +908,7 @@
         <v>1.26</v>
       </c>
       <c r="W2" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X2" t="n">
         <v>17</v>
@@ -1028,13 +1028,13 @@
         <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BN2" t="n">
         <v>4.8</v>
@@ -1052,10 +1052,10 @@
         <v>30</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU2" t="n">
         <v>5.8</v>
@@ -1064,13 +1064,13 @@
         <v>40</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 03:20:50</t>
+          <t>2026-06-04 05:28:11</t>
         </is>
       </c>
     </row>
@@ -1117,13 +1117,13 @@
         <v>1.59</v>
       </c>
       <c r="H3" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="I3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K3" t="n">
         <v>5</v>
@@ -1150,7 +1150,7 @@
         <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="T3" t="n">
         <v>1.89</v>
@@ -1159,7 +1159,7 @@
         <v>1.92</v>
       </c>
       <c r="V3" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W3" t="n">
         <v>2.68</v>
@@ -1174,7 +1174,7 @@
         <v>75</v>
       </c>
       <c r="AA3" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AB3" t="n">
         <v>10.5</v>
@@ -1273,58 +1273,58 @@
         <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN3" t="n">
         <v>4.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BP3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT3" t="n">
         <v>11</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 03:20:50</t>
+          <t>2026-06-04 05:28:11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
         <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1425,7 +1425,7 @@
         <v>16.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA4" t="n">
         <v>180</v>
@@ -1434,7 +1434,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4" t="n">
         <v>22</v>
@@ -1455,7 +1455,7 @@
         <v>110</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK4" t="n">
         <v>23</v>
@@ -1467,7 +1467,7 @@
         <v>180</v>
       </c>
       <c r="AN4" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AO4" t="n">
         <v>150</v>
@@ -1479,13 +1479,13 @@
         <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AS4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT4" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>6.4</v>
       </c>
       <c r="AU4" t="n">
         <v>6.8</v>
@@ -1494,19 +1494,19 @@
         <v>15</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AX4" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AY4" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BB4" t="n">
         <v>15</v>
@@ -1515,22 +1515,22 @@
         <v>16</v>
       </c>
       <c r="BD4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF4" t="n">
         <v>11.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BH4" t="n">
         <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="BJ4" t="n">
         <v>11.5</v>
@@ -1545,40 +1545,40 @@
         <v>10</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP4" t="n">
         <v>14</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="BR4" t="n">
         <v>34</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT4" t="n">
         <v>9</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
         <v>9</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>9.4</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 03:20:50</t>
+          <t>2026-06-04 05:28:11</t>
         </is>
       </c>
     </row>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O5" t="n">
         <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q5" t="n">
         <v>1.02</v>
@@ -1658,7 +1658,7 @@
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-04 03:20:50</t>
+          <t>2026-06-04 05:28:11</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>FBK Karlstad</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>IF Karlstad</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>1.09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.55</v>
+        <v>970</v>
       </c>
       <c r="H6" t="n">
-        <v>6.6</v>
+        <v>1.09</v>
       </c>
       <c r="I6" t="n">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="J6" t="n">
-        <v>4.4</v>
+        <v>1.09</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
         <v>1.05</v>
       </c>
-      <c r="N6" t="n">
-        <v>4.5</v>
-      </c>
       <c r="O6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="R6" t="n">
         <v>1.24</v>
       </c>
-      <c r="P6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.48</v>
-      </c>
       <c r="S6" t="n">
-        <v>2.8</v>
+        <v>1.26</v>
       </c>
       <c r="T6" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>2.72</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-04 03:20:50</t>
+          <t>2026-06-04 05:28:11</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KaPa</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K7" t="n">
         <v>4.7</v>
       </c>
-      <c r="G7" t="n">
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X7" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>6</v>
       </c>
-      <c r="H7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="BA7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BI7" t="n">
         <v>2.12</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V7" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X7" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="BJ7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>26</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BV7" t="n">
         <v>21</v>
       </c>
-      <c r="AC7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>140</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>22</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>9</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>8</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>12</v>
-      </c>
       <c r="BW7" t="n">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="BX7" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.2</v>
+        <v>2.68</v>
       </c>
       <c r="BZ7" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="CA7" t="n">
-        <v>6.6</v>
+        <v>2.5</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-04 03:20:50</t>
+          <t>2026-06-04 05:28:11</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,244 +2367,244 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FBK Karlstad</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IF Karlstad</t>
+          <t>Leiknir R</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.09</v>
+        <v>2.62</v>
       </c>
       <c r="G8" t="n">
-        <v>970</v>
+        <v>2.96</v>
       </c>
       <c r="H8" t="n">
-        <v>1.09</v>
+        <v>2.34</v>
       </c>
       <c r="I8" t="n">
-        <v>970</v>
+        <v>2.62</v>
       </c>
       <c r="J8" t="n">
-        <v>1.09</v>
+        <v>3.55</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="O8" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>2.46</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.26</v>
+        <v>1.54</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.59</v>
       </c>
       <c r="S8" t="n">
-        <v>1.26</v>
+        <v>2.36</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1.61</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.51</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-04 03:20:50</t>
+          <t>2026-06-04 05:28:11</t>
         </is>
       </c>
     </row>
@@ -2626,31 +2626,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.76</v>
+        <v>1.84</v>
       </c>
       <c r="G9" t="n">
-        <v>3.05</v>
+        <v>2.02</v>
       </c>
       <c r="H9" t="n">
-        <v>2.22</v>
+        <v>3.4</v>
       </c>
       <c r="I9" t="n">
-        <v>2.44</v>
+        <v>4.3</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="K9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2659,213 +2659,213 @@
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="O9" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="P9" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="S9" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="T9" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="U9" t="n">
-        <v>3.05</v>
+        <v>2.54</v>
       </c>
       <c r="V9" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.48</v>
+        <v>1.98</v>
       </c>
       <c r="X9" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE9" t="n">
         <v>40</v>
       </c>
-      <c r="Y9" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z9" t="n">
+      <c r="AF9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>23</v>
       </c>
-      <c r="AA9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>55</v>
-      </c>
       <c r="AK9" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="AL9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO9" t="n">
         <v>28</v>
       </c>
-      <c r="AM9" t="n">
-        <v>48</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>9</v>
-      </c>
       <c r="AP9" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX9" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="AY9" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AZ9" t="n">
         <v>6</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BH9" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="BJ9" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BK9" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="BN9" t="n">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BO9" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="BP9" t="n">
-        <v>26</v>
+        <v>17.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="BR9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BS9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY9" t="n">
         <v>2.7</v>
       </c>
-      <c r="BT9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>21</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>29</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>2.68</v>
-      </c>
       <c r="BZ9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="CA9" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-04 03:20:50</t>
+          <t>2026-06-04 05:28:11</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,251 +2875,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Wanderers (Uru)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Leiknir R</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="G10" t="n">
-        <v>3.05</v>
+        <v>2.58</v>
       </c>
       <c r="H10" t="n">
-        <v>2.34</v>
+        <v>3.45</v>
       </c>
       <c r="I10" t="n">
-        <v>2.68</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.35</v>
+        <v>2.94</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
       <c r="M10" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="O10" t="n">
-        <v>1.18</v>
+        <v>1.49</v>
       </c>
       <c r="P10" t="n">
-        <v>2.46</v>
+        <v>1.56</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.54</v>
+        <v>2.42</v>
       </c>
       <c r="R10" t="n">
-        <v>1.59</v>
+        <v>1.2</v>
       </c>
       <c r="S10" t="n">
-        <v>2.36</v>
+        <v>4.8</v>
       </c>
       <c r="T10" t="n">
-        <v>1.51</v>
+        <v>2.02</v>
       </c>
       <c r="U10" t="n">
-        <v>2.56</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="X10" t="n">
-        <v>26</v>
+        <v>10.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AA10" t="n">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="AB10" t="n">
-        <v>18</v>
+        <v>8.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="AF10" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AG10" t="n">
         <v>14</v>
       </c>
       <c r="AH10" t="n">
-        <v>15.5</v>
+        <v>23</v>
       </c>
       <c r="AI10" t="n">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="AJ10" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AK10" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AL10" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AM10" t="n">
-        <v>65</v>
+        <v>190</v>
       </c>
       <c r="AN10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>17</v>
       </c>
-      <c r="AO10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ10" t="n">
+      <c r="BA10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG10" t="n">
         <v>5.7</v>
       </c>
-      <c r="AR10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS10" t="n">
+      <c r="BH10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT10" t="n">
         <v>7</v>
       </c>
-      <c r="AT10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF10" t="n">
+      <c r="BU10" t="n">
         <v>5.7</v>
       </c>
-      <c r="BG10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>20</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>27</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BV10" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BX10" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="BZ10" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-04 03:20:50</t>
+          <t>2026-06-04 05:28:11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,251 +3129,251 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Operario PR</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.84</v>
+        <v>2.16</v>
       </c>
       <c r="G11" t="n">
-        <v>2.02</v>
+        <v>2.34</v>
       </c>
       <c r="H11" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="I11" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3.65</v>
+        <v>2.92</v>
       </c>
       <c r="K11" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M11" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="N11" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="O11" t="n">
-        <v>1.17</v>
+        <v>1.51</v>
       </c>
       <c r="P11" t="n">
-        <v>2.36</v>
+        <v>1.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.5</v>
+        <v>2.56</v>
       </c>
       <c r="R11" t="n">
-        <v>1.65</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T11" t="n">
         <v>2.06</v>
       </c>
-      <c r="T11" t="n">
-        <v>1.53</v>
-      </c>
       <c r="U11" t="n">
-        <v>2.54</v>
+        <v>1.82</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W11" t="n">
-        <v>1.98</v>
+        <v>1.74</v>
       </c>
       <c r="X11" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="Y11" t="n">
-        <v>24</v>
+        <v>12.5</v>
       </c>
       <c r="Z11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK11" t="n">
         <v>36</v>
       </c>
-      <c r="AA11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>18</v>
-      </c>
       <c r="AL11" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="AM11" t="n">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="AN11" t="n">
-        <v>8.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="AO11" t="n">
-        <v>28</v>
+        <v>120</v>
       </c>
       <c r="AP11" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR11" t="n">
-        <v>7.6</v>
+        <v>22</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX11" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>5.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
         <v>6</v>
       </c>
       <c r="BA11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG11" t="n">
         <v>7.8</v>
       </c>
-      <c r="BB11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD11" t="n">
+      <c r="BH11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>16</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>19</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>12</v>
+      </c>
+      <c r="BT11" t="n">
         <v>7</v>
       </c>
-      <c r="BE11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BT11" t="n">
+      <c r="BU11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA11" t="n">
         <v>12.5</v>
       </c>
-      <c r="BU11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>48</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>50</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>18</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>2.46</v>
-      </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-04 03:20:50</t>
+          <t>2026-06-04 05:28:11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,251 +3383,251 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wanderers (Uru)</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G12" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="H12" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="I12" t="n">
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="L12" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M12" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="O12" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="P12" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.46</v>
+        <v>2.14</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="T12" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="U12" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="V12" t="n">
         <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="X12" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="Y12" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z12" t="n">
         <v>29</v>
       </c>
       <c r="AA12" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AB12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC12" t="n">
         <v>8.6</v>
       </c>
-      <c r="AC12" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AD12" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AE12" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH12" t="n">
         <v>23</v>
       </c>
       <c r="AI12" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AJ12" t="n">
         <v>38</v>
       </c>
       <c r="AK12" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM12" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="AN12" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AO12" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AP12" t="n">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9</v>
+        <v>3.75</v>
       </c>
       <c r="AR12" t="n">
-        <v>19</v>
+        <v>4.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.7</v>
+        <v>3.25</v>
       </c>
       <c r="AV12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC12" t="n">
         <v>4.5</v>
       </c>
-      <c r="AW12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB12" t="n">
+      <c r="BD12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BN12" t="n">
         <v>5.3</v>
       </c>
-      <c r="BC12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BO12" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BT12" t="n">
         <v>7</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-04 03:20:50</t>
+          <t>2026-06-04 05:28:11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,752 +3637,244 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>23:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atletico Ottawa</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="G13" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="H13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I13" t="n">
         <v>3.6</v>
       </c>
-      <c r="I13" t="n">
-        <v>4.1</v>
-      </c>
       <c r="J13" t="n">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="K13" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>2.62</v>
+        <v>3.9</v>
       </c>
       <c r="O13" t="n">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="P13" t="n">
-        <v>1.54</v>
+        <v>2.08</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.52</v>
+        <v>1.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X13" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>5.1</v>
       </c>
-      <c r="T13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X13" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AR13" t="n">
-        <v>21</v>
+        <v>5.9</v>
       </c>
       <c r="AS13" t="n">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="AT13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA13" t="n">
         <v>6.6</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="BB13" t="n">
         <v>6</v>
       </c>
-      <c r="AV13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BC13" t="n">
-        <v>9</v>
+        <v>5.7</v>
       </c>
       <c r="BD13" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="BF13" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BG13" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.84</v>
+        <v>4.8</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.36</v>
+        <v>2.76</v>
       </c>
       <c r="BJ13" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BN13" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>4</v>
+        <v>1.27</v>
       </c>
       <c r="BP13" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BT13" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.3</v>
+        <v>1.27</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-04 03:20:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Chilean Primera B</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>San Luis</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>San Marcos</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="H14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I14" t="n">
-        <v>4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X14" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB14" t="inlineStr">
-        <is>
-          <t>2026-06-04 03:20:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>23:00:00</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Vancouver FC</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Atletico Ottawa</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="X15" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="CB15" t="inlineStr">
-        <is>
-          <t>2026-06-04 03:20:50</t>
+          <t>2026-06-04 05:28:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
@@ -866,13 +866,13 @@
         <v>4.2</v>
       </c>
       <c r="I2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
         <v>1.34</v>
@@ -881,7 +881,7 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O2" t="n">
         <v>1.32</v>
@@ -905,7 +905,7 @@
         <v>2.04</v>
       </c>
       <c r="V2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W2" t="n">
         <v>1.94</v>
@@ -914,43 +914,43 @@
         <v>17</v>
       </c>
       <c r="Y2" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="Z2" t="n">
         <v>36</v>
       </c>
       <c r="AA2" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2" t="n">
         <v>22</v>
       </c>
       <c r="AE2" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG2" t="n">
         <v>12.5</v>
       </c>
-      <c r="AG2" t="n">
-        <v>11</v>
-      </c>
       <c r="AH2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AI2" t="n">
         <v>70</v>
       </c>
       <c r="AJ2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL2" t="n">
         <v>40</v>
@@ -968,13 +968,13 @@
         <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>20</v>
+        <v>5.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="AT2" t="n">
         <v>7.6</v>
@@ -986,10 +986,10 @@
         <v>13</v>
       </c>
       <c r="AW2" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY2" t="n">
         <v>7.8</v>
@@ -998,7 +998,7 @@
         <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="BB2" t="n">
         <v>16.5</v>
@@ -1007,22 +1007,22 @@
         <v>15.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.6</v>
+        <v>30</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="BH2" t="n">
         <v>3.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BJ2" t="n">
         <v>10.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -1111,55 +1111,55 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G3" t="n">
         <v>1.59</v>
       </c>
       <c r="H3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
         <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="O3" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P3" t="n">
         <v>2.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="U3" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="W3" t="n">
         <v>2.68</v>
@@ -1168,13 +1168,13 @@
         <v>22</v>
       </c>
       <c r="Y3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AA3" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="AB3" t="n">
         <v>10.5</v>
@@ -1186,13 +1186,13 @@
         <v>34</v>
       </c>
       <c r="AE3" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AF3" t="n">
         <v>11.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
         <v>28</v>
@@ -1210,13 +1210,13 @@
         <v>44</v>
       </c>
       <c r="AM3" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AO3" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AP3" t="n">
         <v>13</v>
@@ -1231,13 +1231,13 @@
         <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU3" t="n">
         <v>7.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW3" t="n">
         <v>1.01</v>
@@ -1273,58 +1273,58 @@
         <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="G4" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="I4" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1392,7 +1392,7 @@
         <v>3.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="P4" t="n">
         <v>1.73</v>
@@ -1407,22 +1407,22 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="U4" t="n">
         <v>1.86</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W4" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X4" t="n">
         <v>14</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z4" t="n">
         <v>42</v>
@@ -1434,16 +1434,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AF4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG4" t="n">
         <v>11</v>
@@ -1455,10 +1455,10 @@
         <v>110</v>
       </c>
       <c r="AJ4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AL4" t="n">
         <v>48</v>
@@ -1470,7 +1470,7 @@
         <v>17</v>
       </c>
       <c r="AO4" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP4" t="n">
         <v>8.6</v>
@@ -1479,58 +1479,58 @@
         <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY4" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.6</v>
+        <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC4" t="n">
         <v>16</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BF4" t="n">
         <v>11.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BH4" t="n">
         <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.76</v>
+        <v>2.52</v>
       </c>
       <c r="BJ4" t="n">
         <v>11.5</v>
@@ -1554,7 +1554,7 @@
         <v>14</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9.6</v>
+        <v>6</v>
       </c>
       <c r="BR4" t="n">
         <v>34</v>
@@ -1566,7 +1566,7 @@
         <v>9</v>
       </c>
       <c r="BU4" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>3.05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I7" t="n">
         <v>2.44</v>
@@ -2151,13 +2151,13 @@
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>6.4</v>
+        <v>1.02</v>
       </c>
       <c r="O7" t="n">
         <v>1.12</v>
       </c>
       <c r="P7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q7" t="n">
         <v>1.37</v>
@@ -2175,13 +2175,13 @@
         <v>3.05</v>
       </c>
       <c r="V7" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W7" t="n">
         <v>1.48</v>
       </c>
       <c r="X7" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="Y7" t="n">
         <v>22</v>
@@ -2196,7 +2196,7 @@
         <v>25</v>
       </c>
       <c r="AC7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD7" t="n">
         <v>13</v>
@@ -2220,10 +2220,10 @@
         <v>55</v>
       </c>
       <c r="AK7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL7" t="n">
         <v>27</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>28</v>
       </c>
       <c r="AM7" t="n">
         <v>48</v>
@@ -2235,58 +2235,58 @@
         <v>9</v>
       </c>
       <c r="AP7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS7" t="n">
         <v>8.6</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AT7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU7" t="n">
         <v>5.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA7" t="n">
         <v>7.8</v>
       </c>
-      <c r="AY7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ7" t="n">
+      <c r="BB7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF7" t="n">
         <v>6</v>
       </c>
-      <c r="BA7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BG7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH7" t="n">
         <v>7.6</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="G8" t="n">
         <v>2.96</v>
@@ -2393,7 +2393,7 @@
         <v>2.62</v>
       </c>
       <c r="J8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
         <v>4.5</v>
@@ -2411,7 +2411,7 @@
         <v>1.18</v>
       </c>
       <c r="P8" t="n">
-        <v>2.46</v>
+        <v>2.24</v>
       </c>
       <c r="Q8" t="n">
         <v>1.54</v>
@@ -2420,7 +2420,7 @@
         <v>1.59</v>
       </c>
       <c r="S8" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="T8" t="n">
         <v>1.51</v>
@@ -2435,112 +2435,112 @@
         <v>1.51</v>
       </c>
       <c r="X8" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Y8" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB8" t="n">
         <v>21</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AC8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI8" t="n">
         <v>36</v>
       </c>
-      <c r="AB8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI8" t="n">
+      <c r="AJ8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK8" t="n">
         <v>32</v>
       </c>
-      <c r="AJ8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>28</v>
-      </c>
       <c r="AL8" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM8" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AN8" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AP8" t="n">
-        <v>6.4</v>
+        <v>3.75</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="AS8" t="n">
-        <v>7</v>
+        <v>3.9</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.8</v>
+        <v>3.55</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.7</v>
+        <v>3.15</v>
       </c>
       <c r="AV8" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.4</v>
+        <v>3.75</v>
       </c>
       <c r="AX8" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="AY8" t="n">
-        <v>5.3</v>
+        <v>3.35</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.5</v>
+        <v>3.45</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.8</v>
+        <v>3.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.4</v>
+        <v>3.95</v>
       </c>
       <c r="BC8" t="n">
-        <v>6.6</v>
+        <v>3.75</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.8</v>
+        <v>3.85</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.6</v>
+        <v>4</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.3</v>
+        <v>3.35</v>
       </c>
       <c r="BH8" t="n">
         <v>4.6</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -2665,13 +2665,13 @@
         <v>1.17</v>
       </c>
       <c r="P9" t="n">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="Q9" t="n">
         <v>1.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="S9" t="n">
         <v>2.06</v>
@@ -2689,112 +2689,112 @@
         <v>1.98</v>
       </c>
       <c r="X9" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Y9" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Z9" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AA9" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AB9" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AF9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AG9" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AI9" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AJ9" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AK9" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AL9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM9" t="n">
         <v>60</v>
       </c>
       <c r="AN9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AO9" t="n">
         <v>28</v>
       </c>
       <c r="AP9" t="n">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6.8</v>
+        <v>4.1</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.3</v>
+        <v>3.55</v>
       </c>
       <c r="AV9" t="n">
-        <v>6.2</v>
+        <v>3.95</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="AX9" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="AY9" t="n">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.8</v>
+        <v>4.1</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="BD9" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="BH9" t="n">
         <v>6.8</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
         <v>2.58</v>
       </c>
       <c r="H10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I10" t="n">
         <v>4</v>
@@ -2913,16 +2913,16 @@
         <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="O10" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P10" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R10" t="n">
         <v>1.2</v>
@@ -2955,7 +2955,7 @@
         <v>95</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC10" t="n">
         <v>8.199999999999999</v>
@@ -2967,7 +2967,7 @@
         <v>60</v>
       </c>
       <c r="AF10" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AG10" t="n">
         <v>14</v>
@@ -3006,19 +3006,19 @@
         <v>19</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AT10" t="n">
         <v>6.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AX10" t="n">
         <v>10.5</v>
@@ -3030,25 +3030,25 @@
         <v>17</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BD10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF10" t="n">
         <v>5.6</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BG10" t="n">
         <v>6</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>5.7</v>
       </c>
       <c r="BH10" t="n">
         <v>2.88</v>
@@ -3090,7 +3090,7 @@
         <v>7</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -3155,10 +3155,10 @@
         <v>4.6</v>
       </c>
       <c r="J11" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L11" t="n">
         <v>1.5</v>
@@ -3173,7 +3173,7 @@
         <v>1.51</v>
       </c>
       <c r="P11" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q11" t="n">
         <v>2.56</v>
@@ -3182,22 +3182,22 @@
         <v>1.2</v>
       </c>
       <c r="S11" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V11" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
         <v>1.74</v>
       </c>
       <c r="X11" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y11" t="n">
         <v>12.5</v>
@@ -3218,7 +3218,7 @@
         <v>970</v>
       </c>
       <c r="AE11" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AF11" t="n">
         <v>15</v>
@@ -3239,13 +3239,13 @@
         <v>36</v>
       </c>
       <c r="AL11" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM11" t="n">
         <v>190</v>
       </c>
       <c r="AN11" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO11" t="n">
         <v>120</v>
@@ -3260,7 +3260,7 @@
         <v>22</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT11" t="n">
         <v>6.2</v>
@@ -3272,7 +3272,7 @@
         <v>14.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AX11" t="n">
         <v>10.5</v>
@@ -3281,28 +3281,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BA11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD11" t="n">
         <v>7.6</v>
       </c>
-      <c r="BB11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BE11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG11" t="n">
         <v>8</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>7.8</v>
       </c>
       <c r="BH11" t="n">
         <v>2.8</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
         <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="O12" t="n">
         <v>1.4</v>
@@ -3460,7 +3460,7 @@
         <v>29</v>
       </c>
       <c r="AA12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB12" t="n">
         <v>9.800000000000001</v>
@@ -3520,7 +3520,7 @@
         <v>3.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AV12" t="n">
         <v>4</v>
@@ -3541,7 +3541,7 @@
         <v>4.8</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BC12" t="n">
         <v>4.5</v>
@@ -3562,7 +3562,7 @@
         <v>3.15</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="BJ12" t="n">
         <v>11</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G13" t="n">
         <v>2.28</v>
@@ -3660,7 +3660,7 @@
         <v>3.25</v>
       </c>
       <c r="I13" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J13" t="n">
         <v>3.75</v>
@@ -3675,22 +3675,22 @@
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O13" t="n">
         <v>1.27</v>
       </c>
       <c r="P13" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="Q13" t="n">
         <v>1.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="S13" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T13" t="n">
         <v>1.68</v>
@@ -3699,31 +3699,31 @@
         <v>2.22</v>
       </c>
       <c r="V13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X13" t="n">
         <v>23</v>
       </c>
       <c r="Y13" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="Z13" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AA13" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB13" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AD13" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AE13" t="n">
         <v>46</v>
@@ -3732,13 +3732,13 @@
         <v>15.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH13" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AI13" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AJ13" t="n">
         <v>29</v>
@@ -3753,64 +3753,64 @@
         <v>100</v>
       </c>
       <c r="AN13" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AO13" t="n">
         <v>40</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="AU13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB13" t="n">
         <v>4.2</v>
       </c>
-      <c r="AV13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>6</v>
-      </c>
       <c r="BC13" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE13" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="BF13" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH13" t="n">
         <v>4.8</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
@@ -863,46 +863,46 @@
         <v>2.06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I2" t="n">
         <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K2" t="n">
         <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S2" t="n">
         <v>3.55</v>
       </c>
-      <c r="O2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.4</v>
-      </c>
       <c r="T2" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="U2" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="V2" t="n">
         <v>1.25</v>
@@ -911,7 +911,7 @@
         <v>1.94</v>
       </c>
       <c r="X2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y2" t="n">
         <v>18.5</v>
@@ -923,13 +923,13 @@
         <v>130</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
         <v>65</v>
@@ -941,7 +941,7 @@
         <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
         <v>70</v>
@@ -959,10 +959,10 @@
         <v>130</v>
       </c>
       <c r="AN2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO2" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AP2" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
         <v>11.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AT2" t="n">
         <v>7.6</v>
@@ -986,7 +986,7 @@
         <v>13</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AX2" t="n">
         <v>10</v>
@@ -998,7 +998,7 @@
         <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BB2" t="n">
         <v>16.5</v>
@@ -1010,19 +1010,19 @@
         <v>30</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF2" t="n">
         <v>12</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="BJ2" t="n">
         <v>10.5</v>
@@ -1040,7 +1040,7 @@
         <v>4.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BP2" t="n">
         <v>14.5</v>
@@ -1049,10 +1049,10 @@
         <v>6</v>
       </c>
       <c r="BR2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT2" t="n">
         <v>8.199999999999999</v>
@@ -1061,16 +1061,16 @@
         <v>5.8</v>
       </c>
       <c r="BV2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BW2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
@@ -1114,16 +1114,16 @@
         <v>1.53</v>
       </c>
       <c r="G3" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H3" t="n">
         <v>6.8</v>
       </c>
       <c r="I3" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="K3" t="n">
         <v>5</v>
@@ -1135,55 +1135,55 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="S3" t="n">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="T3" t="n">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="U3" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="V3" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W3" t="n">
         <v>2.68</v>
       </c>
       <c r="X3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z3" t="n">
         <v>80</v>
       </c>
       <c r="AA3" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AB3" t="n">
         <v>10.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AE3" t="n">
         <v>140</v>
@@ -1195,13 +1195,13 @@
         <v>12.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI3" t="n">
         <v>120</v>
       </c>
       <c r="AJ3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK3" t="n">
         <v>19.5</v>
@@ -1213,16 +1213,16 @@
         <v>160</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO3" t="n">
         <v>170</v>
       </c>
       <c r="AP3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR3" t="n">
         <v>1.01</v>
@@ -1234,7 +1234,7 @@
         <v>6.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV3" t="n">
         <v>20</v>
@@ -1243,13 +1243,13 @@
         <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AY3" t="n">
         <v>7.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA3" t="n">
         <v>1.01</v>
@@ -1267,7 +1267,7 @@
         <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BG3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>1.85</v>
       </c>
       <c r="G4" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="H4" t="n">
         <v>4.7</v>
@@ -1380,7 +1380,7 @@
         <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.45</v>
@@ -1392,7 +1392,7 @@
         <v>3.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="P4" t="n">
         <v>1.73</v>
@@ -1407,7 +1407,7 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U4" t="n">
         <v>1.86</v>
@@ -1434,7 +1434,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4" t="n">
         <v>21</v>
@@ -1458,7 +1458,7 @@
         <v>23</v>
       </c>
       <c r="AK4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL4" t="n">
         <v>48</v>
@@ -1479,34 +1479,34 @@
         <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AV4" t="n">
         <v>14.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AX4" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ4" t="n">
         <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BB4" t="n">
         <v>15.5</v>
@@ -1515,16 +1515,16 @@
         <v>16</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BF4" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BH4" t="n">
         <v>3.2</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
@@ -1619,46 +1619,46 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.09</v>
+        <v>2.92</v>
       </c>
       <c r="G5" t="n">
-        <v>970</v>
+        <v>4.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.09</v>
+        <v>2.46</v>
       </c>
       <c r="I5" t="n">
-        <v>970</v>
+        <v>3.1</v>
       </c>
       <c r="J5" t="n">
-        <v>1.09</v>
+        <v>2.56</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>1.28</v>
+        <v>2.22</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="P5" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.02</v>
+        <v>2.78</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S5" t="n">
-        <v>1.61</v>
+        <v>3.45</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
@@ -2151,16 +2151,16 @@
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>1.02</v>
+        <v>7.6</v>
       </c>
       <c r="O7" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R7" t="n">
         <v>1.89</v>
@@ -2175,13 +2175,13 @@
         <v>3.05</v>
       </c>
       <c r="V7" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W7" t="n">
         <v>1.48</v>
       </c>
       <c r="X7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Y7" t="n">
         <v>22</v>
@@ -2238,7 +2238,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR7" t="n">
         <v>7.6</v>
@@ -2250,7 +2250,7 @@
         <v>7.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AV7" t="n">
         <v>6</v>
@@ -2289,68 +2289,68 @@
         <v>5</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
         <v>2.96</v>
       </c>
       <c r="H8" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="I8" t="n">
         <v>2.62</v>
@@ -2402,28 +2402,28 @@
         <v>1.24</v>
       </c>
       <c r="M8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P8" t="n">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="R8" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S8" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="T8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U8" t="n">
         <v>2.56</v>
@@ -2486,7 +2486,7 @@
         <v>19.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AP8" t="n">
         <v>3.75</v>
@@ -2495,10 +2495,10 @@
         <v>3.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AT8" t="n">
         <v>3.55</v>
@@ -2510,7 +2510,7 @@
         <v>3.3</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AX8" t="n">
         <v>3.7</v>
@@ -2525,13 +2525,13 @@
         <v>3.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BC8" t="n">
         <v>3.75</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BE8" t="n">
         <v>4</v>
@@ -2546,7 +2546,7 @@
         <v>4.6</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="BJ8" t="n">
         <v>8.800000000000001</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
@@ -2635,25 +2635,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G9" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H9" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I9" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
         <v>4.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
@@ -2662,46 +2662,46 @@
         <v>1.01</v>
       </c>
       <c r="O9" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P9" t="n">
-        <v>2.24</v>
+        <v>2.66</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R9" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="S9" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="T9" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="U9" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W9" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z9" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AA9" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AB9" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC9" t="n">
         <v>13</v>
@@ -2710,10 +2710,10 @@
         <v>21</v>
       </c>
       <c r="AE9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF9" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG9" t="n">
         <v>13.5</v>
@@ -2722,7 +2722,7 @@
         <v>19</v>
       </c>
       <c r="AI9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ9" t="n">
         <v>28</v>
@@ -2731,134 +2731,134 @@
         <v>22</v>
       </c>
       <c r="AL9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM9" t="n">
         <v>60</v>
       </c>
       <c r="AN9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>21</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>32</v>
+      </c>
+      <c r="BY9" t="n">
         <v>8.4</v>
       </c>
-      <c r="AO9" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>48</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>50</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>2.7</v>
-      </c>
       <c r="BZ9" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="CA9" t="n">
-        <v>2.46</v>
+        <v>6.2</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>2.3</v>
       </c>
       <c r="G10" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H10" t="n">
         <v>3.4</v>
@@ -2904,7 +2904,7 @@
         <v>2.94</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L10" t="n">
         <v>1.47</v>
@@ -2913,13 +2913,13 @@
         <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="O10" t="n">
         <v>1.48</v>
       </c>
       <c r="P10" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="Q10" t="n">
         <v>2.44</v>
@@ -2931,7 +2931,7 @@
         <v>4.8</v>
       </c>
       <c r="T10" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U10" t="n">
         <v>1.8</v>
@@ -2940,7 +2940,7 @@
         <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X10" t="n">
         <v>10.5</v>
@@ -2949,7 +2949,7 @@
         <v>12.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA10" t="n">
         <v>95</v>
@@ -3015,10 +3015,10 @@
         <v>6.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX10" t="n">
         <v>10.5</v>
@@ -3030,16 +3030,16 @@
         <v>17</v>
       </c>
       <c r="BA10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD10" t="n">
         <v>6</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>5.9</v>
       </c>
       <c r="BE10" t="n">
         <v>6.4</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>2.16</v>
       </c>
       <c r="G11" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H11" t="n">
         <v>4.1</v>
@@ -3158,7 +3158,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L11" t="n">
         <v>1.5</v>
@@ -3167,37 +3167,37 @@
         <v>1.12</v>
       </c>
       <c r="N11" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="O11" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="P11" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
         <v>5.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U11" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V11" t="n">
         <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y11" t="n">
         <v>12.5</v>
@@ -3233,34 +3233,34 @@
         <v>110</v>
       </c>
       <c r="AJ11" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AK11" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL11" t="n">
         <v>60</v>
       </c>
       <c r="AM11" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO11" t="n">
         <v>120</v>
       </c>
       <c r="AP11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ11" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AR11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AT11" t="n">
         <v>6.2</v>
@@ -3269,19 +3269,19 @@
         <v>6.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AX11" t="n">
         <v>10.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BA11" t="n">
         <v>8</v>
@@ -3290,16 +3290,16 @@
         <v>7</v>
       </c>
       <c r="BC11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.6</v>
+        <v>40</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BF11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BG11" t="n">
         <v>8</v>
@@ -3344,7 +3344,7 @@
         <v>7</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD12" t="n">
         <v>18</v>
@@ -3505,64 +3505,64 @@
         <v>70</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AU12" t="n">
         <v>3.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AY12" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG12" t="n">
         <v>5</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>4.8</v>
       </c>
       <c r="BH12" t="n">
         <v>3.15</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="BJ12" t="n">
         <v>11</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G13" t="n">
         <v>2.28</v>
@@ -3675,19 +3675,19 @@
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="O13" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P13" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="Q13" t="n">
         <v>1.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
         <v>2.92</v>
@@ -3699,31 +3699,31 @@
         <v>2.22</v>
       </c>
       <c r="V13" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
         <v>23</v>
       </c>
       <c r="Y13" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AA13" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AB13" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AE13" t="n">
         <v>46</v>
@@ -3732,13 +3732,13 @@
         <v>15.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AJ13" t="n">
         <v>29</v>
@@ -3753,128 +3753,128 @@
         <v>100</v>
       </c>
       <c r="AN13" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AO13" t="n">
         <v>40</v>
       </c>
       <c r="AP13" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="AQ13" t="n">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="AR13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU13" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AV13" t="n">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>3.75</v>
+        <v>5.1</v>
       </c>
       <c r="AY13" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BC13" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH13" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BN13" t="n">
         <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB13"/>
+  <dimension ref="A1:CB15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="G2" t="n">
         <v>2.06</v>
@@ -866,37 +866,37 @@
         <v>4.3</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P2" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R2" t="n">
         <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="T2" t="n">
         <v>1.84</v>
@@ -911,118 +911,118 @@
         <v>1.94</v>
       </c>
       <c r="X2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y2" t="n">
         <v>18.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AA2" t="n">
         <v>130</v>
       </c>
       <c r="AB2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE2" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AF2" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AG2" t="n">
         <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AK2" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AL2" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AM2" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU2" t="n">
         <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="AX2" t="n">
         <v>10</v>
       </c>
       <c r="AY2" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BB2" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="BF2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BJ2" t="n">
         <v>10.5</v>
@@ -1034,16 +1034,16 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN2" t="n">
         <v>4.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="BP2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ2" t="n">
         <v>6</v>
@@ -1064,7 +1064,7 @@
         <v>42</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX2" t="n">
         <v>55</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -1114,28 +1114,28 @@
         <v>1.53</v>
       </c>
       <c r="G3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H3" t="n">
         <v>6.8</v>
       </c>
       <c r="I3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O3" t="n">
         <v>1.26</v>
@@ -1144,49 +1144,49 @@
         <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R3" t="n">
         <v>1.43</v>
       </c>
       <c r="S3" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T3" t="n">
         <v>1.92</v>
       </c>
       <c r="U3" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V3" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W3" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="X3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Z3" t="n">
         <v>80</v>
       </c>
       <c r="AA3" t="n">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="AB3" t="n">
         <v>10.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD3" t="n">
         <v>36</v>
       </c>
       <c r="AE3" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF3" t="n">
         <v>11.5</v>
@@ -1195,10 +1195,10 @@
         <v>12.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ3" t="n">
         <v>16.5</v>
@@ -1216,115 +1216,115 @@
         <v>9</v>
       </c>
       <c r="AO3" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AP3" t="n">
-        <v>13.5</v>
+        <v>3.75</v>
       </c>
       <c r="AQ3" t="n">
-        <v>18</v>
+        <v>3.9</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU3" t="n">
         <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AY3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17</v>
+        <v>3.9</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB3" t="n">
-        <v>10</v>
+        <v>3.6</v>
       </c>
       <c r="BC3" t="n">
         <v>11.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BQ3" t="n">
         <v>5.6</v>
       </c>
-      <c r="BG3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="G4" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="H4" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
@@ -1383,46 +1383,46 @@
         <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="R4" t="n">
         <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T4" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="U4" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="V4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W4" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X4" t="n">
         <v>14</v>
       </c>
       <c r="Y4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Z4" t="n">
         <v>42</v>
@@ -1431,16 +1431,16 @@
         <v>180</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE4" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AF4" t="n">
         <v>11.5</v>
@@ -1449,7 +1449,7 @@
         <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AI4" t="n">
         <v>110</v>
@@ -1458,7 +1458,7 @@
         <v>23</v>
       </c>
       <c r="AK4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL4" t="n">
         <v>48</v>
@@ -1467,7 +1467,7 @@
         <v>180</v>
       </c>
       <c r="AN4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO4" t="n">
         <v>140</v>
@@ -1476,67 +1476,67 @@
         <v>8.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU4" t="n">
         <v>5.9</v>
       </c>
-      <c r="AU4" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AV4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="AX4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AZ4" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC4" t="n">
         <v>15.5</v>
       </c>
-      <c r="BA4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>16</v>
-      </c>
       <c r="BD4" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BF4" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="BH4" t="n">
         <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BJ4" t="n">
         <v>11.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1545,7 +1545,7 @@
         <v>10</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO4" t="n">
         <v>3.35</v>
@@ -1560,25 +1560,25 @@
         <v>34</v>
       </c>
       <c r="BS4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT4" t="n">
         <v>9</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -1619,175 +1619,175 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU5" t="n">
         <v>2.92</v>
       </c>
-      <c r="G5" t="n">
+      <c r="AV5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BA5" t="n">
         <v>4.2</v>
       </c>
-      <c r="H5" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="BB5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG5" t="n">
         <v>4</v>
       </c>
-      <c r="L5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>2.74</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK5" t="n">
         <v>1.01</v>
@@ -1799,37 +1799,37 @@
         <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO5" t="n">
         <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ5" t="n">
         <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS5" t="n">
         <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU5" t="n">
         <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW5" t="n">
         <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
         <v>1.01</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,33 +1859,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FBK Karlstad</t>
+          <t>FK Kudrivka</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IF Karlstad</t>
+          <t>Agrobiznes Volochysk</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="G6" t="n">
-        <v>970</v>
+        <v>110</v>
       </c>
       <c r="H6" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="I6" t="n">
-        <v>970</v>
+        <v>110</v>
       </c>
       <c r="J6" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="n">
         <v>950</v>
@@ -1897,22 +1897,22 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.05</v>
+        <v>1.28</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.26</v>
+        <v>1.78</v>
       </c>
       <c r="R6" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.26</v>
+        <v>2.24</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1921,10 +1921,10 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,180 +2113,180 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>FBK Karlstad</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>IF Karlstad</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>3.05</v>
+        <v>970</v>
       </c>
       <c r="H7" t="n">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>2.44</v>
+        <v>970</v>
       </c>
       <c r="J7" t="n">
-        <v>4.1</v>
+        <v>1.09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.7</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V7" t="n">
         <v>1.02</v>
       </c>
-      <c r="N7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.7</v>
-      </c>
       <c r="W7" t="n">
-        <v>1.48</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -2372,239 +2372,239 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Leiknir R</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="G8" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="I8" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="M8" t="n">
         <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="O8" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="P8" t="n">
-        <v>2.44</v>
+        <v>3.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="R8" t="n">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="S8" t="n">
-        <v>2.38</v>
+        <v>1.94</v>
       </c>
       <c r="T8" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="U8" t="n">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="V8" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="W8" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="X8" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="Y8" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="Z8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE8" t="n">
         <v>25</v>
       </c>
-      <c r="AA8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE8" t="n">
+      <c r="AF8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI8" t="n">
         <v>29</v>
       </c>
-      <c r="AF8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>36</v>
-      </c>
       <c r="AJ8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK8" t="n">
         <v>32</v>
       </c>
       <c r="AL8" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM8" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="AN8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>17</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD8" t="n">
         <v>19.5</v>
       </c>
-      <c r="AO8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU8" t="n">
+      <c r="BE8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG8" t="n">
         <v>3.15</v>
       </c>
-      <c r="AV8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>3.35</v>
-      </c>
       <c r="BH8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO8" t="n">
         <v>4.6</v>
       </c>
-      <c r="BI8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>4</v>
-      </c>
       <c r="BP8" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BR8" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BV8" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BX8" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="BY8" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BZ8" t="n">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="CA8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -2626,246 +2626,246 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Leiknir R</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.85</v>
+        <v>2.62</v>
       </c>
       <c r="G9" t="n">
-        <v>2.04</v>
+        <v>2.96</v>
       </c>
       <c r="H9" t="n">
-        <v>3.35</v>
+        <v>2.34</v>
       </c>
       <c r="I9" t="n">
-        <v>4.2</v>
+        <v>2.62</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P9" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="R9" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="S9" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="T9" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U9" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="V9" t="n">
-        <v>1.31</v>
+        <v>1.61</v>
       </c>
       <c r="W9" t="n">
-        <v>1.96</v>
+        <v>1.51</v>
       </c>
       <c r="X9" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI9" t="n">
         <v>36</v>
       </c>
-      <c r="Y9" t="n">
-        <v>28</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD9" t="n">
+      <c r="AJ9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA9" t="n">
         <v>21</v>
       </c>
-      <c r="AE9" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH9" t="n">
+      <c r="BB9" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC9" t="n">
         <v>19</v>
       </c>
-      <c r="AI9" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>26</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP9" t="n">
+      <c r="BD9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH9" t="n">
         <v>4.6</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BI9" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="BJ9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BP9" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BR9" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BS9" t="n">
         <v>7.4</v>
       </c>
       <c r="BT9" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="BV9" t="n">
-        <v>27</v>
+        <v>17.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="BX9" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ9" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="CA9" t="n">
         <v>6.2</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,251 +2875,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wanderers (Uru)</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="G10" t="n">
-        <v>2.56</v>
+        <v>2.06</v>
       </c>
       <c r="H10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J10" t="n">
         <v>4</v>
       </c>
-      <c r="J10" t="n">
-        <v>2.94</v>
-      </c>
       <c r="K10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="X10" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BI10" t="n">
         <v>3.35</v>
       </c>
-      <c r="L10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="X10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="BJ10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>21</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>30</v>
+      </c>
+      <c r="BY10" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AC10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG10" t="n">
+      <c r="BZ10" t="n">
         <v>14</v>
       </c>
-      <c r="AH10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS10" t="n">
+      <c r="CA10" t="n">
         <v>6.2</v>
       </c>
-      <c r="AT10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>9</v>
-      </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,251 +3129,251 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>CA Ituzaingo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Real Pilar FC</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.16</v>
+        <v>3.35</v>
       </c>
       <c r="G11" t="n">
-        <v>2.32</v>
+        <v>4.9</v>
       </c>
       <c r="H11" t="n">
-        <v>4.1</v>
+        <v>2.06</v>
       </c>
       <c r="I11" t="n">
-        <v>4.6</v>
+        <v>2.64</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="K11" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="L11" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M11" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.72</v>
+        <v>2.44</v>
       </c>
       <c r="O11" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="P11" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="S11" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="T11" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="V11" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Y11" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB11" t="n">
         <v>12.5</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AC11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF11" t="n">
         <v>32</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AG11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>120</v>
       </c>
-      <c r="AB11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF11" t="n">
+      <c r="AK11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>130</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>27</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BW11" t="n">
         <v>15</v>
       </c>
-      <c r="AG11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>8</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>16</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>19</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>9</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>12</v>
-      </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,498 +3383,1006 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Wanderers (Uru)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G12" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="H12" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="I12" t="n">
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="L12" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M12" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="O12" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="P12" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.14</v>
+        <v>2.44</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S12" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="U12" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="V12" t="n">
         <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X12" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA12" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC12" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD12" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AE12" t="n">
         <v>60</v>
       </c>
       <c r="AF12" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AG12" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH12" t="n">
         <v>23</v>
       </c>
       <c r="AI12" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AJ12" t="n">
         <v>38</v>
       </c>
       <c r="AK12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AL12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM12" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="AN12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AO12" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.85</v>
+        <v>9</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.6</v>
+        <v>19</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.5</v>
+        <v>6.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AW12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.1</v>
+        <v>10.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>3.85</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.4</v>
+        <v>17</v>
       </c>
       <c r="BA12" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BE12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN12" t="n">
         <v>5.2</v>
       </c>
-      <c r="BF12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BO12" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="BP12" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT12" t="n">
         <v>7</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Operario PR</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X13" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>22</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>13</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>12</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:52:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>San Marcos</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>19</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:52:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Canadian Premier League</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>23:00:00</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Vancouver FC</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Atletico Ottawa</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M13" t="n">
+      <c r="F15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M15" t="n">
         <v>1.05</v>
       </c>
-      <c r="N13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O13" t="n">
+      <c r="N15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O15" t="n">
         <v>1.26</v>
       </c>
-      <c r="P13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R13" t="n">
+      <c r="P15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.42</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X13" t="n">
+      <c r="S15" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X15" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK15" t="n">
         <v>23</v>
       </c>
-      <c r="Y13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z13" t="n">
+      <c r="AL15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV15" t="n">
         <v>27</v>
       </c>
-      <c r="AA13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK13" t="n">
+      <c r="BW15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>36</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BZ15" t="n">
         <v>23</v>
       </c>
-      <c r="AL13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE13" t="n">
+      <c r="CA15" t="n">
         <v>7</v>
       </c>
-      <c r="BF13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB13" t="inlineStr">
-        <is>
-          <t>2026-06-04 09:43:16</t>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB15"/>
+  <dimension ref="A1:CB20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,43 +866,43 @@
         <v>4.3</v>
       </c>
       <c r="I2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
         <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="M2" t="n">
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P2" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R2" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="U2" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V2" t="n">
         <v>1.25</v>
@@ -926,13 +926,13 @@
         <v>10</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
         <v>22</v>
       </c>
       <c r="AE2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AF2" t="n">
         <v>14.5</v>
@@ -941,43 +941,43 @@
         <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK2" t="n">
         <v>28</v>
       </c>
-      <c r="AK2" t="n">
-        <v>27</v>
-      </c>
       <c r="AL2" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM2" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN2" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AP2" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ2" t="n">
         <v>12.5</v>
       </c>
       <c r="AR2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS2" t="n">
         <v>5.1</v>
       </c>
-      <c r="AS2" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AT2" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AU2" t="n">
         <v>7</v>
@@ -986,7 +986,7 @@
         <v>15.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AX2" t="n">
         <v>10</v>
@@ -998,34 +998,34 @@
         <v>16.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BB2" t="n">
         <v>19.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD2" t="n">
-        <v>29</v>
+        <v>4.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BH2" t="n">
         <v>3.35</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK2" t="n">
         <v>5.2</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN2" t="n">
         <v>4.8</v>
@@ -1052,7 +1052,7 @@
         <v>32</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT2" t="n">
         <v>8.199999999999999</v>
@@ -1064,13 +1064,13 @@
         <v>42</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BX2" t="n">
         <v>55</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>1.53</v>
       </c>
       <c r="G3" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="H3" t="n">
         <v>6.8</v>
@@ -1123,13 +1123,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K3" t="n">
         <v>4.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
@@ -1141,28 +1141,28 @@
         <v>1.26</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q3" t="n">
         <v>1.76</v>
       </c>
       <c r="R3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V3" t="n">
         <v>1.14</v>
       </c>
       <c r="W3" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="X3" t="n">
         <v>22</v>
@@ -1174,13 +1174,13 @@
         <v>80</v>
       </c>
       <c r="AA3" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AB3" t="n">
         <v>10.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD3" t="n">
         <v>36</v>
@@ -1195,13 +1195,13 @@
         <v>12.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI3" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ3" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AK3" t="n">
         <v>19.5</v>
@@ -1213,118 +1213,118 @@
         <v>160</v>
       </c>
       <c r="AN3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO3" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.75</v>
+        <v>13</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AR3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS3" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS3" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AT3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AY3" t="n">
         <v>7.6</v>
       </c>
-      <c r="AU3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>3.9</v>
+        <v>17</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BB3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BC3" t="n">
         <v>3.6</v>
       </c>
-      <c r="BC3" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BD3" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12.5</v>
+        <v>1.91</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.15</v>
+        <v>2.76</v>
       </c>
       <c r="BP3" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.6</v>
+        <v>1.68</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.800000000000001</v>
+        <v>1.82</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.6</v>
+        <v>1.88</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>5.6</v>
+        <v>1.88</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -1368,13 +1368,13 @@
         <v>1.82</v>
       </c>
       <c r="G4" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="H4" t="n">
         <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
@@ -1389,13 +1389,13 @@
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O4" t="n">
         <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q4" t="n">
         <v>2.12</v>
@@ -1404,16 +1404,16 @@
         <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T4" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U4" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W4" t="n">
         <v>2.04</v>
@@ -1425,127 +1425,127 @@
         <v>21</v>
       </c>
       <c r="Z4" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AA4" t="n">
         <v>180</v>
       </c>
       <c r="AB4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD4" t="n">
         <v>24</v>
       </c>
       <c r="AE4" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AF4" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG4" t="n">
         <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI4" t="n">
         <v>110</v>
       </c>
       <c r="AJ4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AK4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AL4" t="n">
         <v>48</v>
       </c>
       <c r="AM4" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN4" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO4" t="n">
         <v>140</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS4" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="AT4" t="n">
         <v>6.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="AX4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY4" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="BB4" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="BH4" t="n">
         <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="BJ4" t="n">
         <v>11.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO4" t="n">
         <v>3.35</v>
@@ -1554,31 +1554,31 @@
         <v>14</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BR4" t="n">
         <v>34</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BT4" t="n">
         <v>9</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G5" t="n">
         <v>3.7</v>
@@ -1628,7 +1628,7 @@
         <v>2.48</v>
       </c>
       <c r="I5" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J5" t="n">
         <v>2.82</v>
@@ -1643,7 +1643,7 @@
         <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
         <v>1.55</v>
@@ -1652,7 +1652,7 @@
         <v>1.49</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
@@ -1727,7 +1727,7 @@
         <v>48</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AQ5" t="n">
         <v>3</v>
@@ -1742,10 +1742,10 @@
         <v>3.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AW5" t="n">
         <v>4</v>
@@ -1784,65 +1784,65 @@
         <v>2.74</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="BJ5" t="n">
         <v>12</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BN5" t="n">
         <v>6.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP5" t="n">
         <v>34</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BR5" t="n">
         <v>60</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BT5" t="n">
         <v>5.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BV5" t="n">
         <v>25</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BX5" t="n">
         <v>50</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -1873,175 +1873,175 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.02</v>
+        <v>1.62</v>
       </c>
       <c r="G6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="X6" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM6" t="n">
         <v>110</v>
       </c>
-      <c r="H6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I6" t="n">
-        <v>110</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K6" t="n">
-        <v>950</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI6" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK6" t="n">
         <v>1.01</v>
@@ -2053,50 +2053,50 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO6" t="n">
         <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ6" t="n">
         <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS6" t="n">
         <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU6" t="n">
         <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW6" t="n">
         <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA6" t="n">
         <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>970</v>
       </c>
       <c r="J7" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="G8" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="I8" t="n">
-        <v>2.44</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="K8" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>7.6</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R8" t="n">
         <v>1.12</v>
       </c>
-      <c r="P8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.9</v>
-      </c>
       <c r="S8" t="n">
-        <v>1.94</v>
+        <v>1.54</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,246 +2626,246 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Reynir Sandgeroi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Leiknir R</t>
+          <t>Augnablik</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="G9" t="n">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="I9" t="n">
-        <v>2.62</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="R9" t="n">
         <v>1.24</v>
       </c>
-      <c r="M9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.59</v>
-      </c>
       <c r="S9" t="n">
-        <v>2.34</v>
+        <v>1.11</v>
       </c>
       <c r="T9" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP9" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR9" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BV9" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX9" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,246 +2880,246 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Kormakur/Hvot</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>IF Magni</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="G10" t="n">
-        <v>2.06</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="I10" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="K10" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S10" t="n">
         <v>1.02</v>
       </c>
-      <c r="N10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.04</v>
-      </c>
       <c r="T10" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BP10" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BR10" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT10" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV10" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BX10" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,251 +3129,251 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CA Ituzaingo</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Real Pilar FC</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.35</v>
+        <v>1.87</v>
       </c>
       <c r="G11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="X11" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK11" t="n">
         <v>4.9</v>
       </c>
-      <c r="H11" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Y11" t="n">
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT11" t="n">
         <v>8</v>
       </c>
-      <c r="Z11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC11" t="n">
+      <c r="BU11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>30</v>
+      </c>
+      <c r="BY11" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="BZ11" t="n">
         <v>14</v>
       </c>
-      <c r="AE11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>240</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>130</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>27</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>21</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,251 +3383,251 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wanderers (Uru)</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>Leiknir R</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="G12" t="n">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="H12" t="n">
-        <v>3.4</v>
+        <v>2.34</v>
       </c>
       <c r="I12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X12" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE12" t="n">
         <v>4</v>
       </c>
-      <c r="J12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="BF12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO12" t="n">
         <v>4.8</v>
       </c>
-      <c r="T12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="X12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP12" t="n">
+      <c r="BP12" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>27</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>25</v>
+      </c>
+      <c r="BY12" t="n">
         <v>7.2</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS12" t="n">
+      <c r="BZ12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="CA12" t="n">
         <v>6.2</v>
       </c>
-      <c r="AT12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>9</v>
-      </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,251 +3637,251 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.26</v>
+        <v>2.72</v>
       </c>
       <c r="G13" t="n">
-        <v>2.42</v>
+        <v>2.96</v>
       </c>
       <c r="H13" t="n">
-        <v>3.95</v>
+        <v>2.32</v>
       </c>
       <c r="I13" t="n">
-        <v>4.3</v>
+        <v>2.54</v>
       </c>
       <c r="J13" t="n">
-        <v>2.92</v>
+        <v>3.7</v>
       </c>
       <c r="K13" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.54</v>
+        <v>1.18</v>
       </c>
       <c r="M13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="O13" t="n">
         <v>1.12</v>
       </c>
-      <c r="N13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.5</v>
-      </c>
       <c r="P13" t="n">
-        <v>1.55</v>
+        <v>3.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.52</v>
+        <v>1.39</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2</v>
+        <v>1.91</v>
       </c>
       <c r="S13" t="n">
-        <v>5.2</v>
+        <v>1.94</v>
       </c>
       <c r="T13" t="n">
-        <v>2.04</v>
+        <v>1.4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="W13" t="n">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="X13" t="n">
-        <v>970</v>
+        <v>46</v>
       </c>
       <c r="Y13" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="Z13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA13" t="n">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="AB13" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.8</v>
+        <v>14</v>
       </c>
       <c r="AD13" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="AF13" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="AG13" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="AJ13" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AK13" t="n">
         <v>32</v>
       </c>
       <c r="AL13" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AM13" t="n">
-        <v>190</v>
+        <v>46</v>
       </c>
       <c r="AN13" t="n">
-        <v>32</v>
+        <v>14.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>110</v>
+        <v>11</v>
       </c>
       <c r="AP13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BJ13" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX13" t="n">
+      <c r="BK13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>55</v>
+      </c>
+      <c r="BM13" t="n">
         <v>10.5</v>
       </c>
-      <c r="AY13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB13" t="n">
+      <c r="BN13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>22</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>15</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BY13" t="n">
         <v>7.8</v>
       </c>
-      <c r="BC13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>22</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>9</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>9</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>12</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW13" t="n">
+      <c r="BZ13" t="n">
         <v>11.5</v>
       </c>
-      <c r="BX13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>13</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA13" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,72 +3891,72 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Hviti Riddarinn</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Haukar</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="I14" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>2.62</v>
+        <v>1.25</v>
       </c>
       <c r="O14" t="n">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.12</v>
+        <v>1.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="T14" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4013,37 +4013,37 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
         <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
         <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
         <v>1.01</v>
@@ -4061,328 +4061,1598 @@
         <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
         <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN14" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP14" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BT14" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CA Ituzaingo</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Real Pilar FC</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>130</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>27</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>15</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:01:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Wanderers (Uru)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Danubio</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>9</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:01:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Plaza Colonia</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Huracan del Paso</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:01:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Operario PR</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>9</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>12</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>13</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>12</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:01:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>San Marcos</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:01:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Canadian Premier League</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>23:00:00</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Vancouver FC</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Atletico Ottawa</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="H15" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="I15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K15" t="n">
+      <c r="F20" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K20" t="n">
         <v>4.1</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L20" t="n">
         <v>1.3</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M20" t="n">
         <v>1.05</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N20" t="n">
         <v>4.1</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O20" t="n">
         <v>1.26</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P20" t="n">
         <v>2.06</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q20" t="n">
         <v>1.76</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="R20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S20" t="n">
         <v>2.96</v>
       </c>
-      <c r="T15" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U15" t="n">
+      <c r="T20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U20" t="n">
         <v>2.24</v>
       </c>
-      <c r="V15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X15" t="n">
+      <c r="V20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X20" t="n">
         <v>22</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Y20" t="n">
         <v>18</v>
       </c>
-      <c r="Z15" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="Z20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AX20" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AY20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
         <v>9.6</v>
       </c>
-      <c r="AD15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK15" t="n">
+      <c r="BN20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>36</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ20" t="n">
         <v>23</v>
       </c>
-      <c r="AL15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>27</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>36</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>8</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>23</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>7</v>
-      </c>
-      <c r="CB15" t="inlineStr">
-        <is>
-          <t>2026-06-04 11:52:00</t>
+      <c r="CA20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
@@ -860,7 +860,7 @@
         <v>1.91</v>
       </c>
       <c r="G2" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H2" t="n">
         <v>4.3</v>
@@ -875,7 +875,7 @@
         <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="M2" t="n">
         <v>1.08</v>
@@ -911,13 +911,13 @@
         <v>1.94</v>
       </c>
       <c r="X2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y2" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z2" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AA2" t="n">
         <v>130</v>
@@ -929,7 +929,7 @@
         <v>8.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
         <v>70</v>
@@ -950,7 +950,7 @@
         <v>25</v>
       </c>
       <c r="AK2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL2" t="n">
         <v>44</v>
@@ -959,10 +959,10 @@
         <v>150</v>
       </c>
       <c r="AN2" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AO2" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AP2" t="n">
         <v>9.199999999999999</v>
@@ -974,7 +974,7 @@
         <v>24</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT2" t="n">
         <v>7</v>
@@ -986,7 +986,7 @@
         <v>15.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AX2" t="n">
         <v>10</v>
@@ -998,7 +998,7 @@
         <v>16.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB2" t="n">
         <v>19.5</v>
@@ -1007,16 +1007,16 @@
         <v>19</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF2" t="n">
         <v>13.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH2" t="n">
         <v>3.35</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>1.59</v>
       </c>
       <c r="H3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I3" t="n">
         <v>8.199999999999999</v>
@@ -1129,7 +1129,7 @@
         <v>4.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
@@ -1144,25 +1144,25 @@
         <v>2.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R3" t="n">
         <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="T3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U3" t="n">
         <v>1.93</v>
       </c>
       <c r="V3" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="W3" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="X3" t="n">
         <v>22</v>
@@ -1171,7 +1171,7 @@
         <v>29</v>
       </c>
       <c r="Z3" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AA3" t="n">
         <v>270</v>
@@ -1180,7 +1180,7 @@
         <v>10.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD3" t="n">
         <v>36</v>
@@ -1195,7 +1195,7 @@
         <v>12.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
         <v>120</v>
@@ -1216,61 +1216,61 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AO3" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AP3" t="n">
-        <v>13</v>
+        <v>3.75</v>
       </c>
       <c r="AQ3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>3.8</v>
       </c>
-      <c r="AR3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS3" t="n">
+      <c r="BA3" t="n">
         <v>4.2</v>
       </c>
-      <c r="AT3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BB3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="G4" t="n">
         <v>1.96</v>
@@ -1374,7 +1374,7 @@
         <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
@@ -1383,13 +1383,13 @@
         <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
         <v>1.38</v>
@@ -1404,13 +1404,13 @@
         <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T4" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U4" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="V4" t="n">
         <v>1.21</v>
@@ -1419,19 +1419,19 @@
         <v>2.04</v>
       </c>
       <c r="X4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AA4" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC4" t="n">
         <v>9.199999999999999</v>
@@ -1440,25 +1440,25 @@
         <v>24</v>
       </c>
       <c r="AE4" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AF4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG4" t="n">
         <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI4" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AK4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL4" t="n">
         <v>48</v>
@@ -1470,7 +1470,7 @@
         <v>17</v>
       </c>
       <c r="AO4" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP4" t="n">
         <v>9.800000000000001</v>
@@ -1479,10 +1479,10 @@
         <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AT4" t="n">
         <v>6.6</v>
@@ -1494,7 +1494,7 @@
         <v>16.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AX4" t="n">
         <v>9.199999999999999</v>
@@ -1506,7 +1506,7 @@
         <v>17.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BB4" t="n">
         <v>17.5</v>
@@ -1515,70 +1515,70 @@
         <v>18</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF4" t="n">
         <v>13</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH4" t="n">
         <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="BJ4" t="n">
         <v>11.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN4" t="n">
         <v>4.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BR4" t="n">
         <v>34</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
         <v>2.94</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AW5" t="n">
         <v>4</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -1873,25 +1873,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="G6" t="n">
         <v>1.8</v>
       </c>
       <c r="H6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I6" t="n">
         <v>6.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="K6" t="n">
         <v>4.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1900,10 +1900,10 @@
         <v>3.8</v>
       </c>
       <c r="O6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Q6" t="n">
         <v>1.7</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="G7" t="n">
-        <v>970</v>
+        <v>3.95</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="I7" t="n">
-        <v>970</v>
+        <v>2.92</v>
       </c>
       <c r="J7" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>6.2</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2151,22 +2151,22 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.05</v>
+        <v>2.9</v>
       </c>
       <c r="O7" t="n">
         <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.26</v>
+        <v>1.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>1.26</v>
+        <v>2.58</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -2175,10 +2175,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.52</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>1.78</v>
       </c>
       <c r="H8" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -2405,22 +2405,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P8" t="n">
         <v>1.25</v>
       </c>
-      <c r="O8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Q8" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="R8" t="n">
         <v>1.12</v>
       </c>
       <c r="S8" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2432,7 +2432,7 @@
         <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2489,52 +2489,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -2647,10 +2647,10 @@
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2743,52 +2743,52 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
         <v>1.01</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
         <v>1.01</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2928,7 +2928,7 @@
         <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2997,52 +2997,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -3185,7 +3185,7 @@
         <v>2.22</v>
       </c>
       <c r="T11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U11" t="n">
         <v>2.58</v>
@@ -3263,7 +3263,7 @@
         <v>5.1</v>
       </c>
       <c r="AT11" t="n">
-        <v>11</v>
+        <v>4.1</v>
       </c>
       <c r="AU11" t="n">
         <v>8</v>
@@ -3275,7 +3275,7 @@
         <v>4.8</v>
       </c>
       <c r="AX11" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY11" t="n">
         <v>8.199999999999999</v>
@@ -3302,7 +3302,7 @@
         <v>6</v>
       </c>
       <c r="BG11" t="n">
-        <v>17.5</v>
+        <v>4.5</v>
       </c>
       <c r="BH11" t="n">
         <v>4.8</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -3403,16 +3403,16 @@
         <v>2.96</v>
       </c>
       <c r="H12" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="I12" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="J12" t="n">
         <v>3.8</v>
       </c>
       <c r="K12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L12" t="n">
         <v>1.24</v>
@@ -3445,22 +3445,22 @@
         <v>2.58</v>
       </c>
       <c r="V12" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="W12" t="n">
         <v>1.51</v>
       </c>
       <c r="X12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y12" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z12" t="n">
         <v>25</v>
       </c>
       <c r="AA12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AB12" t="n">
         <v>21</v>
@@ -3469,13 +3469,13 @@
         <v>12</v>
       </c>
       <c r="AD12" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE12" t="n">
         <v>29</v>
       </c>
       <c r="AF12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG12" t="n">
         <v>16</v>
@@ -3496,43 +3496,43 @@
         <v>38</v>
       </c>
       <c r="AM12" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN12" t="n">
         <v>19.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AP12" t="n">
         <v>18</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AT12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW12" t="n">
         <v>17</v>
       </c>
       <c r="AX12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
         <v>10.5</v>
@@ -3541,13 +3541,13 @@
         <v>21</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BC12" t="n">
         <v>19</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BE12" t="n">
         <v>4</v>
@@ -3556,7 +3556,7 @@
         <v>11.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH12" t="n">
         <v>4.6</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="G13" t="n">
         <v>2.96</v>
@@ -3660,10 +3660,10 @@
         <v>2.32</v>
       </c>
       <c r="I13" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K13" t="n">
         <v>4.6</v>
@@ -3699,7 +3699,7 @@
         <v>3.1</v>
       </c>
       <c r="V13" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="W13" t="n">
         <v>1.51</v>
@@ -3771,13 +3771,13 @@
         <v>3.95</v>
       </c>
       <c r="AT13" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AU13" t="n">
         <v>8.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AW13" t="n">
         <v>15</v>
@@ -3789,7 +3789,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>10</v>
+        <v>3.45</v>
       </c>
       <c r="BA13" t="n">
         <v>17.5</v>
@@ -3798,7 +3798,7 @@
         <v>4</v>
       </c>
       <c r="BC13" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD13" t="n">
         <v>19</v>
@@ -3807,7 +3807,7 @@
         <v>4</v>
       </c>
       <c r="BF13" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BG13" t="n">
         <v>6.8</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -3917,10 +3917,10 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3929,16 +3929,16 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O14" t="n">
         <v>1.1</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
         <v>1.24</v>
@@ -4013,52 +4013,52 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
         <v>1.01</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -4168,10 +4168,10 @@
         <v>2.16</v>
       </c>
       <c r="I15" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="J15" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K15" t="n">
         <v>3.35</v>
@@ -4183,7 +4183,7 @@
         <v>1.11</v>
       </c>
       <c r="N15" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="O15" t="n">
         <v>1.54</v>
@@ -4192,10 +4192,10 @@
         <v>1.48</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="S15" t="n">
         <v>1.01</v>
@@ -4207,10 +4207,10 @@
         <v>1.7</v>
       </c>
       <c r="V15" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W15" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X15" t="n">
         <v>9.4</v>
@@ -4255,7 +4255,7 @@
         <v>85</v>
       </c>
       <c r="AL15" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AM15" t="n">
         <v>240</v>
@@ -4318,7 +4318,7 @@
         <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BH15" t="n">
         <v>2.76</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
         <v>970</v>
       </c>
       <c r="AG16" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AH16" t="n">
         <v>23</v>
@@ -4527,10 +4527,10 @@
         <v>9</v>
       </c>
       <c r="AR16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT16" t="n">
         <v>6.6</v>
@@ -4539,10 +4539,10 @@
         <v>6.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX16" t="n">
         <v>10.5</v>
@@ -4551,28 +4551,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BA16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD16" t="n">
         <v>7.2</v>
       </c>
-      <c r="BB16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BE16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG16" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>7</v>
       </c>
       <c r="BH16" t="n">
         <v>2.88</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -4667,31 +4667,31 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I17" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J17" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="K17" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="L17" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="M17" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="O17" t="n">
         <v>1.4</v>
@@ -4709,34 +4709,34 @@
         <v>3.45</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="V17" t="n">
         <v>1.18</v>
       </c>
       <c r="W17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X17" t="n">
         <v>13.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z17" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA17" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD17" t="n">
         <v>26</v>
@@ -4745,7 +4745,7 @@
         <v>110</v>
       </c>
       <c r="AF17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG17" t="n">
         <v>12</v>
@@ -4754,13 +4754,13 @@
         <v>27</v>
       </c>
       <c r="AI17" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL17" t="n">
         <v>55</v>
@@ -4769,104 +4769,104 @@
         <v>190</v>
       </c>
       <c r="AN17" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AO17" t="n">
         <v>160</v>
       </c>
       <c r="AP17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT17" t="n">
         <v>9</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>1000</v>
-      </c>
       <c r="BU17" t="n">
         <v>1.01</v>
       </c>
@@ -4883,14 +4883,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA17" t="n">
         <v>1.01</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4927,7 @@
         <v>2.38</v>
       </c>
       <c r="H18" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I18" t="n">
         <v>4.3</v>
@@ -4945,37 +4945,37 @@
         <v>1.12</v>
       </c>
       <c r="N18" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="O18" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P18" t="n">
         <v>1.56</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S18" t="n">
         <v>5.1</v>
       </c>
       <c r="T18" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U18" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V18" t="n">
         <v>1.3</v>
       </c>
       <c r="W18" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X18" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y18" t="n">
         <v>11.5</v>
@@ -4999,22 +4999,22 @@
         <v>65</v>
       </c>
       <c r="AF18" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG18" t="n">
         <v>12</v>
       </c>
       <c r="AH18" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI18" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AJ18" t="n">
         <v>34</v>
       </c>
       <c r="AK18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL18" t="n">
         <v>60</v>
@@ -5029,58 +5029,58 @@
         <v>110</v>
       </c>
       <c r="AP18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR18" t="n">
         <v>8</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AS18" t="n">
         <v>10</v>
       </c>
-      <c r="AR18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AT18" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV18" t="n">
         <v>15</v>
       </c>
       <c r="AW18" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX18" t="n">
         <v>11.5</v>
       </c>
       <c r="AY18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BE18" t="n">
         <v>10.5</v>
       </c>
-      <c r="AZ18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>9</v>
-      </c>
       <c r="BF18" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BH18" t="n">
         <v>2.8</v>
@@ -5104,7 +5104,7 @@
         <v>4.9</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP18" t="n">
         <v>19.5</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
         <v>10</v>
       </c>
       <c r="AC19" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD19" t="n">
         <v>18</v>
@@ -5280,7 +5280,7 @@
         <v>28</v>
       </c>
       <c r="AO19" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP19" t="n">
         <v>9</v>
@@ -5292,10 +5292,10 @@
         <v>19</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AT19" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU19" t="n">
         <v>5.9</v>
@@ -5304,7 +5304,7 @@
         <v>11.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AX19" t="n">
         <v>11</v>
@@ -5316,25 +5316,25 @@
         <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BC19" t="n">
         <v>21</v>
       </c>
       <c r="BD19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE19" t="n">
         <v>5</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>5.2</v>
       </c>
       <c r="BF19" t="n">
         <v>18.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G20" t="n">
         <v>2.38</v>
@@ -5441,10 +5441,10 @@
         <v>3.45</v>
       </c>
       <c r="J20" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="K20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L20" t="n">
         <v>1.3</v>
@@ -5471,7 +5471,7 @@
         <v>2.96</v>
       </c>
       <c r="T20" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U20" t="n">
         <v>2.24</v>
@@ -5492,7 +5492,7 @@
         <v>30</v>
       </c>
       <c r="AA20" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB20" t="n">
         <v>14</v>
@@ -5534,7 +5534,7 @@
         <v>18.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP20" t="n">
         <v>12.5</v>
@@ -5543,7 +5543,7 @@
         <v>10.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>17.5</v>
+        <v>3.8</v>
       </c>
       <c r="AS20" t="n">
         <v>4</v>
@@ -5552,19 +5552,19 @@
         <v>8.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV20" t="n">
         <v>10.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AX20" t="n">
         <v>11.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>8.199999999999999</v>
+        <v>3.25</v>
       </c>
       <c r="AZ20" t="n">
         <v>12</v>
@@ -5573,28 +5573,28 @@
         <v>4</v>
       </c>
       <c r="BB20" t="n">
-        <v>21</v>
+        <v>3.85</v>
       </c>
       <c r="BC20" t="n">
-        <v>16.5</v>
+        <v>3.75</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BE20" t="n">
         <v>4.1</v>
       </c>
       <c r="BF20" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>6.4</v>
+        <v>3.85</v>
       </c>
       <c r="BH20" t="n">
         <v>3.85</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="BJ20" t="n">
         <v>9.4</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
@@ -857,43 +857,43 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G2" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O2" t="n">
         <v>1.35</v>
       </c>
       <c r="P2" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S2" t="n">
         <v>3.7</v>
@@ -908,7 +908,7 @@
         <v>1.25</v>
       </c>
       <c r="W2" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
         <v>15</v>
@@ -923,13 +923,13 @@
         <v>130</v>
       </c>
       <c r="AB2" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC2" t="n">
         <v>8.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE2" t="n">
         <v>70</v>
@@ -956,10 +956,10 @@
         <v>44</v>
       </c>
       <c r="AM2" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AO2" t="n">
         <v>80</v>
@@ -968,13 +968,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR2" t="n">
         <v>24</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AT2" t="n">
         <v>7</v>
@@ -986,7 +986,7 @@
         <v>15.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AX2" t="n">
         <v>10</v>
@@ -998,7 +998,7 @@
         <v>16.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BB2" t="n">
         <v>19.5</v>
@@ -1007,25 +1007,25 @@
         <v>19</v>
       </c>
       <c r="BD2" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BF2" t="n">
         <v>13.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK2" t="n">
         <v>5.2</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN2" t="n">
         <v>4.8</v>
@@ -1043,7 +1043,7 @@
         <v>3.55</v>
       </c>
       <c r="BP2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ2" t="n">
         <v>6</v>
@@ -1064,13 +1064,13 @@
         <v>42</v>
       </c>
       <c r="BW2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX2" t="n">
         <v>55</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="G3" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="H3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I3" t="n">
         <v>8.199999999999999</v>
@@ -1126,7 +1126,7 @@
         <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
         <v>1.27</v>
@@ -1135,19 +1135,19 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O3" t="n">
         <v>1.26</v>
       </c>
       <c r="P3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S3" t="n">
         <v>2.96</v>
@@ -1162,7 +1162,7 @@
         <v>1.16</v>
       </c>
       <c r="W3" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="X3" t="n">
         <v>22</v>
@@ -1201,7 +1201,7 @@
         <v>120</v>
       </c>
       <c r="AJ3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK3" t="n">
         <v>19.5</v>
@@ -1213,7 +1213,7 @@
         <v>160</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO3" t="n">
         <v>160</v>
@@ -1222,13 +1222,13 @@
         <v>3.75</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AR3" t="n">
         <v>4.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT3" t="n">
         <v>7.6</v>
@@ -1237,22 +1237,22 @@
         <v>9</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AW3" t="n">
         <v>4.3</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.45</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB3" t="n">
         <v>3.55</v>
@@ -1264,13 +1264,13 @@
         <v>4.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G4" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="I4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
@@ -1395,7 +1395,7 @@
         <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Q4" t="n">
         <v>2.12</v>
@@ -1404,7 +1404,7 @@
         <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
         <v>1.96</v>
@@ -1413,7 +1413,7 @@
         <v>1.89</v>
       </c>
       <c r="V4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W4" t="n">
         <v>2.04</v>
@@ -1425,10 +1425,10 @@
         <v>17.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AA4" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB4" t="n">
         <v>8</v>
@@ -1437,10 +1437,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE4" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AF4" t="n">
         <v>13</v>
@@ -1449,10 +1449,10 @@
         <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AJ4" t="n">
         <v>22</v>
@@ -1476,13 +1476,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT4" t="n">
         <v>6.6</v>
@@ -1494,7 +1494,7 @@
         <v>16.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX4" t="n">
         <v>9.199999999999999</v>
@@ -1506,46 +1506,46 @@
         <v>17.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB4" t="n">
         <v>17.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF4" t="n">
         <v>13</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH4" t="n">
         <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ4" t="n">
         <v>11.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO4" t="n">
         <v>3.4</v>
@@ -1554,31 +1554,31 @@
         <v>14.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR4" t="n">
         <v>34</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BT4" t="n">
         <v>8.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="G5" t="n">
         <v>3.7</v>
       </c>
       <c r="H5" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I5" t="n">
         <v>2.82</v>
@@ -1673,7 +1673,7 @@
         <v>1.37</v>
       </c>
       <c r="X5" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="Y5" t="n">
         <v>9.4</v>
@@ -1688,7 +1688,7 @@
         <v>11.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD5" t="n">
         <v>16</v>
@@ -1727,58 +1727,58 @@
         <v>48</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AS5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY5" t="n">
         <v>4.1</v>
       </c>
-      <c r="AT5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BH5" t="n">
         <v>2.74</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="G6" t="n">
         <v>1.8</v>
@@ -1885,7 +1885,7 @@
         <v>6.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
         <v>4.8</v>
@@ -1930,49 +1930,49 @@
         <v>22</v>
       </c>
       <c r="Y6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Z6" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AA6" t="n">
         <v>150</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
-        <v>80</v>
+        <v>470</v>
       </c>
       <c r="AF6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>80</v>
+        <v>450</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL6" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM6" t="n">
-        <v>110</v>
+        <v>450</v>
       </c>
       <c r="AN6" t="n">
         <v>9.4</v>
@@ -1981,122 +1981,122 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF6" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>3.35</v>
-      </c>
       <c r="BG6" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BH6" t="n">
         <v>4.1</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BJ6" t="n">
         <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BN6" t="n">
         <v>4.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BP6" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BR6" t="n">
         <v>25</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BT6" t="n">
         <v>9.4</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV6" t="n">
         <v>46</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BX6" t="n">
         <v>50</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BZ6" t="n">
         <v>18.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -2130,31 +2130,31 @@
         <v>2.72</v>
       </c>
       <c r="G7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
         <v>2.12</v>
       </c>
       <c r="I7" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="J7" t="n">
         <v>3.05</v>
       </c>
       <c r="K7" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M7" t="n">
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="P7" t="n">
         <v>1.86</v>
@@ -2163,25 +2163,25 @@
         <v>1.8</v>
       </c>
       <c r="R7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.33</v>
       </c>
-      <c r="S7" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.34</v>
-      </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y7" t="n">
         <v>1000</v>
@@ -2283,10 +2283,10 @@
         <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="G8" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="H8" t="n">
-        <v>2.28</v>
+        <v>3.55</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J8" t="n">
-        <v>2.32</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -2405,10 +2405,10 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="P8" t="n">
         <v>1.25</v>
@@ -2420,7 +2420,7 @@
         <v>1.12</v>
       </c>
       <c r="S8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2429,118 +2429,118 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W8" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.91</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.93</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.93</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.93</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.93</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="H9" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="J9" t="n">
-        <v>1.02</v>
+        <v>2.66</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>9.4</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2659,22 +2659,22 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="O9" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25</v>
+        <v>2.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.86</v>
       </c>
       <c r="S9" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2683,10 +2683,10 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2788,13 +2788,13 @@
         <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
         <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>2.1</v>
       </c>
       <c r="H10" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>44</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2913,22 +2913,22 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O10" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="S10" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2958,7 +2958,7 @@
         <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD10" t="n">
         <v>1000</v>
@@ -3042,7 +3042,7 @@
         <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G11" t="n">
         <v>2.06</v>
@@ -3155,7 +3155,7 @@
         <v>4.2</v>
       </c>
       <c r="J11" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
         <v>4.7</v>
@@ -3218,7 +3218,7 @@
         <v>20</v>
       </c>
       <c r="AE11" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AF11" t="n">
         <v>19.5</v>
@@ -3257,13 +3257,13 @@
         <v>16</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AU11" t="n">
         <v>8</v>
@@ -3296,13 +3296,13 @@
         <v>18</v>
       </c>
       <c r="BE11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH11" t="n">
         <v>4.8</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="G12" t="n">
         <v>2.96</v>
@@ -3406,13 +3406,13 @@
         <v>2.4</v>
       </c>
       <c r="I12" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="J12" t="n">
         <v>3.8</v>
       </c>
       <c r="K12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L12" t="n">
         <v>1.24</v>
@@ -3454,19 +3454,19 @@
         <v>30</v>
       </c>
       <c r="Y12" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z12" t="n">
         <v>25</v>
       </c>
       <c r="AA12" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB12" t="n">
         <v>21</v>
       </c>
       <c r="AC12" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD12" t="n">
         <v>15.5</v>
@@ -3481,7 +3481,7 @@
         <v>16</v>
       </c>
       <c r="AH12" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AI12" t="n">
         <v>36</v>
@@ -3496,7 +3496,7 @@
         <v>38</v>
       </c>
       <c r="AM12" t="n">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="AN12" t="n">
         <v>19.5</v>
@@ -3514,7 +3514,7 @@
         <v>15</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AT12" t="n">
         <v>12</v>
@@ -3541,16 +3541,16 @@
         <v>21</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BC12" t="n">
         <v>19</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BF12" t="n">
         <v>11.5</v>
@@ -3574,7 +3574,7 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN12" t="n">
         <v>6.6</v>
@@ -3586,7 +3586,7 @@
         <v>20</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR12" t="n">
         <v>27</v>
@@ -3601,7 +3601,7 @@
         <v>4.5</v>
       </c>
       <c r="BV12" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BW12" t="n">
         <v>6.4</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -3651,58 +3651,58 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="G13" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="H13" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="I13" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="J13" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
         <v>4.6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="M13" t="n">
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O13" t="n">
         <v>1.12</v>
       </c>
       <c r="P13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="R13" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="S13" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="T13" t="n">
         <v>1.4</v>
       </c>
       <c r="U13" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V13" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="W13" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="X13" t="n">
         <v>46</v>
@@ -3711,10 +3711,10 @@
         <v>27</v>
       </c>
       <c r="Z13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA13" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AB13" t="n">
         <v>29</v>
@@ -3726,7 +3726,7 @@
         <v>16</v>
       </c>
       <c r="AE13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF13" t="n">
         <v>34</v>
@@ -3735,16 +3735,16 @@
         <v>17.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ13" t="n">
         <v>55</v>
       </c>
       <c r="AK13" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AL13" t="n">
         <v>32</v>
@@ -3753,22 +3753,22 @@
         <v>46</v>
       </c>
       <c r="AN13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP13" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AQ13" t="n">
         <v>15.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.95</v>
+        <v>18</v>
       </c>
       <c r="AT13" t="n">
         <v>17</v>
@@ -3777,7 +3777,7 @@
         <v>8.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>10</v>
+        <v>3.75</v>
       </c>
       <c r="AW13" t="n">
         <v>15</v>
@@ -3786,16 +3786,16 @@
         <v>20</v>
       </c>
       <c r="AY13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ13" t="n">
-        <v>3.45</v>
+        <v>10</v>
       </c>
       <c r="BA13" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="BC13" t="n">
         <v>18</v>
@@ -3804,16 +3804,16 @@
         <v>19</v>
       </c>
       <c r="BE13" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="BF13" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.8</v>
+        <v>3.35</v>
       </c>
       <c r="BH13" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BI13" t="n">
         <v>4.2</v>
@@ -3831,10 +3831,10 @@
         <v>10.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BP13" t="n">
         <v>18.5</v>
@@ -3852,29 +3852,29 @@
         <v>6.4</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV13" t="n">
         <v>15</v>
       </c>
       <c r="BW13" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BX13" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BY13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>11</v>
+      </c>
+      <c r="CA13" t="n">
         <v>7.8</v>
       </c>
-      <c r="BZ13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>6</v>
-      </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -3905,19 +3905,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="H14" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>1.81</v>
       </c>
       <c r="J14" t="n">
-        <v>1.02</v>
+        <v>2.82</v>
       </c>
       <c r="K14" t="n">
         <v>950</v>
@@ -3929,58 +3929,58 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.24</v>
+        <v>6.2</v>
       </c>
       <c r="O14" t="n">
         <v>1.1</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>2.86</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.24</v>
+        <v>1.86</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1</v>
+        <v>1.74</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB14" t="n">
         <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF14" t="n">
         <v>1000</v>
@@ -3992,7 +3992,7 @@
         <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ14" t="n">
         <v>1000</v>
@@ -4010,7 +4010,7 @@
         <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP14" t="n">
         <v>1.03</v>
@@ -4058,7 +4058,7 @@
         <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
         <v>1.01</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -4159,175 +4159,175 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="G15" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="J15" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="K15" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="M15" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="P15" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.5</v>
+        <v>1.02</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="S15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="W15" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="X15" t="n">
         <v>9.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="AA15" t="n">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="AB15" t="n">
         <v>12.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="AD15" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AE15" t="n">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="AF15" t="n">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="AG15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>540</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BG15" t="n">
         <v>21</v>
       </c>
-      <c r="AH15" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>240</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>130</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>26</v>
-      </c>
       <c r="BH15" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="BJ15" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK15" t="n">
         <v>8.800000000000001</v>
@@ -4339,50 +4339,50 @@
         <v>1.01</v>
       </c>
       <c r="BN15" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BO15" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BT15" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BU15" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="BV15" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
         <v>3.35</v>
       </c>
       <c r="L16" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M16" t="n">
         <v>1.11</v>
@@ -4443,13 +4443,13 @@
         <v>1.48</v>
       </c>
       <c r="P16" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q16" t="n">
         <v>2.44</v>
       </c>
       <c r="R16" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S16" t="n">
         <v>4.8</v>
@@ -4458,7 +4458,7 @@
         <v>2.02</v>
       </c>
       <c r="U16" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V16" t="n">
         <v>1.33</v>
@@ -4467,16 +4467,16 @@
         <v>1.64</v>
       </c>
       <c r="X16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y16" t="n">
         <v>12</v>
       </c>
       <c r="Z16" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AA16" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AB16" t="n">
         <v>8.199999999999999</v>
@@ -4485,52 +4485,52 @@
         <v>7.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AE16" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AF16" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="AG16" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AH16" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="AI16" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AJ16" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AK16" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AL16" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AM16" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AN16" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AO16" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AP16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ16" t="n">
         <v>9</v>
       </c>
       <c r="AR16" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT16" t="n">
         <v>6.6</v>
@@ -4539,10 +4539,10 @@
         <v>6.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX16" t="n">
         <v>10.5</v>
@@ -4551,49 +4551,49 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ16" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.4</v>
+        <v>28</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BJ16" t="n">
         <v>11.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN16" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO16" t="n">
         <v>4</v>
@@ -4602,13 +4602,13 @@
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BT16" t="n">
         <v>7</v>
@@ -4620,23 +4620,23 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA16" t="n">
         <v>8.4</v>
       </c>
-      <c r="BX16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>9</v>
-      </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -4670,16 +4670,16 @@
         <v>1.76</v>
       </c>
       <c r="G17" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="H17" t="n">
         <v>4.5</v>
       </c>
       <c r="I17" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J17" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K17" t="n">
         <v>3.9</v>
@@ -4691,7 +4691,7 @@
         <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O17" t="n">
         <v>1.4</v>
@@ -4700,13 +4700,13 @@
         <v>1.69</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R17" t="n">
         <v>1.26</v>
       </c>
       <c r="S17" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
         <v>2</v>
@@ -4715,10 +4715,10 @@
         <v>1.82</v>
       </c>
       <c r="V17" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X17" t="n">
         <v>13.5</v>
@@ -4730,19 +4730,19 @@
         <v>50</v>
       </c>
       <c r="AA17" t="n">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AB17" t="n">
         <v>8.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD17" t="n">
         <v>26</v>
       </c>
       <c r="AE17" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AF17" t="n">
         <v>12</v>
@@ -4751,10 +4751,10 @@
         <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI17" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AJ17" t="n">
         <v>24</v>
@@ -4766,67 +4766,67 @@
         <v>55</v>
       </c>
       <c r="AM17" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AN17" t="n">
         <v>18.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH17" t="n">
         <v>3.2</v>
@@ -4838,59 +4838,59 @@
         <v>11.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BN17" t="n">
         <v>4.4</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BP17" t="n">
         <v>14</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BT17" t="n">
         <v>9</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BZ17" t="n">
         <v>32</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -4924,10 +4924,10 @@
         <v>2.26</v>
       </c>
       <c r="G18" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I18" t="n">
         <v>4.3</v>
@@ -4942,19 +4942,19 @@
         <v>1.48</v>
       </c>
       <c r="M18" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N18" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
         <v>1.5</v>
       </c>
       <c r="P18" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R18" t="n">
         <v>1.21</v>
@@ -4963,19 +4963,19 @@
         <v>5.1</v>
       </c>
       <c r="T18" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U18" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V18" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W18" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X18" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y18" t="n">
         <v>11.5</v>
@@ -4984,10 +4984,10 @@
         <v>27</v>
       </c>
       <c r="AA18" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC18" t="n">
         <v>7.8</v>
@@ -4999,7 +4999,7 @@
         <v>65</v>
       </c>
       <c r="AF18" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG18" t="n">
         <v>12</v>
@@ -5008,7 +5008,7 @@
         <v>22</v>
       </c>
       <c r="AI18" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ18" t="n">
         <v>34</v>
@@ -5017,7 +5017,7 @@
         <v>32</v>
       </c>
       <c r="AL18" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM18" t="n">
         <v>190</v>
@@ -5026,22 +5026,22 @@
         <v>32</v>
       </c>
       <c r="AO18" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP18" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR18" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="AS18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT18" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU18" t="n">
         <v>6.6</v>
@@ -5050,37 +5050,37 @@
         <v>15</v>
       </c>
       <c r="AW18" t="n">
-        <v>9.800000000000001</v>
+        <v>50</v>
       </c>
       <c r="AX18" t="n">
         <v>11.5</v>
       </c>
       <c r="AY18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BB18" t="n">
         <v>10</v>
       </c>
-      <c r="AZ18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BC18" t="n">
-        <v>8.4</v>
+        <v>27</v>
       </c>
       <c r="BD18" t="n">
-        <v>9.6</v>
+        <v>50</v>
       </c>
       <c r="BE18" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BG18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH18" t="n">
         <v>2.8</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>2.18</v>
       </c>
       <c r="G20" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="H20" t="n">
         <v>3.1</v>
@@ -5441,10 +5441,10 @@
         <v>3.45</v>
       </c>
       <c r="J20" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L20" t="n">
         <v>1.3</v>
@@ -5543,7 +5543,7 @@
         <v>10.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>3.8</v>
+        <v>17.5</v>
       </c>
       <c r="AS20" t="n">
         <v>4</v>
@@ -5564,7 +5564,7 @@
         <v>11.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>3.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ20" t="n">
         <v>12</v>
@@ -5576,7 +5576,7 @@
         <v>3.85</v>
       </c>
       <c r="BC20" t="n">
-        <v>3.75</v>
+        <v>16.5</v>
       </c>
       <c r="BD20" t="n">
         <v>3.95</v>
@@ -5585,7 +5585,7 @@
         <v>4.1</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="BG20" t="n">
         <v>3.85</v>
@@ -5594,7 +5594,7 @@
         <v>3.85</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BJ20" t="n">
         <v>9.4</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB20"/>
+  <dimension ref="A1:CB21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="H2" t="n">
         <v>4.6</v>
       </c>
       <c r="I2" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="J2" t="n">
         <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
         <v>1.42</v>
@@ -887,34 +887,34 @@
         <v>1.35</v>
       </c>
       <c r="P2" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R2" t="n">
         <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="U2" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z2" t="n">
         <v>36</v>
@@ -929,16 +929,16 @@
         <v>8.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF2" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
         <v>21</v>
@@ -947,25 +947,25 @@
         <v>75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK2" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AL2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
         <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO2" t="n">
         <v>80</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>13</v>
@@ -974,10 +974,10 @@
         <v>24</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="AT2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU2" t="n">
         <v>7</v>
@@ -986,19 +986,19 @@
         <v>15.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.7</v>
+        <v>22</v>
       </c>
       <c r="AX2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
         <v>16.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="BB2" t="n">
         <v>19.5</v>
@@ -1007,37 +1007,37 @@
         <v>19</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.5</v>
+        <v>14</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="BF2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="BH2" t="n">
         <v>3.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ2" t="n">
         <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO2" t="n">
         <v>3.55</v>
@@ -1046,31 +1046,31 @@
         <v>14.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR2" t="n">
         <v>32</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="BV2" t="n">
         <v>42</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX2" t="n">
         <v>55</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="G3" t="n">
         <v>1.57</v>
@@ -1123,13 +1123,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K3" t="n">
         <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
@@ -1141,13 +1141,13 @@
         <v>1.26</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q3" t="n">
         <v>1.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
         <v>2.96</v>
@@ -1156,16 +1156,16 @@
         <v>1.92</v>
       </c>
       <c r="U3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V3" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="W3" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="X3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y3" t="n">
         <v>29</v>
@@ -1177,7 +1177,7 @@
         <v>270</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC3" t="n">
         <v>12.5</v>
@@ -1213,118 +1213,118 @@
         <v>160</v>
       </c>
       <c r="AN3" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AO3" t="n">
         <v>160</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.75</v>
+        <v>15.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.2</v>
+        <v>42</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BA3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB3" t="n">
         <v>4.3</v>
       </c>
-      <c r="BB3" t="n">
-        <v>3.55</v>
-      </c>
       <c r="BC3" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BF3" t="n">
         <v>6.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.91</v>
+        <v>3.4</v>
       </c>
       <c r="BJ3" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.7</v>
+        <v>6.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.91</v>
+        <v>2.98</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="BP3" t="n">
-        <v>13.5</v>
+        <v>9.4</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.68</v>
+        <v>5.7</v>
       </c>
       <c r="BR3" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.82</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.7</v>
+        <v>6.2</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.88</v>
+        <v>12</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.88</v>
+        <v>12</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="G4" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L4" t="n">
         <v>1.46</v>
@@ -1392,13 +1392,13 @@
         <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P4" t="n">
         <v>1.74</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R4" t="n">
         <v>1.27</v>
@@ -1407,22 +1407,22 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W4" t="n">
         <v>2.04</v>
       </c>
       <c r="X4" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y4" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z4" t="n">
         <v>48</v>
@@ -1440,7 +1440,7 @@
         <v>23</v>
       </c>
       <c r="AE4" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AF4" t="n">
         <v>13</v>
@@ -1479,10 +1479,10 @@
         <v>13.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT4" t="n">
         <v>6.6</v>
@@ -1494,7 +1494,7 @@
         <v>16.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AX4" t="n">
         <v>9.199999999999999</v>
@@ -1506,7 +1506,7 @@
         <v>17.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BB4" t="n">
         <v>17.5</v>
@@ -1515,16 +1515,16 @@
         <v>16.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF4" t="n">
         <v>13</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH4" t="n">
         <v>3.2</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
         <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O5" t="n">
         <v>1.55</v>
@@ -1679,13 +1679,13 @@
         <v>9.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC5" t="n">
         <v>7.4</v>
@@ -1694,31 +1694,31 @@
         <v>16</v>
       </c>
       <c r="AE5" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AF5" t="n">
         <v>27</v>
       </c>
       <c r="AG5" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AH5" t="n">
         <v>28</v>
       </c>
       <c r="AI5" t="n">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AJ5" t="n">
         <v>90</v>
       </c>
       <c r="AK5" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AL5" t="n">
         <v>100</v>
       </c>
       <c r="AM5" t="n">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AN5" t="n">
         <v>1000</v>
@@ -1727,64 +1727,64 @@
         <v>48</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AS5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV5" t="n">
         <v>4.7</v>
       </c>
-      <c r="AT5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AW5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY5" t="n">
         <v>4.7</v>
       </c>
-      <c r="AX5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BH5" t="n">
         <v>2.74</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="BJ5" t="n">
         <v>12</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
         <v>4.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1900,7 +1900,7 @@
         <v>3.8</v>
       </c>
       <c r="O6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P6" t="n">
         <v>2.08</v>
@@ -1936,7 +1936,7 @@
         <v>48</v>
       </c>
       <c r="AA6" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AB6" t="n">
         <v>10.5</v>
@@ -1948,7 +1948,7 @@
         <v>23</v>
       </c>
       <c r="AE6" t="n">
-        <v>470</v>
+        <v>160</v>
       </c>
       <c r="AF6" t="n">
         <v>12</v>
@@ -1960,7 +1960,7 @@
         <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>450</v>
+        <v>160</v>
       </c>
       <c r="AJ6" t="n">
         <v>18.5</v>
@@ -1972,7 +1972,7 @@
         <v>34</v>
       </c>
       <c r="AM6" t="n">
-        <v>450</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
         <v>9.4</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.72</v>
+        <v>2.36</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H7" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="L7" t="n">
         <v>1.27</v>
@@ -2151,16 +2151,16 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1</v>
+        <v>3.25</v>
       </c>
       <c r="O7" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="P7" t="n">
         <v>1.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R7" t="n">
         <v>1.29</v>
@@ -2175,64 +2175,64 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="X7" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP7" t="n">
         <v>1.03</v>
@@ -2280,77 +2280,77 @@
         <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="G8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="H8" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="I8" t="n">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -2423,28 +2423,28 @@
         <v>1.56</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="W8" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="X8" t="n">
         <v>29</v>
       </c>
       <c r="Y8" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Z8" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB8" t="n">
         <v>15</v>
@@ -2453,22 +2453,22 @@
         <v>13</v>
       </c>
       <c r="AD8" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AF8" t="n">
         <v>14</v>
       </c>
       <c r="AG8" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="AH8" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ8" t="n">
         <v>23</v>
@@ -2477,31 +2477,31 @@
         <v>55</v>
       </c>
       <c r="AL8" t="n">
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AN8" t="n">
         <v>48</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AQ8" t="n">
         <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -2510,7 +2510,7 @@
         <v>17.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AX8" t="n">
         <v>5.9</v>
@@ -2522,10 +2522,10 @@
         <v>14</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="BB8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BC8" t="n">
         <v>11.5</v>
@@ -2534,10 +2534,10 @@
         <v>19.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BG8" t="n">
         <v>32</v>
@@ -2546,65 +2546,65 @@
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.16</v>
+        <v>1.48</v>
       </c>
       <c r="G9" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="H9" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I9" t="n">
-        <v>3.75</v>
+        <v>44</v>
       </c>
       <c r="J9" t="n">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="K9" t="n">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2671,76 +2671,76 @@
         <v>1.09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="S9" t="n">
         <v>1.8</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP9" t="n">
         <v>1.03</v>
@@ -2791,10 +2791,10 @@
         <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2913,7 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O10" t="n">
         <v>1.12</v>
@@ -2931,10 +2931,10 @@
         <v>1.8</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
         <v>1.01</v>
@@ -2943,58 +2943,58 @@
         <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC10" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP10" t="n">
         <v>1.03</v>
@@ -3048,7 +3048,7 @@
         <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G11" t="n">
         <v>2.06</v>
@@ -3200,7 +3200,7 @@
         <v>34</v>
       </c>
       <c r="Y11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Z11" t="n">
         <v>40</v>
@@ -3212,13 +3212,13 @@
         <v>18</v>
       </c>
       <c r="AC11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD11" t="n">
         <v>20</v>
       </c>
       <c r="AE11" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AF11" t="n">
         <v>19.5</v>
@@ -3257,13 +3257,13 @@
         <v>16</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="AU11" t="n">
         <v>8</v>
@@ -3272,7 +3272,7 @@
         <v>12</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX11" t="n">
         <v>13.5</v>
@@ -3284,7 +3284,7 @@
         <v>11</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB11" t="n">
         <v>16.5</v>
@@ -3296,13 +3296,13 @@
         <v>18</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF11" t="n">
         <v>7</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH11" t="n">
         <v>4.8</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="G12" t="n">
         <v>2.96</v>
       </c>
       <c r="H12" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="I12" t="n">
         <v>2.68</v>
@@ -3451,16 +3451,16 @@
         <v>1.51</v>
       </c>
       <c r="X12" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="Y12" t="n">
         <v>19.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA12" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AB12" t="n">
         <v>21</v>
@@ -3469,37 +3469,37 @@
         <v>10.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE12" t="n">
         <v>29</v>
       </c>
       <c r="AF12" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AG12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH12" t="n">
         <v>15.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ12" t="n">
-        <v>50</v>
+        <v>900</v>
       </c>
       <c r="AK12" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AL12" t="n">
         <v>38</v>
       </c>
       <c r="AM12" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="AN12" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AO12" t="n">
         <v>16.5</v>
@@ -3514,7 +3514,7 @@
         <v>15</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.2</v>
+        <v>16</v>
       </c>
       <c r="AT12" t="n">
         <v>12</v>
@@ -3541,16 +3541,16 @@
         <v>21</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BC12" t="n">
         <v>19</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.2</v>
+        <v>16</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="BF12" t="n">
         <v>11.5</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -3657,13 +3657,13 @@
         <v>3.2</v>
       </c>
       <c r="H13" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="I13" t="n">
         <v>2.34</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K13" t="n">
         <v>4.6</v>
@@ -3693,7 +3693,7 @@
         <v>1.92</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="U13" t="n">
         <v>3.15</v>
@@ -3834,7 +3834,7 @@
         <v>7.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="BP13" t="n">
         <v>18.5</v>
@@ -3870,11 +3870,11 @@
         <v>11</v>
       </c>
       <c r="CA13" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -3905,37 +3905,37 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="G14" t="n">
-        <v>44</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="I14" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>12</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N14" t="n">
         <v>2.82</v>
       </c>
-      <c r="K14" t="n">
-        <v>950</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N14" t="n">
-        <v>6.2</v>
-      </c>
       <c r="O14" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P14" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="Q14" t="n">
         <v>1.1</v>
@@ -3944,7 +3944,7 @@
         <v>1.86</v>
       </c>
       <c r="S14" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="T14" t="n">
         <v>1.11</v>
@@ -3953,10 +3953,10 @@
         <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="W14" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3968,13 +3968,13 @@
         <v>500</v>
       </c>
       <c r="AA14" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AC14" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AD14" t="n">
         <v>500</v>
@@ -3983,13 +3983,13 @@
         <v>500</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AI14" t="n">
         <v>500</v>
@@ -4025,7 +4025,7 @@
         <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
         <v>1.03</v>
@@ -4037,10 +4037,10 @@
         <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
         <v>1.03</v>
@@ -4049,19 +4049,19 @@
         <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
         <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG14" t="n">
         <v>1.01</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -4159,97 +4159,97 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H15" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="I15" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="J15" t="n">
         <v>2.96</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="L15" t="n">
         <v>1.49</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N15" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O15" t="n">
         <v>1.51</v>
       </c>
       <c r="P15" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.02</v>
+        <v>2.52</v>
       </c>
       <c r="R15" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="S15" t="n">
-        <v>1.02</v>
+        <v>4.7</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V15" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="W15" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="X15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y15" t="n">
-        <v>13.5</v>
+        <v>7.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>30</v>
+        <v>12.5</v>
       </c>
       <c r="AA15" t="n">
         <v>130</v>
       </c>
       <c r="AB15" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC15" t="n">
-        <v>42</v>
+        <v>7.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="AE15" t="n">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="AF15" t="n">
         <v>120</v>
       </c>
       <c r="AG15" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AI15" t="n">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AJ15" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK15" t="n">
         <v>500</v>
@@ -4270,10 +4270,10 @@
         <v>7.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AS15" t="n">
         <v>11.5</v>
@@ -4282,49 +4282,49 @@
         <v>10</v>
       </c>
       <c r="AU15" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AY15" t="n">
         <v>16</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.36</v>
+        <v>8.6</v>
       </c>
       <c r="BG15" t="n">
         <v>21</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="BJ15" t="n">
         <v>12</v>
@@ -4357,13 +4357,13 @@
         <v>48</v>
       </c>
       <c r="BT15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BU15" t="n">
         <v>3.75</v>
       </c>
       <c r="BV15" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BW15" t="n">
         <v>13.5</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         <v>2.3</v>
       </c>
       <c r="G16" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H16" t="n">
         <v>3.45</v>
@@ -4425,10 +4425,10 @@
         <v>3.95</v>
       </c>
       <c r="J16" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K16" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.52</v>
@@ -4461,13 +4461,13 @@
         <v>1.81</v>
       </c>
       <c r="V16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W16" t="n">
         <v>1.64</v>
       </c>
       <c r="X16" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y16" t="n">
         <v>12</v>
@@ -4476,7 +4476,7 @@
         <v>500</v>
       </c>
       <c r="AA16" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB16" t="n">
         <v>8.199999999999999</v>
@@ -4491,28 +4491,28 @@
         <v>500</v>
       </c>
       <c r="AF16" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AG16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH16" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AI16" t="n">
         <v>500</v>
       </c>
       <c r="AJ16" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AK16" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AL16" t="n">
         <v>500</v>
       </c>
       <c r="AM16" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN16" t="n">
         <v>500</v>
@@ -4530,7 +4530,7 @@
         <v>10.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT16" t="n">
         <v>6.6</v>
@@ -4542,7 +4542,7 @@
         <v>8.4</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX16" t="n">
         <v>10.5</v>
@@ -4560,19 +4560,19 @@
         <v>14.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH16" t="n">
         <v>2.92</v>
@@ -4584,7 +4584,7 @@
         <v>11.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
@@ -4593,7 +4593,7 @@
         <v>10</v>
       </c>
       <c r="BN16" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO16" t="n">
         <v>4</v>
@@ -4602,13 +4602,13 @@
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT16" t="n">
         <v>7</v>
@@ -4620,23 +4620,23 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA16" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BZ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>8.4</v>
-      </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
         <v>1.91</v>
       </c>
       <c r="H17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I17" t="n">
         <v>6.2</v>
@@ -4691,7 +4691,7 @@
         <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O17" t="n">
         <v>1.4</v>
@@ -4700,13 +4700,13 @@
         <v>1.69</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="R17" t="n">
         <v>1.26</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T17" t="n">
         <v>2</v>
@@ -4724,16 +4724,16 @@
         <v>13.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Z17" t="n">
         <v>50</v>
       </c>
       <c r="AA17" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC17" t="n">
         <v>8.6</v>
@@ -4745,10 +4745,10 @@
         <v>700</v>
       </c>
       <c r="AF17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH17" t="n">
         <v>24</v>
@@ -4757,76 +4757,76 @@
         <v>700</v>
       </c>
       <c r="AJ17" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AK17" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL17" t="n">
         <v>55</v>
       </c>
       <c r="AM17" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO17" t="n">
         <v>700</v>
       </c>
       <c r="AP17" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AS17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF17" t="n">
         <v>5.3</v>
       </c>
-      <c r="AT17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BG17" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BH17" t="n">
         <v>3.2</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,246 +4912,246 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>Talleres (RE)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Deportivo Merlo</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.26</v>
+        <v>1.96</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="H18" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="I18" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>2.42</v>
       </c>
       <c r="K18" t="n">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>1.27</v>
       </c>
       <c r="O18" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="P18" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="R18" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="S18" t="n">
-        <v>5.1</v>
+        <v>2.66</v>
       </c>
       <c r="T18" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="W18" t="n">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="X18" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AR18" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AS18" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV18" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY18" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA18" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BC18" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="BD18" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BE18" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF18" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="n">
-        <v>2.8</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN18" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BP18" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BT18" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,498 +5161,752 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Operario PR</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="H19" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="J19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" t="n">
         <v>3.1</v>
       </c>
-      <c r="K19" t="n">
-        <v>3.55</v>
-      </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M19" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="N19" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="O19" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="P19" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.12</v>
+        <v>2.58</v>
       </c>
       <c r="R19" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="S19" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="U19" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="V19" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W19" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="X19" t="n">
-        <v>13.5</v>
+        <v>8.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA19" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AB19" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AF19" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="AG19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH19" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI19" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="AJ19" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AK19" t="n">
         <v>32</v>
       </c>
       <c r="AL19" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM19" t="n">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="AN19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BB19" t="n">
         <v>28</v>
       </c>
-      <c r="AO19" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS19" t="n">
+      <c r="BC19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>70</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>17</v>
+      </c>
+      <c r="BN19" t="n">
         <v>4.9</v>
       </c>
-      <c r="AT19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ19" t="n">
+      <c r="BO19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>13</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY19" t="n">
         <v>14.5</v>
       </c>
-      <c r="BA19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BZ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-04 18:19:43</t>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>San Marcos</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-06-04 20:34:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Canadian Premier League</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>23:00:00</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Vancouver FC</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Atletico Ottawa</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="G20" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="H20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="F21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K21" t="n">
         <v>4.1</v>
       </c>
-      <c r="L20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="L21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M21" t="n">
         <v>1.05</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X21" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP21" t="n">
         <v>4.1</v>
       </c>
-      <c r="O20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X20" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y20" t="n">
+      <c r="AQ21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC21" t="n">
         <v>18</v>
       </c>
-      <c r="Z20" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN20" t="n">
+      <c r="BD21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG21" t="n">
         <v>18.5</v>
       </c>
-      <c r="AO20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU20" t="n">
+      <c r="BH21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT21" t="n">
         <v>6.6</v>
       </c>
-      <c r="AV20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT20" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU20" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV20" t="n">
-        <v>26</v>
-      </c>
-      <c r="BW20" t="n">
+      <c r="BU21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>23</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>32</v>
+      </c>
+      <c r="BY21" t="n">
         <v>7.4</v>
       </c>
-      <c r="BX20" t="n">
-        <v>36</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BZ20" t="n">
+      <c r="BZ21" t="n">
         <v>23</v>
       </c>
-      <c r="CA20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="CB20" t="inlineStr">
-        <is>
-          <t>2026-06-04 18:19:43</t>
+      <c r="CA21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-06-04 20:34:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
@@ -866,7 +866,7 @@
         <v>4.6</v>
       </c>
       <c r="I2" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J2" t="n">
         <v>3.5</v>
@@ -881,7 +881,7 @@
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O2" t="n">
         <v>1.35</v>
@@ -896,16 +896,16 @@
         <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T2" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U2" t="n">
         <v>1.98</v>
       </c>
       <c r="V2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W2" t="n">
         <v>2.02</v>
@@ -935,10 +935,10 @@
         <v>65</v>
       </c>
       <c r="AF2" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH2" t="n">
         <v>21</v>
@@ -971,7 +971,7 @@
         <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="AS2" t="n">
         <v>9</v>
@@ -992,19 +992,19 @@
         <v>10.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
         <v>16.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB2" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BC2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD2" t="n">
         <v>14</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="G3" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="H3" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="I3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J3" t="n">
         <v>4.6</v>
@@ -1135,46 +1135,46 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q3" t="n">
         <v>1.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S3" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="T3" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="U3" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="X3" t="n">
         <v>23</v>
       </c>
       <c r="Y3" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="Z3" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AA3" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AB3" t="n">
         <v>10</v>
@@ -1186,7 +1186,7 @@
         <v>36</v>
       </c>
       <c r="AE3" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF3" t="n">
         <v>11.5</v>
@@ -1198,7 +1198,7 @@
         <v>28</v>
       </c>
       <c r="AI3" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ3" t="n">
         <v>16.5</v>
@@ -1210,37 +1210,37 @@
         <v>44</v>
       </c>
       <c r="AM3" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AO3" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>15.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="AR3" t="n">
         <v>42</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.8</v>
+        <v>3.7</v>
       </c>
       <c r="AU3" t="n">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AX3" t="n">
         <v>8.199999999999999</v>
@@ -1249,10 +1249,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BB3" t="n">
         <v>4.3</v>
@@ -1261,10 +1261,10 @@
         <v>4.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BF3" t="n">
         <v>6.4</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.98</v>
+        <v>8.6</v>
       </c>
       <c r="BN3" t="n">
         <v>4.1</v>
@@ -1312,19 +1312,19 @@
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>12</v>
+        <v>2.62</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>12</v>
+        <v>2.62</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H4" t="n">
         <v>4.7</v>
@@ -1395,7 +1395,7 @@
         <v>1.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
         <v>2.2</v>
@@ -1413,7 +1413,7 @@
         <v>1.9</v>
       </c>
       <c r="V4" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W4" t="n">
         <v>2.04</v>
@@ -1425,7 +1425,7 @@
         <v>16.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AA4" t="n">
         <v>150</v>
@@ -1434,19 +1434,19 @@
         <v>8</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
         <v>80</v>
       </c>
       <c r="AF4" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
         <v>22</v>
@@ -1479,10 +1479,10 @@
         <v>13.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT4" t="n">
         <v>6.6</v>
@@ -1491,46 +1491,46 @@
         <v>6.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>16.5</v>
+        <v>7</v>
       </c>
       <c r="AW4" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="n">
         <v>17.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB4" t="n">
         <v>17.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BF4" t="n">
         <v>13</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH4" t="n">
         <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BJ4" t="n">
         <v>11.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G5" t="n">
         <v>3.7</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I5" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J5" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L5" t="n">
         <v>1.49</v>
@@ -1652,13 +1652,13 @@
         <v>1.49</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S5" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="T5" t="n">
         <v>2.08</v>
@@ -1667,7 +1667,7 @@
         <v>1.75</v>
       </c>
       <c r="V5" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W5" t="n">
         <v>1.37</v>
@@ -1676,10 +1676,10 @@
         <v>8.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA5" t="n">
         <v>46</v>
@@ -1691,7 +1691,7 @@
         <v>7.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE5" t="n">
         <v>42</v>
@@ -1721,70 +1721,70 @@
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO5" t="n">
         <v>48</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.75</v>
+        <v>7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.9</v>
+        <v>6.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.7</v>
+        <v>13</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.95</v>
+        <v>8</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.3</v>
+        <v>18.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.7</v>
+        <v>13</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.4</v>
+        <v>19.5</v>
       </c>
       <c r="BA5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG5" t="n">
         <v>6</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>5.8</v>
       </c>
       <c r="BH5" t="n">
         <v>2.74</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BJ5" t="n">
         <v>12</v>
@@ -1796,25 +1796,25 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>2.18</v>
+        <v>10</v>
       </c>
       <c r="BN5" t="n">
         <v>6.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BP5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BQ5" t="n">
-        <v>2.06</v>
+        <v>8.4</v>
       </c>
       <c r="BR5" t="n">
         <v>60</v>
       </c>
       <c r="BS5" t="n">
-        <v>2.12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT5" t="n">
         <v>5.5</v>
@@ -1826,23 +1826,23 @@
         <v>25</v>
       </c>
       <c r="BW5" t="n">
-        <v>2.02</v>
+        <v>7.6</v>
       </c>
       <c r="BX5" t="n">
         <v>50</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>2.12</v>
+        <v>9</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
         <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T6" t="n">
         <v>1.73</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>3.25</v>
+        <v>1.1</v>
       </c>
       <c r="O7" t="n">
         <v>1.01</v>
@@ -2181,10 +2181,10 @@
         <v>1.45</v>
       </c>
       <c r="X7" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y7" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z7" t="n">
         <v>500</v>
@@ -2193,13 +2193,13 @@
         <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC7" t="n">
-        <v>95</v>
+        <v>950</v>
       </c>
       <c r="AD7" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE7" t="n">
         <v>500</v>
@@ -2208,10 +2208,10 @@
         <v>500</v>
       </c>
       <c r="AG7" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH7" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI7" t="n">
         <v>500</v>
@@ -2235,52 +2235,52 @@
         <v>500</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BF7" t="n">
         <v>1.55</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="I8" t="n">
         <v>990</v>
@@ -2396,7 +2396,7 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -2429,10 +2429,10 @@
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W8" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="X8" t="n">
         <v>29</v>
@@ -2489,7 +2489,7 @@
         <v>700</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AQ8" t="n">
         <v>11</v>
@@ -2501,7 +2501,7 @@
         <v>2</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -2537,7 +2537,7 @@
         <v>2</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BG8" t="n">
         <v>32</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.48</v>
+        <v>2.06</v>
       </c>
       <c r="G9" t="n">
         <v>2.76</v>
@@ -2644,13 +2644,13 @@
         <v>2.48</v>
       </c>
       <c r="I9" t="n">
-        <v>44</v>
+        <v>3.25</v>
       </c>
       <c r="J9" t="n">
         <v>3.1</v>
       </c>
       <c r="K9" t="n">
-        <v>14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2683,7 +2683,7 @@
         <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="W9" t="n">
         <v>1.56</v>
@@ -2800,65 +2800,65 @@
         <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -3054,65 +3054,65 @@
         <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="G11" t="n">
         <v>2.06</v>
@@ -3164,7 +3164,7 @@
         <v>1.22</v>
       </c>
       <c r="M11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N11" t="n">
         <v>5.8</v>
@@ -3209,7 +3209,7 @@
         <v>85</v>
       </c>
       <c r="AB11" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC11" t="n">
         <v>11</v>
@@ -3260,7 +3260,7 @@
         <v>5</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT11" t="n">
         <v>10.5</v>
@@ -3284,7 +3284,7 @@
         <v>11</v>
       </c>
       <c r="BA11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB11" t="n">
         <v>16.5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
         <v>2.44</v>
       </c>
       <c r="I12" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J12" t="n">
         <v>3.8</v>
@@ -3415,13 +3415,13 @@
         <v>4.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M12" t="n">
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O12" t="n">
         <v>1.19</v>
@@ -3433,7 +3433,7 @@
         <v>1.56</v>
       </c>
       <c r="R12" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S12" t="n">
         <v>2.36</v>
@@ -3445,7 +3445,7 @@
         <v>2.58</v>
       </c>
       <c r="V12" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W12" t="n">
         <v>1.51</v>
@@ -3454,13 +3454,13 @@
         <v>26</v>
       </c>
       <c r="Y12" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z12" t="n">
         <v>22</v>
       </c>
       <c r="AA12" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AB12" t="n">
         <v>21</v>
@@ -3496,10 +3496,10 @@
         <v>38</v>
       </c>
       <c r="AM12" t="n">
-        <v>250</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO12" t="n">
         <v>16.5</v>
@@ -3541,7 +3541,7 @@
         <v>21</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BC12" t="n">
         <v>19</v>
@@ -3550,7 +3550,7 @@
         <v>16</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BF12" t="n">
         <v>11.5</v>
@@ -3568,16 +3568,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK12" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BN12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO12" t="n">
         <v>4.8</v>
@@ -3586,13 +3586,13 @@
         <v>20</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR12" t="n">
         <v>27</v>
       </c>
       <c r="BS12" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT12" t="n">
         <v>6.2</v>
@@ -3604,23 +3604,23 @@
         <v>17</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX12" t="n">
         <v>25</v>
       </c>
       <c r="BY12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BZ12" t="n">
         <v>16.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
         <v>3.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R13" t="n">
         <v>1.94</v>
@@ -3711,7 +3711,7 @@
         <v>27</v>
       </c>
       <c r="Z13" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AA13" t="n">
         <v>34</v>
@@ -3720,25 +3720,25 @@
         <v>29</v>
       </c>
       <c r="AC13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD13" t="n">
         <v>16</v>
       </c>
       <c r="AE13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF13" t="n">
         <v>34</v>
       </c>
       <c r="AG13" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH13" t="n">
         <v>16</v>
       </c>
       <c r="AI13" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AJ13" t="n">
         <v>55</v>
@@ -3753,13 +3753,13 @@
         <v>46</v>
       </c>
       <c r="AN13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO13" t="n">
         <v>10.5</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AQ13" t="n">
         <v>15.5</v>
@@ -3777,7 +3777,7 @@
         <v>8.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AW13" t="n">
         <v>15</v>
@@ -3810,7 +3810,7 @@
         <v>10.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="BH13" t="n">
         <v>5.6</v>
@@ -3834,7 +3834,7 @@
         <v>7.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BP13" t="n">
         <v>18.5</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.92</v>
+        <v>4.6</v>
       </c>
       <c r="G14" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="H14" t="n">
         <v>1.5</v>
@@ -3920,7 +3920,7 @@
         <v>5.1</v>
       </c>
       <c r="K14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3929,28 +3929,28 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>2.82</v>
+        <v>6.4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="P14" t="n">
-        <v>2.82</v>
+        <v>1.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
       <c r="R14" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="T14" t="n">
-        <v>1.11</v>
+        <v>1.51</v>
       </c>
       <c r="U14" t="n">
-        <v>1.11</v>
+        <v>2.58</v>
       </c>
       <c r="V14" t="n">
         <v>2.62</v>
@@ -3959,37 +3959,37 @@
         <v>1.18</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y14" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z14" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AA14" t="n">
-        <v>900</v>
+        <v>970</v>
       </c>
       <c r="AB14" t="n">
-        <v>150</v>
+        <v>950</v>
       </c>
       <c r="AC14" t="n">
-        <v>95</v>
+        <v>970</v>
       </c>
       <c r="AD14" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AE14" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AF14" t="n">
         <v>180</v>
       </c>
       <c r="AG14" t="n">
-        <v>130</v>
+        <v>950</v>
       </c>
       <c r="AH14" t="n">
-        <v>240</v>
+        <v>970</v>
       </c>
       <c r="AI14" t="n">
         <v>500</v>
@@ -3998,137 +3998,137 @@
         <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO14" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>2.22</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -4165,10 +4165,10 @@
         <v>4.8</v>
       </c>
       <c r="H15" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="I15" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="J15" t="n">
         <v>2.96</v>
@@ -4207,7 +4207,7 @@
         <v>1.75</v>
       </c>
       <c r="V15" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="W15" t="n">
         <v>1.26</v>
@@ -4330,13 +4330,13 @@
         <v>12</v>
       </c>
       <c r="BK15" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN15" t="n">
         <v>7.8</v>
@@ -4348,13 +4348,13 @@
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>32</v>
+        <v>1.04</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>48</v>
+        <v>1.04</v>
       </c>
       <c r="BT15" t="n">
         <v>4.9</v>
@@ -4366,23 +4366,23 @@
         <v>19</v>
       </c>
       <c r="BW15" t="n">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>30</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>32</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -4416,10 +4416,10 @@
         <v>2.3</v>
       </c>
       <c r="G16" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="H16" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="I16" t="n">
         <v>3.95</v>
@@ -4440,13 +4440,13 @@
         <v>2.74</v>
       </c>
       <c r="O16" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P16" t="n">
         <v>1.57</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R16" t="n">
         <v>1.21</v>
@@ -4464,7 +4464,7 @@
         <v>1.34</v>
       </c>
       <c r="W16" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="X16" t="n">
         <v>9.800000000000001</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
         <v>1.91</v>
       </c>
       <c r="H17" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="I17" t="n">
         <v>6.2</v>
@@ -4691,22 +4691,22 @@
         <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="O17" t="n">
         <v>1.4</v>
       </c>
       <c r="P17" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="R17" t="n">
         <v>1.26</v>
       </c>
       <c r="S17" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="T17" t="n">
         <v>2</v>
@@ -4775,10 +4775,10 @@
         <v>700</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.3</v>
+        <v>12</v>
       </c>
       <c r="AR17" t="n">
         <v>6.6</v>
@@ -4787,34 +4787,34 @@
         <v>7.4</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.85</v>
+        <v>5.7</v>
       </c>
       <c r="AU17" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>6</v>
+        <v>16.5</v>
       </c>
       <c r="AW17" t="n">
         <v>7.2</v>
       </c>
       <c r="AX17" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="AY17" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>5.9</v>
+        <v>17.5</v>
       </c>
       <c r="BA17" t="n">
         <v>7.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.7</v>
+        <v>15</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.8</v>
+        <v>16.5</v>
       </c>
       <c r="BD17" t="n">
         <v>6.8</v>
@@ -4823,7 +4823,7 @@
         <v>7.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.3</v>
+        <v>12</v>
       </c>
       <c r="BG17" t="n">
         <v>7.4</v>
@@ -4832,7 +4832,7 @@
         <v>3.2</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="BJ17" t="n">
         <v>11.5</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -4921,118 +4921,118 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="G18" t="n">
-        <v>2.76</v>
+        <v>2.58</v>
       </c>
       <c r="H18" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="I18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S18" t="n">
         <v>6.2</v>
       </c>
-      <c r="J18" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="K18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.66</v>
-      </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="V18" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="W18" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AR18" t="n">
         <v>1.03</v>
@@ -5041,22 +5041,22 @@
         <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AW18" t="n">
         <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ18" t="n">
         <v>1.03</v>
@@ -5077,74 +5077,74 @@
         <v>1.03</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>120</v>
       </c>
       <c r="BH18" t="n">
         <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18" t="n">
         <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN18" t="n">
         <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT18" t="n">
         <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G19" t="n">
         <v>2.38</v>
@@ -5184,22 +5184,22 @@
         <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J19" t="n">
         <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L19" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M19" t="n">
         <v>1.13</v>
       </c>
       <c r="N19" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O19" t="n">
         <v>1.51</v>
@@ -5208,28 +5208,28 @@
         <v>1.57</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="R19" t="n">
         <v>1.21</v>
       </c>
       <c r="S19" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="U19" t="n">
         <v>1.83</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W19" t="n">
         <v>1.72</v>
       </c>
       <c r="X19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y19" t="n">
         <v>11.5</v>
@@ -5241,7 +5241,7 @@
         <v>100</v>
       </c>
       <c r="AB19" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC19" t="n">
         <v>7.4</v>
@@ -5250,7 +5250,7 @@
         <v>17.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF19" t="n">
         <v>13</v>
@@ -5262,7 +5262,7 @@
         <v>21</v>
       </c>
       <c r="AI19" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ19" t="n">
         <v>32</v>
@@ -5271,7 +5271,7 @@
         <v>32</v>
       </c>
       <c r="AL19" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM19" t="n">
         <v>190</v>
@@ -5292,7 +5292,7 @@
         <v>23</v>
       </c>
       <c r="AS19" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT19" t="n">
         <v>6.8</v>
@@ -5304,7 +5304,7 @@
         <v>15.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX19" t="n">
         <v>11.5</v>
@@ -5313,16 +5313,16 @@
         <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA19" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BB19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BD19" t="n">
         <v>50</v>
@@ -5334,10 +5334,10 @@
         <v>10</v>
       </c>
       <c r="BG19" t="n">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="BH19" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BI19" t="n">
         <v>2.42</v>
@@ -5346,13 +5346,13 @@
         <v>11</v>
       </c>
       <c r="BK19" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BN19" t="n">
         <v>4.9</v>
@@ -5364,13 +5364,13 @@
         <v>19.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BT19" t="n">
         <v>6.8</v>
@@ -5382,23 +5382,23 @@
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -5435,19 +5435,19 @@
         <v>2.5</v>
       </c>
       <c r="H20" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I20" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J20" t="n">
         <v>3.1</v>
       </c>
       <c r="K20" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M20" t="n">
         <v>1.09</v>
@@ -5477,7 +5477,7 @@
         <v>1.94</v>
       </c>
       <c r="V20" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W20" t="n">
         <v>1.67</v>
@@ -5498,7 +5498,7 @@
         <v>10</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD20" t="n">
         <v>18</v>
@@ -5513,7 +5513,7 @@
         <v>13</v>
       </c>
       <c r="AH20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI20" t="n">
         <v>65</v>
@@ -5546,7 +5546,7 @@
         <v>19</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT20" t="n">
         <v>7.4</v>
@@ -5558,7 +5558,7 @@
         <v>11.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX20" t="n">
         <v>11</v>
@@ -5570,79 +5570,79 @@
         <v>14.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BC20" t="n">
         <v>21</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF20" t="n">
         <v>18.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH20" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN20" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP20" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV20" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>
@@ -5740,16 +5740,16 @@
         <v>22</v>
       </c>
       <c r="Y21" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Z21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA21" t="n">
         <v>60</v>
       </c>
       <c r="AB21" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC21" t="n">
         <v>10.5</v>
@@ -5758,13 +5758,13 @@
         <v>16</v>
       </c>
       <c r="AE21" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF21" t="n">
         <v>19</v>
       </c>
       <c r="AG21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH21" t="n">
         <v>19.5</v>
@@ -5791,16 +5791,16 @@
         <v>29</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AR21" t="n">
         <v>16</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AT21" t="n">
         <v>9.199999999999999</v>
@@ -5809,13 +5809,13 @@
         <v>6.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AX21" t="n">
-        <v>3.95</v>
+        <v>14.5</v>
       </c>
       <c r="AY21" t="n">
         <v>8.800000000000001</v>
@@ -5824,25 +5824,25 @@
         <v>12</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BC21" t="n">
         <v>18</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BF21" t="n">
         <v>12.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH21" t="n">
         <v>3.95</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-04 20:34:09</t>
+          <t>2026-06-04 22:43:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="G2" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
         <v>4.6</v>
       </c>
       <c r="I2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
         <v>3.5</v>
@@ -887,13 +887,13 @@
         <v>1.35</v>
       </c>
       <c r="P2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q2" t="n">
         <v>2.02</v>
       </c>
       <c r="R2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S2" t="n">
         <v>3.65</v>
@@ -902,7 +902,7 @@
         <v>1.82</v>
       </c>
       <c r="U2" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
         <v>1.25</v>
@@ -914,13 +914,13 @@
         <v>14</v>
       </c>
       <c r="Y2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z2" t="n">
         <v>36</v>
       </c>
       <c r="AA2" t="n">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AB2" t="n">
         <v>8.800000000000001</v>
@@ -932,10 +932,10 @@
         <v>19</v>
       </c>
       <c r="AE2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF2" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG2" t="n">
         <v>10.5</v>
@@ -953,31 +953,31 @@
         <v>23</v>
       </c>
       <c r="AL2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM2" t="n">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="AN2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO2" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AP2" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR2" t="n">
         <v>13</v>
       </c>
       <c r="AS2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU2" t="n">
         <v>7</v>
@@ -989,16 +989,16 @@
         <v>22</v>
       </c>
       <c r="AX2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.800000000000001</v>
+        <v>25</v>
       </c>
       <c r="BB2" t="n">
         <v>19</v>
@@ -1010,16 +1010,16 @@
         <v>14</v>
       </c>
       <c r="BE2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2" t="n">
         <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.6</v>
+        <v>32</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BI2" t="n">
         <v>2.64</v>
@@ -1028,13 +1028,13 @@
         <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN2" t="n">
         <v>4.7</v>
@@ -1046,31 +1046,31 @@
         <v>14.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR2" t="n">
         <v>32</v>
       </c>
       <c r="BS2" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BT2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BV2" t="n">
         <v>42</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX2" t="n">
         <v>55</v>
       </c>
       <c r="BY2" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>1.48</v>
       </c>
       <c r="G3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="H3" t="n">
         <v>7.2</v>
@@ -1129,7 +1129,7 @@
         <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
@@ -1144,16 +1144,16 @@
         <v>2.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R3" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S3" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="T3" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U3" t="n">
         <v>2</v>
@@ -1162,28 +1162,28 @@
         <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="X3" t="n">
         <v>23</v>
       </c>
       <c r="Y3" t="n">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="Z3" t="n">
         <v>65</v>
       </c>
       <c r="AA3" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AB3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC3" t="n">
         <v>12.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="AE3" t="n">
         <v>120</v>
@@ -1204,13 +1204,13 @@
         <v>16.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM3" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN3" t="n">
         <v>8.4</v>
@@ -1219,28 +1219,28 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR3" t="n">
         <v>42</v>
       </c>
       <c r="AS3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV3" t="n">
         <v>5</v>
       </c>
-      <c r="AT3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AW3" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AX3" t="n">
         <v>8.199999999999999</v>
@@ -1249,31 +1249,31 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF3" t="n">
         <v>6.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI3" t="n">
         <v>3.4</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>8.6</v>
+        <v>2.98</v>
       </c>
       <c r="BN3" t="n">
         <v>4.1</v>
@@ -1306,25 +1306,25 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="G4" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="H4" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K4" t="n">
         <v>3.75</v>
       </c>
       <c r="L4" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1392,13 +1392,13 @@
         <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R4" t="n">
         <v>1.27</v>
@@ -1407,16 +1407,16 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U4" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="V4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W4" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X4" t="n">
         <v>12</v>
@@ -1425,10 +1425,10 @@
         <v>16.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AA4" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="AB4" t="n">
         <v>8</v>
@@ -1440,13 +1440,13 @@
         <v>21</v>
       </c>
       <c r="AE4" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF4" t="n">
         <v>11.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH4" t="n">
         <v>22</v>
@@ -1458,7 +1458,7 @@
         <v>22</v>
       </c>
       <c r="AK4" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AL4" t="n">
         <v>48</v>
@@ -1473,40 +1473,40 @@
         <v>130</v>
       </c>
       <c r="AP4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
         <v>13.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>8.199999999999999</v>
+        <v>25</v>
       </c>
       <c r="AX4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
         <v>17.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BB4" t="n">
         <v>17.5</v>
@@ -1515,25 +1515,25 @@
         <v>19</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF4" t="n">
         <v>13</v>
       </c>
       <c r="BG4" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BH4" t="n">
         <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BJ4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK4" t="n">
         <v>5.4</v>
@@ -1542,7 +1542,7 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN4" t="n">
         <v>4.6</v>
@@ -1554,31 +1554,31 @@
         <v>14.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR4" t="n">
         <v>34</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT4" t="n">
         <v>8.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
         <v>2.48</v>
       </c>
       <c r="O5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P5" t="n">
         <v>1.49</v>
@@ -1661,10 +1661,10 @@
         <v>5.6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V5" t="n">
         <v>1.56</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -1873,25 +1873,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G6" t="n">
         <v>1.8</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I6" t="n">
         <v>6.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1903,7 +1903,7 @@
         <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
         <v>1.7</v>
@@ -1921,7 +1921,7 @@
         <v>2.06</v>
       </c>
       <c r="V6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W6" t="n">
         <v>2.24</v>
@@ -1978,13 +1978,13 @@
         <v>9.4</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
         <v>5.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AR6" t="n">
         <v>6.4</v>
@@ -1999,7 +1999,7 @@
         <v>4.9</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AW6" t="n">
         <v>6.8</v>
@@ -2011,16 +2011,16 @@
         <v>7</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA6" t="n">
         <v>6.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BD6" t="n">
         <v>6.2</v>
@@ -2029,7 +2029,7 @@
         <v>7</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BG6" t="n">
         <v>6.8</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -2145,28 +2145,28 @@
         <v>4.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1</v>
+        <v>3.45</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P7" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2265,16 +2265,16 @@
         <v>1.16</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BA7" t="n">
         <v>1.18</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BD7" t="n">
         <v>1.18</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
         <v>1.12</v>
       </c>
       <c r="S8" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2435,10 +2435,10 @@
         <v>2.32</v>
       </c>
       <c r="X8" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z8" t="n">
         <v>130</v>
@@ -2447,10 +2447,10 @@
         <v>700</v>
       </c>
       <c r="AB8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD8" t="n">
         <v>85</v>
@@ -2459,7 +2459,7 @@
         <v>900</v>
       </c>
       <c r="AF8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG8" t="n">
         <v>36</v>
@@ -2474,7 +2474,7 @@
         <v>23</v>
       </c>
       <c r="AK8" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AL8" t="n">
         <v>280</v>
@@ -2483,61 +2483,61 @@
         <v>700</v>
       </c>
       <c r="AN8" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AO8" t="n">
         <v>700</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="AS8" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
       </c>
       <c r="AV8" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AX8" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AY8" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="BB8" t="n">
-        <v>13</v>
+        <v>1.95</v>
       </c>
       <c r="BC8" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BE8" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG8" t="n">
         <v>32</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -2635,79 +2635,79 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="G9" t="n">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="H9" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I9" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="K9" t="n">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>2.78</v>
+        <v>7.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="P9" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="R9" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="S9" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>3.05</v>
       </c>
       <c r="V9" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="W9" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="X9" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y9" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z9" t="n">
         <v>500</v>
       </c>
       <c r="AA9" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB9" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC9" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AD9" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AE9" t="n">
         <v>500</v>
@@ -2716,16 +2716,16 @@
         <v>500</v>
       </c>
       <c r="AG9" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AI9" t="n">
         <v>500</v>
       </c>
       <c r="AJ9" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK9" t="n">
         <v>500</v>
@@ -2734,7 +2734,7 @@
         <v>500</v>
       </c>
       <c r="AM9" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN9" t="n">
         <v>500</v>
@@ -2743,58 +2743,58 @@
         <v>500</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>1.96</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>1.95</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>1.97</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>1.96</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>1.95</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>2.62</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>1.96</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>2.08</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>1.96</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.55</v>
+        <v>2.16</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -2943,10 +2943,10 @@
         <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y10" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z10" t="n">
         <v>500</v>
@@ -2955,13 +2955,13 @@
         <v>500</v>
       </c>
       <c r="AB10" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC10" t="n">
-        <v>95</v>
+        <v>950</v>
       </c>
       <c r="AD10" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE10" t="n">
         <v>500</v>
@@ -2970,10 +2970,10 @@
         <v>500</v>
       </c>
       <c r="AG10" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH10" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI10" t="n">
         <v>500</v>
@@ -2997,55 +2997,55 @@
         <v>500</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BG10" t="n">
         <v>1.55</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="G11" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H11" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I11" t="n">
         <v>4.2</v>
@@ -3173,13 +3173,13 @@
         <v>1.16</v>
       </c>
       <c r="P11" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q11" t="n">
         <v>1.49</v>
       </c>
       <c r="R11" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S11" t="n">
         <v>2.22</v>
@@ -3194,7 +3194,7 @@
         <v>1.32</v>
       </c>
       <c r="W11" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X11" t="n">
         <v>34</v>
@@ -3203,7 +3203,7 @@
         <v>24</v>
       </c>
       <c r="Z11" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA11" t="n">
         <v>85</v>
@@ -3233,7 +3233,7 @@
         <v>40</v>
       </c>
       <c r="AJ11" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AK11" t="n">
         <v>21</v>
@@ -3245,7 +3245,7 @@
         <v>60</v>
       </c>
       <c r="AN11" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO11" t="n">
         <v>30</v>
@@ -3257,10 +3257,10 @@
         <v>16</v>
       </c>
       <c r="AR11" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AT11" t="n">
         <v>10.5</v>
@@ -3272,7 +3272,7 @@
         <v>12</v>
       </c>
       <c r="AW11" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AX11" t="n">
         <v>13.5</v>
@@ -3284,7 +3284,7 @@
         <v>11</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BB11" t="n">
         <v>16.5</v>
@@ -3296,13 +3296,13 @@
         <v>18</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BF11" t="n">
         <v>7</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BH11" t="n">
         <v>4.8</v>
@@ -3311,7 +3311,7 @@
         <v>3.6</v>
       </c>
       <c r="BJ11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK11" t="n">
         <v>4.9</v>
@@ -3320,7 +3320,7 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN11" t="n">
         <v>5.4</v>
@@ -3332,13 +3332,13 @@
         <v>13</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BR11" t="n">
         <v>21</v>
       </c>
       <c r="BS11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT11" t="n">
         <v>8</v>
@@ -3350,23 +3350,23 @@
         <v>27</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BY11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ11" t="n">
         <v>14</v>
       </c>
       <c r="CA11" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
         <v>28</v>
       </c>
       <c r="AL12" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AM12" t="n">
         <v>580</v>
@@ -3502,7 +3502,7 @@
         <v>16.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AP12" t="n">
         <v>18</v>
@@ -3541,7 +3541,7 @@
         <v>21</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BC12" t="n">
         <v>19</v>
@@ -3550,7 +3550,7 @@
         <v>16</v>
       </c>
       <c r="BE12" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BF12" t="n">
         <v>11.5</v>
@@ -3559,7 +3559,7 @@
         <v>10</v>
       </c>
       <c r="BH12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI12" t="n">
         <v>3.45</v>
@@ -3586,13 +3586,13 @@
         <v>20</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR12" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT12" t="n">
         <v>6.2</v>
@@ -3613,14 +3613,14 @@
         <v>7</v>
       </c>
       <c r="BZ12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA12" t="n">
         <v>6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -3654,13 +3654,13 @@
         <v>2.86</v>
       </c>
       <c r="G13" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H13" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="I13" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="J13" t="n">
         <v>4.1</v>
@@ -3675,19 +3675,19 @@
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O13" t="n">
         <v>1.12</v>
       </c>
       <c r="P13" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q13" t="n">
         <v>1.37</v>
       </c>
       <c r="R13" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="S13" t="n">
         <v>1.92</v>
@@ -3699,10 +3699,10 @@
         <v>3.15</v>
       </c>
       <c r="V13" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="W13" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X13" t="n">
         <v>46</v>
@@ -3813,10 +3813,10 @@
         <v>3.6</v>
       </c>
       <c r="BH13" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BI13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BJ13" t="n">
         <v>8.199999999999999</v>
@@ -3828,7 +3828,7 @@
         <v>55</v>
       </c>
       <c r="BM13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN13" t="n">
         <v>7.2</v>
@@ -3843,10 +3843,10 @@
         <v>7.6</v>
       </c>
       <c r="BR13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BT13" t="n">
         <v>6.4</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
         <v>11.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M14" t="n">
         <v>1.01</v>
@@ -3944,7 +3944,7 @@
         <v>1.9</v>
       </c>
       <c r="S14" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="T14" t="n">
         <v>1.51</v>
@@ -4067,68 +4067,68 @@
         <v>3.55</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.04</v>
+        <v>1.57</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H15" t="n">
         <v>2.12</v>
       </c>
       <c r="I15" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="J15" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
         <v>3.45</v>
       </c>
       <c r="L15" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M15" t="n">
         <v>1.11</v>
       </c>
       <c r="N15" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="O15" t="n">
         <v>1.51</v>
       </c>
       <c r="P15" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q15" t="n">
         <v>2.52</v>
@@ -4207,10 +4207,10 @@
         <v>1.75</v>
       </c>
       <c r="V15" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="W15" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X15" t="n">
         <v>9.199999999999999</v>
@@ -4246,7 +4246,7 @@
         <v>42</v>
       </c>
       <c r="AI15" t="n">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="AJ15" t="n">
         <v>900</v>
@@ -4264,7 +4264,7 @@
         <v>500</v>
       </c>
       <c r="AO15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP15" t="n">
         <v>7.6</v>
@@ -4300,31 +4300,31 @@
         <v>20</v>
       </c>
       <c r="BA15" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC15" t="n">
         <v>8.6</v>
       </c>
-      <c r="BC15" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BD15" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BG15" t="n">
         <v>21</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="BJ15" t="n">
         <v>12</v>
@@ -4342,7 +4342,7 @@
         <v>7.8</v>
       </c>
       <c r="BO15" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
@@ -4357,13 +4357,13 @@
         <v>1.04</v>
       </c>
       <c r="BT15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BU15" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BV15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BW15" t="n">
         <v>1.04</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -4485,7 +4485,7 @@
         <v>7.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AE16" t="n">
         <v>500</v>
@@ -4530,7 +4530,7 @@
         <v>10.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT16" t="n">
         <v>6.6</v>
@@ -4560,19 +4560,19 @@
         <v>14.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BD16" t="n">
         <v>8</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH16" t="n">
         <v>2.92</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -4670,13 +4670,13 @@
         <v>1.76</v>
       </c>
       <c r="G17" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="H17" t="n">
         <v>5</v>
       </c>
       <c r="I17" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J17" t="n">
         <v>3.2</v>
@@ -4685,7 +4685,7 @@
         <v>3.9</v>
       </c>
       <c r="L17" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="M17" t="n">
         <v>1.09</v>
@@ -4715,7 +4715,7 @@
         <v>1.82</v>
       </c>
       <c r="V17" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W17" t="n">
         <v>2.08</v>
@@ -4727,7 +4727,7 @@
         <v>16.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AA17" t="n">
         <v>900</v>
@@ -4739,7 +4739,7 @@
         <v>8.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE17" t="n">
         <v>700</v>
@@ -4781,10 +4781,10 @@
         <v>12</v>
       </c>
       <c r="AR17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT17" t="n">
         <v>5.7</v>
@@ -4796,10 +4796,10 @@
         <v>16.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY17" t="n">
         <v>8</v>
@@ -4808,25 +4808,25 @@
         <v>17.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC17" t="n">
         <v>16.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF17" t="n">
         <v>12</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH17" t="n">
         <v>3.2</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -4924,16 +4924,16 @@
         <v>2.14</v>
       </c>
       <c r="G18" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="H18" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I18" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="J18" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="K18" t="n">
         <v>3.2</v>
@@ -4942,76 +4942,76 @@
         <v>1.54</v>
       </c>
       <c r="M18" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="N18" t="n">
         <v>2.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="P18" t="n">
         <v>1.39</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
         <v>1.13</v>
       </c>
       <c r="S18" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="T18" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U18" t="n">
         <v>1.59</v>
       </c>
       <c r="V18" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W18" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="X18" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y18" t="n">
         <v>12</v>
       </c>
       <c r="Z18" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA18" t="n">
         <v>150</v>
       </c>
       <c r="AB18" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC18" t="n">
         <v>8.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AE18" t="n">
         <v>110</v>
       </c>
       <c r="AF18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG18" t="n">
-        <v>15</v>
+        <v>950</v>
       </c>
       <c r="AH18" t="n">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="AI18" t="n">
         <v>160</v>
       </c>
       <c r="AJ18" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK18" t="n">
         <v>46</v>
@@ -5035,34 +5035,34 @@
         <v>7.8</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
         <v>4.9</v>
       </c>
       <c r="AU18" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV18" t="n">
         <v>15.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>8</v>
+        <v>1.05</v>
       </c>
       <c r="AY18" t="n">
         <v>10</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
         <v>1.03</v>
@@ -5071,16 +5071,16 @@
         <v>1.03</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>120</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
         <v>2.32</v>
       </c>
       <c r="G19" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H19" t="n">
         <v>4</v>
@@ -5205,19 +5205,19 @@
         <v>1.51</v>
       </c>
       <c r="P19" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="U19" t="n">
         <v>1.83</v>
@@ -5226,7 +5226,7 @@
         <v>1.31</v>
       </c>
       <c r="W19" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X19" t="n">
         <v>8.800000000000001</v>
@@ -5259,7 +5259,7 @@
         <v>12</v>
       </c>
       <c r="AH19" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
         <v>90</v>
@@ -5292,7 +5292,7 @@
         <v>23</v>
       </c>
       <c r="AS19" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AT19" t="n">
         <v>6.8</v>
@@ -5313,28 +5313,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA19" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BB19" t="n">
         <v>27</v>
       </c>
       <c r="BC19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BD19" t="n">
         <v>50</v>
       </c>
       <c r="BE19" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BF19" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BG19" t="n">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="BH19" t="n">
         <v>2.76</v>
@@ -5358,7 +5358,7 @@
         <v>4.9</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BP19" t="n">
         <v>19.5</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -5447,7 +5447,7 @@
         <v>3.65</v>
       </c>
       <c r="L20" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="M20" t="n">
         <v>1.09</v>
@@ -5483,7 +5483,7 @@
         <v>1.67</v>
       </c>
       <c r="X20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y20" t="n">
         <v>14</v>
@@ -5537,19 +5537,19 @@
         <v>60</v>
       </c>
       <c r="AP20" t="n">
-        <v>9</v>
+        <v>3.8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR20" t="n">
         <v>19</v>
       </c>
       <c r="AS20" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU20" t="n">
         <v>5.9</v>
@@ -5558,7 +5558,7 @@
         <v>11.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX20" t="n">
         <v>11</v>
@@ -5570,7 +5570,7 @@
         <v>14.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB20" t="n">
         <v>4.7</v>
@@ -5579,16 +5579,16 @@
         <v>21</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF20" t="n">
-        <v>18.5</v>
+        <v>4.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH20" t="n">
         <v>3.2</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>
@@ -5683,22 +5683,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="G21" t="n">
-        <v>2.64</v>
+        <v>2.82</v>
       </c>
       <c r="H21" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="I21" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="J21" t="n">
         <v>3.75</v>
       </c>
       <c r="K21" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L21" t="n">
         <v>1.29</v>
@@ -5707,25 +5707,25 @@
         <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P21" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R21" t="n">
         <v>1.43</v>
       </c>
       <c r="S21" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T21" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U21" t="n">
         <v>2.28</v>
@@ -5740,154 +5740,154 @@
         <v>22</v>
       </c>
       <c r="Y21" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AA21" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AB21" t="n">
         <v>13.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD21" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE21" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AF21" t="n">
         <v>19</v>
       </c>
       <c r="AG21" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH21" t="n">
         <v>19.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AJ21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL21" t="n">
         <v>36</v>
       </c>
-      <c r="AK21" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>42</v>
-      </c>
       <c r="AM21" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN21" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AO21" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="AQ21" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AR21" t="n">
         <v>16</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="AT21" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA21" t="n">
         <v>6.6</v>
       </c>
-      <c r="AV21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>5</v>
-      </c>
       <c r="BB21" t="n">
-        <v>4.8</v>
+        <v>30</v>
       </c>
       <c r="BC21" t="n">
-        <v>18</v>
+        <v>6.4</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.9</v>
+        <v>24</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF21" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BG21" t="n">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI21" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BJ21" t="n">
         <v>9.4</v>
       </c>
       <c r="BK21" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN21" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BO21" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP21" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BQ21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT21" t="n">
         <v>6.2</v>
       </c>
-      <c r="BR21" t="n">
-        <v>29</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BT21" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BU21" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BV21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BW21" t="n">
         <v>6.8</v>
@@ -5896,17 +5896,17 @@
         <v>32</v>
       </c>
       <c r="BY21" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ21" t="n">
         <v>23</v>
       </c>
       <c r="CA21" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-04 22:43:35</t>
+          <t>2026-06-05 00:53:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB21"/>
+  <dimension ref="A1:CB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,130 +857,130 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="H2" t="n">
         <v>4.6</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
         <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="O2" t="n">
         <v>1.35</v>
       </c>
       <c r="P2" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="T2" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="U2" t="n">
         <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X2" t="n">
         <v>14</v>
       </c>
       <c r="Y2" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="Z2" t="n">
         <v>36</v>
       </c>
       <c r="AA2" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AD2" t="n">
         <v>19</v>
       </c>
       <c r="AE2" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AF2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH2" t="n">
         <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AJ2" t="n">
         <v>23</v>
       </c>
       <c r="AK2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO2" t="n">
         <v>110</v>
       </c>
       <c r="AP2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU2" t="n">
         <v>7.2</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7</v>
       </c>
       <c r="AV2" t="n">
         <v>15.5</v>
@@ -992,10 +992,10 @@
         <v>10</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA2" t="n">
         <v>25</v>
@@ -1010,67 +1010,67 @@
         <v>14</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.800000000000001</v>
+        <v>95</v>
       </c>
       <c r="BF2" t="n">
         <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BH2" t="n">
         <v>3.3</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.64</v>
+        <v>2.98</v>
       </c>
       <c r="BJ2" t="n">
         <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>11</v>
+        <v>120</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="BP2" t="n">
         <v>14.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR2" t="n">
         <v>32</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BT2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BV2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BW2" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BX2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -1111,136 +1111,136 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="G3" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="H3" t="n">
         <v>7.2</v>
       </c>
       <c r="I3" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P3" t="n">
         <v>2.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="R3" t="n">
         <v>1.45</v>
       </c>
       <c r="S3" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V3" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W3" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="X3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Y3" t="n">
         <v>950</v>
       </c>
       <c r="Z3" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AA3" t="n">
         <v>250</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD3" t="n">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="AE3" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="AF3" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="AG3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI3" t="n">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="AJ3" t="n">
-        <v>16.5</v>
+        <v>280</v>
       </c>
       <c r="AK3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM3" t="n">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="AN3" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.9</v>
+        <v>13</v>
       </c>
       <c r="AQ3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AR3" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="AS3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV3" t="n">
         <v>5.3</v>
       </c>
-      <c r="AT3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>5</v>
-      </c>
       <c r="AW3" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AX3" t="n">
         <v>8.199999999999999</v>
@@ -1249,28 +1249,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="BA3" t="n">
         <v>5.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.2</v>
+        <v>100</v>
       </c>
       <c r="BF3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG3" t="n">
         <v>6.4</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>5.4</v>
       </c>
       <c r="BH3" t="n">
         <v>3.8</v>
@@ -1279,52 +1279,52 @@
         <v>3.4</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.98</v>
+        <v>130</v>
       </c>
       <c r="BN3" t="n">
         <v>4.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="BP3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.9</v>
+        <v>12.5</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.78</v>
+        <v>12.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -1365,97 +1365,97 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="G4" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="H4" t="n">
         <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L4" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="O4" t="n">
         <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R4" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="U4" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V4" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z4" t="n">
         <v>60</v>
       </c>
       <c r="AA4" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="AB4" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE4" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AF4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG4" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AH4" t="n">
         <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="AJ4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK4" t="n">
         <v>32</v>
@@ -1467,13 +1467,13 @@
         <v>170</v>
       </c>
       <c r="AN4" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AO4" t="n">
         <v>130</v>
       </c>
       <c r="AP4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ4" t="n">
         <v>13.5</v>
@@ -1482,19 +1482,19 @@
         <v>13</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU4" t="n">
         <v>7.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.4</v>
+        <v>17</v>
       </c>
       <c r="AW4" t="n">
-        <v>25</v>
+        <v>8.6</v>
       </c>
       <c r="AX4" t="n">
         <v>9.199999999999999</v>
@@ -1503,82 +1503,82 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="BB4" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD4" t="n">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>10.5</v>
+        <v>100</v>
       </c>
       <c r="BF4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="BH4" t="n">
         <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.52</v>
+        <v>2.9</v>
       </c>
       <c r="BJ4" t="n">
         <v>11</v>
       </c>
       <c r="BK4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>130</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU4" t="n">
         <v>5.4</v>
       </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BX4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -1619,58 +1619,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H5" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="J5" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="K5" t="n">
         <v>3.25</v>
       </c>
       <c r="L5" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="M5" t="n">
         <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="O5" t="n">
         <v>1.54</v>
       </c>
       <c r="P5" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="R5" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
         <v>5.6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U5" t="n">
         <v>1.76</v>
       </c>
       <c r="V5" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X5" t="n">
         <v>8.6</v>
@@ -1682,7 +1682,7 @@
         <v>16</v>
       </c>
       <c r="AA5" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB5" t="n">
         <v>9.800000000000001</v>
@@ -1694,13 +1694,13 @@
         <v>15.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF5" t="n">
         <v>27</v>
       </c>
       <c r="AG5" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH5" t="n">
         <v>28</v>
@@ -1715,7 +1715,7 @@
         <v>60</v>
       </c>
       <c r="AL5" t="n">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="AM5" t="n">
         <v>500</v>
@@ -1724,10 +1724,10 @@
         <v>600</v>
       </c>
       <c r="AO5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AQ5" t="n">
         <v>6.6</v>
@@ -1736,7 +1736,7 @@
         <v>13</v>
       </c>
       <c r="AS5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT5" t="n">
         <v>8</v>
@@ -1748,7 +1748,7 @@
         <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX5" t="n">
         <v>18.5</v>
@@ -1760,31 +1760,31 @@
         <v>19.5</v>
       </c>
       <c r="BA5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG5" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>6</v>
-      </c>
       <c r="BH5" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BJ5" t="n">
         <v>12</v>
@@ -1805,10 +1805,10 @@
         <v>4.8</v>
       </c>
       <c r="BP5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR5" t="n">
         <v>60</v>
@@ -1829,7 +1829,7 @@
         <v>7.6</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
         <v>8.800000000000001</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -1873,64 +1873,64 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="H6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I6" t="n">
         <v>6.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K6" t="n">
         <v>4.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="R6" t="n">
         <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="T6" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="U6" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
         <v>1.2</v>
       </c>
       <c r="W6" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="X6" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y6" t="n">
         <v>22</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>23</v>
       </c>
       <c r="Z6" t="n">
         <v>48</v>
@@ -1939,22 +1939,22 @@
         <v>700</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD6" t="n">
         <v>23</v>
       </c>
       <c r="AE6" t="n">
-        <v>160</v>
+        <v>470</v>
       </c>
       <c r="AF6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH6" t="n">
         <v>21</v>
@@ -1963,7 +1963,7 @@
         <v>160</v>
       </c>
       <c r="AJ6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK6" t="n">
         <v>18</v>
@@ -1975,135 +1975,135 @@
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO6" t="n">
-        <v>600</v>
+        <v>160</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AU6" t="n">
         <v>4.9</v>
       </c>
       <c r="AV6" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AY6" t="n">
         <v>7</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BA6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB6" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="BC6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD6" t="n">
         <v>7.6</v>
       </c>
-      <c r="BC6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BE6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH6" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BJ6" t="n">
         <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BP6" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BR6" t="n">
         <v>25</v>
       </c>
       <c r="BS6" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BT6" t="n">
         <v>9.4</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BV6" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BY6" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ6" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="CA6" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FBK Karlstad</t>
+          <t>Paradou</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IF Karlstad</t>
+          <t>ES Setif</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="G7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT7" t="n">
         <v>3.2</v>
       </c>
-      <c r="H7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K7" t="n">
+      <c r="AU7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE7" t="n">
         <v>4.3</v>
       </c>
-      <c r="L7" t="n">
+      <c r="BF7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
         <v>1.01</v>
       </c>
-      <c r="M7" t="n">
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>27</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>18</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
         <v>1.01</v>
       </c>
-      <c r="N7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>950</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>950</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.04</v>
+        <v>25</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,189 +2367,189 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>FBK Karlstad</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>IF Karlstad</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.62</v>
+        <v>2.66</v>
       </c>
       <c r="G8" t="n">
-        <v>1.75</v>
+        <v>2.9</v>
       </c>
       <c r="H8" t="n">
-        <v>5.5</v>
+        <v>2.58</v>
       </c>
       <c r="I8" t="n">
-        <v>990</v>
+        <v>2.88</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="K8" t="n">
-        <v>5.2</v>
+        <v>3.95</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>4.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>2.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="R8" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5</v>
+        <v>2.98</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>2.34</v>
       </c>
       <c r="V8" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="W8" t="n">
-        <v>2.32</v>
+        <v>1.53</v>
       </c>
       <c r="X8" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="Y8" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="Z8" t="n">
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="AA8" t="n">
-        <v>700</v>
+        <v>85</v>
       </c>
       <c r="AB8" t="n">
         <v>14</v>
       </c>
       <c r="AC8" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>85</v>
       </c>
-      <c r="AE8" t="n">
-        <v>900</v>
-      </c>
-      <c r="AF8" t="n">
+      <c r="AK8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>13</v>
       </c>
-      <c r="AG8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>120</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>280</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>700</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>700</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>15</v>
-      </c>
       <c r="BA8" t="n">
-        <v>2.12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.95</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>21</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.4</v>
+        <v>16</v>
       </c>
       <c r="BG8" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK8" t="n">
         <v>1.04</v>
@@ -2561,57 +2561,57 @@
         <v>1.04</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ8" t="n">
         <v>1.04</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS8" t="n">
         <v>1.04</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW8" t="n">
         <v>1.04</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY8" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA8" t="n">
         <v>1.04</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,180 +2621,180 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Reynir Sandgeroi</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Augnablik</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.26</v>
+        <v>1.61</v>
       </c>
       <c r="G9" t="n">
-        <v>2.62</v>
+        <v>1.72</v>
       </c>
       <c r="H9" t="n">
-        <v>2.5</v>
+        <v>5.8</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1</v>
+        <v>990</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>7.2</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T9" t="n">
         <v>1.11</v>
       </c>
-      <c r="P9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.38</v>
-      </c>
       <c r="U9" t="n">
-        <v>3.05</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.51</v>
+        <v>1.1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.61</v>
+        <v>2.38</v>
       </c>
       <c r="X9" t="n">
-        <v>950</v>
+        <v>27</v>
       </c>
       <c r="Y9" t="n">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="Z9" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AA9" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AB9" t="n">
-        <v>950</v>
+        <v>14</v>
       </c>
       <c r="AC9" t="n">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="AD9" t="n">
-        <v>970</v>
+        <v>70</v>
       </c>
       <c r="AE9" t="n">
-        <v>500</v>
+        <v>680</v>
       </c>
       <c r="AF9" t="n">
-        <v>500</v>
+        <v>13</v>
       </c>
       <c r="AG9" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH9" t="n">
-        <v>970</v>
+        <v>120</v>
       </c>
       <c r="AI9" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AJ9" t="n">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AK9" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL9" t="n">
-        <v>500</v>
+        <v>280</v>
       </c>
       <c r="AM9" t="n">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN9" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AO9" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.96</v>
+        <v>4.3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.95</v>
+        <v>12</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.95</v>
+        <v>3.75</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="AV9" t="n">
-        <v>5</v>
+        <v>18.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.62</v>
+        <v>2.14</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.96</v>
+        <v>6.2</v>
       </c>
       <c r="AY9" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.2</v>
+        <v>15</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="BB9" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="BC9" t="n">
-        <v>2</v>
+        <v>12.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.96</v>
+        <v>21</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.16</v>
+        <v>32</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,67 +2880,67 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Kormakur/Hvot</t>
+          <t>Reynir Sandgeroi</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IF Magni</t>
+          <t>Augnablik</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.61</v>
+        <v>2.26</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="H10" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>2.96</v>
       </c>
       <c r="J10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>44</v>
+        <v>5.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="R10" t="n">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="S10" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>3</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="X10" t="n">
         <v>950</v>
@@ -2958,7 +2958,7 @@
         <v>950</v>
       </c>
       <c r="AC10" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AD10" t="n">
         <v>950</v>
@@ -2979,7 +2979,7 @@
         <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK10" t="n">
         <v>500</v>
@@ -2988,7 +2988,7 @@
         <v>500</v>
       </c>
       <c r="AM10" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
         <v>500</v>
@@ -2997,64 +2997,64 @@
         <v>500</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.13</v>
+        <v>2.56</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.13</v>
+        <v>3</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.13</v>
+        <v>2.42</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.13</v>
+        <v>2.62</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.1</v>
+        <v>2.38</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.13</v>
+        <v>3</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.13</v>
+        <v>2.62</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.13</v>
+        <v>2.4</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.09</v>
+        <v>4.8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.13</v>
+        <v>3.6</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.13</v>
+        <v>2.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.13</v>
+        <v>2.56</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.11</v>
+        <v>3.15</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.13</v>
+        <v>3.05</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.13</v>
+        <v>2.48</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.13</v>
+        <v>3.35</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.55</v>
+        <v>2.64</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
@@ -3090,7 +3090,7 @@
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3134,239 +3134,239 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Kormakur/Hvot</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>IF Magni</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.86</v>
+        <v>1.69</v>
       </c>
       <c r="G11" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="I11" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="K11" t="n">
-        <v>4.7</v>
+        <v>25</v>
       </c>
       <c r="L11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>950</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>1.22</v>
       </c>
-      <c r="M11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="X11" t="n">
-        <v>34</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>16</v>
-      </c>
       <c r="AR11" t="n">
-        <v>5.4</v>
+        <v>1.23</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.9</v>
+        <v>1.23</v>
       </c>
       <c r="AT11" t="n">
-        <v>10.5</v>
+        <v>1.21</v>
       </c>
       <c r="AU11" t="n">
-        <v>8</v>
+        <v>1.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>12</v>
+        <v>1.22</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.8</v>
+        <v>1.23</v>
       </c>
       <c r="AX11" t="n">
-        <v>13.5</v>
+        <v>1.2</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.199999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="AZ11" t="n">
-        <v>11</v>
+        <v>1.24</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.5</v>
+        <v>1.23</v>
       </c>
       <c r="BB11" t="n">
-        <v>16.5</v>
+        <v>1.23</v>
       </c>
       <c r="BC11" t="n">
-        <v>13</v>
+        <v>1.22</v>
       </c>
       <c r="BD11" t="n">
-        <v>18</v>
+        <v>1.23</v>
       </c>
       <c r="BE11" t="n">
-        <v>6</v>
+        <v>1.24</v>
       </c>
       <c r="BF11" t="n">
-        <v>7</v>
+        <v>1.21</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.1</v>
+        <v>1.55</v>
       </c>
       <c r="BH11" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN11" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BP11" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR11" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV11" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX11" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -3388,239 +3388,239 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Leiknir R</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.64</v>
+        <v>1.9</v>
       </c>
       <c r="G12" t="n">
-        <v>2.96</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>2.44</v>
+        <v>3.65</v>
       </c>
       <c r="I12" t="n">
-        <v>2.66</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="M12" t="n">
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
+        <v>6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="X12" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>470</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA12" t="n">
         <v>5.5</v>
       </c>
-      <c r="O12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="X12" t="n">
-        <v>26</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN12" t="n">
+      <c r="BB12" t="n">
         <v>16.5</v>
       </c>
-      <c r="AO12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP12" t="n">
+      <c r="BC12" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD12" t="n">
         <v>18</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>16</v>
-      </c>
       <c r="BE12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF12" t="n">
         <v>6.8</v>
       </c>
-      <c r="BF12" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BG12" t="n">
-        <v>10</v>
+        <v>5.1</v>
       </c>
       <c r="BH12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="BJ12" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK12" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BN12" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="BP12" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT12" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV12" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BX12" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="BY12" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="CA12" t="n">
         <v>6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
@@ -3642,246 +3642,246 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Leiknir R</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="G13" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="H13" t="n">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="I13" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="J13" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="K13" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="M13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="P13" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="R13" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="S13" t="n">
-        <v>1.92</v>
+        <v>2.44</v>
       </c>
       <c r="T13" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="U13" t="n">
-        <v>3.15</v>
+        <v>2.66</v>
       </c>
       <c r="V13" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="W13" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="X13" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="Y13" t="n">
-        <v>27</v>
+        <v>17.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AA13" t="n">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="AB13" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="AC13" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="AF13" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AG13" t="n">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI13" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="AJ13" t="n">
-        <v>55</v>
+        <v>900</v>
       </c>
       <c r="AK13" t="n">
         <v>27</v>
       </c>
       <c r="AL13" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AM13" t="n">
-        <v>46</v>
+        <v>200</v>
       </c>
       <c r="AN13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO13" t="n">
         <v>13.5</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AP13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>10.5</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="BA13" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BO13" t="n">
         <v>4.9</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR13" t="n">
+      <c r="BP13" t="n">
         <v>20</v>
       </c>
-      <c r="AS13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT13" t="n">
+      <c r="BQ13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV13" t="n">
         <v>17</v>
       </c>
-      <c r="AU13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>19</v>
-      </c>
-      <c r="BE13" t="n">
+      <c r="BW13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>24</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BZ13" t="n">
         <v>16</v>
       </c>
-      <c r="BF13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BK13" t="n">
+      <c r="CA13" t="n">
         <v>6</v>
       </c>
-      <c r="BL13" t="n">
-        <v>55</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>21</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>15</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>19</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>11</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>5.9</v>
-      </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,251 +3891,251 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Hviti Riddarinn</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Haukar</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K14" t="n">
         <v>4.6</v>
       </c>
-      <c r="G14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>11.5</v>
-      </c>
       <c r="L14" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="O14" t="n">
         <v>1.12</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="S14" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="T14" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="U14" t="n">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="V14" t="n">
-        <v>2.62</v>
+        <v>1.72</v>
       </c>
       <c r="W14" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="X14" t="n">
-        <v>950</v>
+        <v>46</v>
       </c>
       <c r="Y14" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="Z14" t="n">
-        <v>970</v>
+        <v>28</v>
       </c>
       <c r="AA14" t="n">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="AB14" t="n">
-        <v>950</v>
+        <v>29</v>
       </c>
       <c r="AC14" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AD14" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AE14" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AF14" t="n">
-        <v>180</v>
+        <v>34</v>
       </c>
       <c r="AG14" t="n">
-        <v>950</v>
+        <v>17</v>
       </c>
       <c r="AH14" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AI14" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK14" t="n">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="AL14" t="n">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="AM14" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AN14" t="n">
-        <v>46</v>
+        <v>13.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.38</v>
+        <v>5.1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="AR14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>16</v>
+      </c>
+      <c r="BF14" t="n">
         <v>10.5</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="BG14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BK14" t="n">
         <v>6</v>
       </c>
-      <c r="AT14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU14" t="n">
+      <c r="BL14" t="n">
+        <v>55</v>
+      </c>
+      <c r="BM14" t="n">
         <v>10</v>
       </c>
-      <c r="AV14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BP14" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>2.34</v>
+        <v>7.6</v>
       </c>
       <c r="BR14" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS14" t="n">
-        <v>2.88</v>
+        <v>7.8</v>
       </c>
       <c r="BT14" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="BV14" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BX14" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BY14" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="CA14" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,251 +4145,251 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CA Ituzaingo</t>
+          <t>Hviti Riddarinn</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Real Pilar FC</t>
+          <t>Haukar</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="G15" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="H15" t="n">
-        <v>2.12</v>
+        <v>1.51</v>
       </c>
       <c r="I15" t="n">
-        <v>2.26</v>
+        <v>1.62</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="L15" t="n">
-        <v>1.48</v>
+        <v>1.21</v>
       </c>
       <c r="M15" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>2.62</v>
+        <v>6.2</v>
       </c>
       <c r="O15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="T15" t="n">
         <v>1.51</v>
       </c>
-      <c r="P15" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.1</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.75</v>
+        <v>2.58</v>
       </c>
       <c r="V15" t="n">
-        <v>1.79</v>
+        <v>2.6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X15" t="n">
-        <v>9.199999999999999</v>
+        <v>950</v>
       </c>
       <c r="Y15" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>180</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>240</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>160</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AP15" t="n">
         <v>7.4</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>120</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>540</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>500</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>7.6</v>
       </c>
       <c r="AQ15" t="n">
         <v>6</v>
       </c>
       <c r="AR15" t="n">
-        <v>10</v>
+        <v>5.7</v>
       </c>
       <c r="AS15" t="n">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="AT15" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>9.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="AW15" t="n">
-        <v>14.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX15" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="AY15" t="n">
-        <v>16</v>
+        <v>6.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BF15" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>21</v>
+        <v>3.1</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.86</v>
+        <v>5.8</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.34</v>
+        <v>4.3</v>
       </c>
       <c r="BJ15" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BN15" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BT15" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BU15" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BV15" t="n">
-        <v>18</v>
+        <v>9.4</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BX15" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,251 +4399,251 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wanderers (Uru)</t>
+          <t>CA Ituzaingo</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>Real Pilar FC</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.3</v>
+        <v>3.85</v>
       </c>
       <c r="G16" t="n">
-        <v>2.48</v>
+        <v>4.6</v>
       </c>
       <c r="H16" t="n">
-        <v>3.65</v>
+        <v>2.18</v>
       </c>
       <c r="I16" t="n">
-        <v>3.95</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="K16" t="n">
         <v>3.4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="M16" t="n">
         <v>1.11</v>
       </c>
       <c r="N16" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="O16" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="P16" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="R16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T16" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U16" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="V16" t="n">
-        <v>1.34</v>
+        <v>1.72</v>
       </c>
       <c r="W16" t="n">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="X16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Y16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB16" t="n">
         <v>12</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="AC16" t="n">
         <v>7.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>500</v>
+        <v>12</v>
       </c>
       <c r="AE16" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AF16" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AG16" t="n">
         <v>21</v>
       </c>
       <c r="AH16" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AI16" t="n">
         <v>500</v>
       </c>
       <c r="AJ16" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AK16" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AL16" t="n">
         <v>500</v>
       </c>
       <c r="AM16" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN16" t="n">
         <v>500</v>
       </c>
       <c r="AO16" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AP16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA16" t="n">
         <v>7.4</v>
       </c>
-      <c r="AQ16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT16" t="n">
+      <c r="BB16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG16" t="n">
         <v>6.6</v>
       </c>
-      <c r="AU16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY16" t="n">
+      <c r="BH16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ16" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ16" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
         <v>10</v>
       </c>
-      <c r="BN16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ16" t="n">
+      <c r="BT16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>19</v>
+      </c>
+      <c r="BW16" t="n">
         <v>7.2</v>
       </c>
-      <c r="BR16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,246 +4658,246 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Plaza Colonia</t>
+          <t>Wanderers (Uru)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Huracan del Paso</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.76</v>
+        <v>2.32</v>
       </c>
       <c r="G17" t="n">
-        <v>1.92</v>
+        <v>2.44</v>
       </c>
       <c r="H17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S17" t="n">
         <v>5</v>
       </c>
-      <c r="I17" t="n">
-        <v>6</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S17" t="n">
-        <v>4.1</v>
-      </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U17" t="n">
         <v>1.82</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="W17" t="n">
-        <v>2.08</v>
+        <v>1.69</v>
       </c>
       <c r="X17" t="n">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y17" t="n">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AA17" t="n">
         <v>900</v>
       </c>
       <c r="AB17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC17" t="n">
         <v>7.6</v>
       </c>
-      <c r="AC17" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AD17" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF17" t="n">
         <v>25</v>
       </c>
-      <c r="AE17" t="n">
-        <v>700</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>11</v>
-      </c>
       <c r="AG17" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AH17" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="AI17" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="AJ17" t="n">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AK17" t="n">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="AL17" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AM17" t="n">
         <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>16.5</v>
+        <v>70</v>
       </c>
       <c r="AO17" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="AP17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG17" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BH17" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.74</v>
+        <v>2.38</v>
       </c>
       <c r="BJ17" t="n">
         <v>11.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>2.44</v>
+        <v>11</v>
       </c>
       <c r="BN17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO17" t="n">
         <v>4.4</v>
       </c>
-      <c r="BO17" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BP17" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>2.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="BU17" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>2.36</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.38</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ17" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>2.3</v>
+        <v>9.4</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,251 +4907,251 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Talleres (RE)</t>
+          <t>Plaza Colonia</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Deportivo Merlo</t>
+          <t>Huracan del Paso</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.14</v>
+        <v>1.84</v>
       </c>
       <c r="G18" t="n">
-        <v>2.46</v>
+        <v>1.98</v>
       </c>
       <c r="H18" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="I18" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="J18" t="n">
-        <v>2.74</v>
+        <v>3.3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="L18" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="M18" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P18" t="n">
         <v>1.68</v>
       </c>
-      <c r="P18" t="n">
-        <v>1.39</v>
-      </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.36</v>
+        <v>2.02</v>
       </c>
       <c r="U18" t="n">
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="V18" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W18" t="n">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="X18" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="AA18" t="n">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AC18" t="n">
         <v>8.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AF18" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AG18" t="n">
-        <v>950</v>
+        <v>11</v>
       </c>
       <c r="AH18" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="AI18" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AJ18" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="AK18" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="AL18" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>50</v>
+        <v>18.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="AP18" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.05</v>
+        <v>6.2</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.9</v>
+        <v>3.65</v>
       </c>
       <c r="AU18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ18" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5166,246 +5166,246 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>Talleres (RE)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Deportivo Merlo</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="G19" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="I19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU19" t="n">
         <v>4.2</v>
       </c>
-      <c r="J19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="X19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>27</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>13</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>28</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>70</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>7</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>18</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>13</v>
+        <v>1.86</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>15</v>
+        <v>1.9</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>13.5</v>
+        <v>1.9</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,251 +5415,251 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Operario PR</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="G20" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H20" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J20" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="K20" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="L20" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="M20" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="N20" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="O20" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="P20" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.12</v>
+        <v>2.72</v>
       </c>
       <c r="R20" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="S20" t="n">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="T20" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="U20" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="V20" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W20" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF20" t="n">
         <v>13</v>
       </c>
-      <c r="Y20" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AG20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AI20" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL20" t="n">
         <v>65</v>
       </c>
-      <c r="AJ20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>55</v>
-      </c>
       <c r="AM20" t="n">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="AN20" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AO20" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AP20" t="n">
-        <v>3.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ20" t="n">
         <v>10</v>
       </c>
       <c r="AR20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.1</v>
+        <v>75</v>
       </c>
       <c r="AT20" t="n">
         <v>6.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX20" t="n">
         <v>11.5</v>
       </c>
-      <c r="AW20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX20" t="n">
+      <c r="AY20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>29</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BJ20" t="n">
         <v>11</v>
       </c>
-      <c r="AY20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC20" t="n">
+      <c r="BK20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>17</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP20" t="n">
         <v>21</v>
       </c>
-      <c r="BD20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>19</v>
-      </c>
       <c r="BQ20" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BT20" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BV20" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-05 00:53:58</t>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,244 +5669,498 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>23:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atletico Ottawa</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="G21" t="n">
-        <v>2.82</v>
+        <v>2.44</v>
       </c>
       <c r="H21" t="n">
-        <v>2.5</v>
+        <v>3.35</v>
       </c>
       <c r="I21" t="n">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="J21" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="K21" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="L21" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="M21" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="N21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S21" t="n">
         <v>4.1</v>
       </c>
-      <c r="O21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.88</v>
-      </c>
       <c r="T21" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="U21" t="n">
-        <v>2.28</v>
+        <v>1.94</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="X21" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH21" t="n">
         <v>22</v>
       </c>
-      <c r="Y21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AI21" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>38</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>40</v>
       </c>
       <c r="AK21" t="n">
         <v>32</v>
       </c>
       <c r="AL21" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AM21" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-06-05 03:04:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>23:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Vancouver FC</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Atletico Ottawa</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X22" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM22" t="n">
         <v>80</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AN22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV22" t="n">
         <v>20</v>
       </c>
-      <c r="AO21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA21" t="n">
+      <c r="BW22" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BX22" t="n">
         <v>30</v>
       </c>
-      <c r="BC21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE21" t="n">
+      <c r="BY22" t="n">
         <v>7.4</v>
       </c>
-      <c r="BF21" t="n">
-        <v>16</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>15</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>9</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>20</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>30</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BT21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV21" t="n">
-        <v>21</v>
-      </c>
-      <c r="BW21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BX21" t="n">
-        <v>32</v>
-      </c>
-      <c r="BY21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BZ21" t="n">
+      <c r="BZ22" t="n">
         <v>23</v>
       </c>
-      <c r="CA21" t="n">
+      <c r="CA22" t="n">
         <v>7</v>
       </c>
-      <c r="CB21" t="inlineStr">
-        <is>
-          <t>2026-06-05 00:53:58</t>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-06-05 03:04:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB22"/>
+  <dimension ref="A1:CB24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,7 +860,7 @@
         <v>1.9</v>
       </c>
       <c r="G2" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H2" t="n">
         <v>4.6</v>
@@ -869,31 +869,31 @@
         <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P2" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S2" t="n">
         <v>3.8</v>
@@ -902,22 +902,22 @@
         <v>1.87</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V2" t="n">
         <v>1.26</v>
       </c>
       <c r="W2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA2" t="n">
         <v>180</v>
@@ -926,88 +926,88 @@
         <v>8.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
         <v>19</v>
       </c>
       <c r="AE2" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG2" t="n">
         <v>10</v>
       </c>
       <c r="AH2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK2" t="n">
         <v>21</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>22</v>
       </c>
       <c r="AL2" t="n">
         <v>40</v>
       </c>
       <c r="AM2" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="AN2" t="n">
         <v>15.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP2" t="n">
         <v>12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.4</v>
+        <v>27</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.199999999999999</v>
+        <v>55</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU2" t="n">
         <v>7.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW2" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="AX2" t="n">
         <v>10</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB2" t="n">
         <v>17.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>25</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>19</v>
       </c>
       <c r="BC2" t="n">
         <v>18</v>
       </c>
       <c r="BD2" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="BE2" t="n">
         <v>95</v>
@@ -1016,13 +1016,13 @@
         <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BH2" t="n">
         <v>3.3</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BJ2" t="n">
         <v>10.5</v>
@@ -1040,7 +1040,7 @@
         <v>4.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP2" t="n">
         <v>14.5</v>
@@ -1049,10 +1049,10 @@
         <v>7.2</v>
       </c>
       <c r="BR2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS2" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BT2" t="n">
         <v>7.8</v>
@@ -1067,10 +1067,10 @@
         <v>10.5</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY2" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -1111,178 +1111,178 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="G3" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="H3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="S3" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="T3" t="n">
         <v>1.88</v>
       </c>
       <c r="U3" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="V3" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W3" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y3" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD3" t="n">
         <v>950</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>250</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>42</v>
       </c>
       <c r="AE3" t="n">
         <v>170</v>
       </c>
       <c r="AF3" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AH3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR3" t="n">
         <v>27</v>
       </c>
-      <c r="AI3" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>280</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>6</v>
-      </c>
       <c r="AS3" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.3</v>
+        <v>21</v>
       </c>
       <c r="AW3" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="AX3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA3" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>5.8</v>
       </c>
       <c r="BB3" t="n">
         <v>12</v>
       </c>
       <c r="BC3" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.8</v>
+        <v>17.5</v>
       </c>
       <c r="BE3" t="n">
         <v>100</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1294,37 +1294,37 @@
         <v>4.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BQ3" t="n">
         <v>6.2</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT3" t="n">
         <v>10.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J4" t="n">
         <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.47</v>
@@ -1395,106 +1395,106 @@
         <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U4" t="n">
         <v>1.96</v>
       </c>
       <c r="V4" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA4" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AC4" t="n">
         <v>8.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AE4" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="AF4" t="n">
         <v>11</v>
       </c>
       <c r="AG4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH4" t="n">
         <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ4" t="n">
         <v>21</v>
       </c>
       <c r="AK4" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="AM4" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AN4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO4" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AP4" t="n">
         <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AS4" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU4" t="n">
         <v>7.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AX4" t="n">
         <v>9.199999999999999</v>
@@ -1503,7 +1503,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA4" t="n">
         <v>30</v>
@@ -1515,28 +1515,28 @@
         <v>18</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="BE4" t="n">
         <v>100</v>
       </c>
       <c r="BF4" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>36</v>
+        <v>13.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ4" t="n">
         <v>11</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1554,31 +1554,31 @@
         <v>13.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR4" t="n">
         <v>32</v>
       </c>
       <c r="BS4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV4" t="n">
         <v>46</v>
       </c>
       <c r="BW4" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G5" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H5" t="n">
         <v>2.5</v>
       </c>
       <c r="I5" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="J5" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="K5" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L5" t="n">
         <v>1.57</v>
@@ -1643,19 +1643,19 @@
         <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O5" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P5" t="n">
         <v>1.51</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S5" t="n">
         <v>5.6</v>
@@ -1664,13 +1664,13 @@
         <v>2.08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V5" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X5" t="n">
         <v>8.6</v>
@@ -1679,37 +1679,37 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AA5" t="n">
         <v>44</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
         <v>40</v>
       </c>
       <c r="AF5" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AG5" t="n">
         <v>16</v>
       </c>
       <c r="AH5" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AI5" t="n">
         <v>190</v>
       </c>
       <c r="AJ5" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AK5" t="n">
         <v>60</v>
@@ -1721,13 +1721,13 @@
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AO5" t="n">
         <v>46</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AQ5" t="n">
         <v>6.6</v>
@@ -1736,10 +1736,10 @@
         <v>13</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.2</v>
+        <v>27</v>
       </c>
       <c r="AT5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU5" t="n">
         <v>6</v>
@@ -1748,101 +1748,101 @@
         <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.2</v>
+        <v>24</v>
       </c>
       <c r="AX5" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AY5" t="n">
         <v>13</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE5" t="n">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="BJ5" t="n">
         <v>12</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>10</v>
+        <v>170</v>
       </c>
       <c r="BN5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BP5" t="n">
         <v>34</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR5" t="n">
         <v>60</v>
       </c>
       <c r="BS5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT5" t="n">
         <v>5.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="BV5" t="n">
         <v>25</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.800000000000001</v>
+        <v>50</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA5" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -1873,85 +1873,85 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="G6" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="H6" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="P6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.06</v>
       </c>
-      <c r="Q6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.08</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W6" t="n">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="X6" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Y6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Z6" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AA6" t="n">
         <v>700</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE6" t="n">
-        <v>470</v>
+        <v>230</v>
       </c>
       <c r="AF6" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG6" t="n">
         <v>10.5</v>
@@ -1960,91 +1960,91 @@
         <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="AJ6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK6" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM6" t="n">
         <v>580</v>
       </c>
       <c r="AN6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU6" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AO6" t="n">
-        <v>160</v>
-      </c>
-      <c r="AP6" t="n">
+      <c r="AV6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF6" t="n">
         <v>6.4</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BG6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="BJ6" t="n">
         <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2056,47 +2056,47 @@
         <v>4.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BR6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS6" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BT6" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BU6" t="n">
         <v>5</v>
       </c>
       <c r="BV6" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BX6" t="n">
         <v>55</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="CA6" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -2118,187 +2118,187 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Paradou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Setif</t>
+          <t>MB Rouissat</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="G7" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="I7" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M7" t="n">
         <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="P7" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="R7" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="S7" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="V7" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.52</v>
+        <v>1.91</v>
       </c>
       <c r="X7" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="n">
+        <v>85</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK7" t="n">
         <v>25</v>
       </c>
-      <c r="AA7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC7" t="n">
+      <c r="AL7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY7" t="n">
         <v>9</v>
       </c>
-      <c r="AD7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG7" t="n">
+      <c r="AZ7" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF7" t="n">
         <v>15</v>
       </c>
-      <c r="AH7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>4</v>
-      </c>
       <c r="BG7" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="BH7" t="n">
         <v>3.2</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK7" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2307,34 +2307,34 @@
         <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS7" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
@@ -2346,18 +2346,18 @@
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FBK Karlstad</t>
+          <t>Paradou</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IF Karlstad</t>
+          <t>ES Setif</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>2.66</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="H8" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X8" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>300</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>95</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BB8" t="n">
         <v>2.58</v>
       </c>
-      <c r="I8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X8" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC8" t="n">
+      <c r="BC8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH8" t="n">
+      <c r="BN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
         <v>16</v>
       </c>
-      <c r="AI8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>85</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>16</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>16</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>9</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>20</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BR8" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT8" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BV8" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.04</v>
+        <v>18</v>
       </c>
       <c r="BX8" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.04</v>
+        <v>32</v>
       </c>
       <c r="BZ8" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,189 +2621,189 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>FBK Karlstad</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>IF Karlstad</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.61</v>
+        <v>2.64</v>
       </c>
       <c r="G9" t="n">
-        <v>1.72</v>
+        <v>2.92</v>
       </c>
       <c r="H9" t="n">
-        <v>5.8</v>
+        <v>2.6</v>
       </c>
       <c r="I9" t="n">
-        <v>990</v>
+        <v>2.9</v>
       </c>
       <c r="J9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S9" t="n">
         <v>3</v>
       </c>
-      <c r="K9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.5</v>
-      </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>2.32</v>
       </c>
       <c r="V9" t="n">
-        <v>1.1</v>
+        <v>1.53</v>
       </c>
       <c r="W9" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="X9" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="Y9" t="n">
-        <v>34</v>
+        <v>13.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AA9" t="n">
-        <v>700</v>
+        <v>85</v>
       </c>
       <c r="AB9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE9" t="n">
         <v>12</v>
       </c>
-      <c r="AD9" t="n">
-        <v>70</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>680</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>280</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>700</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>700</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>2.14</v>
-      </c>
       <c r="BF9" t="n">
-        <v>5.4</v>
+        <v>18</v>
       </c>
       <c r="BG9" t="n">
-        <v>32</v>
+        <v>17.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK9" t="n">
         <v>1.04</v>
@@ -2815,57 +2815,57 @@
         <v>1.04</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ9" t="n">
         <v>1.04</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS9" t="n">
         <v>1.04</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW9" t="n">
         <v>1.04</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY9" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA9" t="n">
         <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,251 +2875,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Reynir Sandgeroi</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Augnablik</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.26</v>
+        <v>1.45</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6</v>
+        <v>1.55</v>
       </c>
       <c r="H10" t="n">
-        <v>2.6</v>
+        <v>9.4</v>
       </c>
       <c r="I10" t="n">
-        <v>2.96</v>
+        <v>12</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K10" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="M10" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>7.4</v>
+        <v>3.15</v>
       </c>
       <c r="O10" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>3.25</v>
+        <v>1.71</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.35</v>
+        <v>2.16</v>
       </c>
       <c r="R10" t="n">
-        <v>1.94</v>
+        <v>1.26</v>
       </c>
       <c r="S10" t="n">
-        <v>1.87</v>
+        <v>3.85</v>
       </c>
       <c r="T10" t="n">
-        <v>1.38</v>
+        <v>2.2</v>
       </c>
       <c r="U10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X10" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BO10" t="n">
         <v>3</v>
       </c>
-      <c r="V10" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="X10" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>950</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>500</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>500</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.04</v>
+        <v>20</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.04</v>
+        <v>21</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.04</v>
+        <v>21</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.04</v>
+        <v>17</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,60 +3129,60 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Kormakur/Hvot</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IF Magni</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>11</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1.9</v>
       </c>
-      <c r="H11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K11" t="n">
-        <v>25</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.41</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.78</v>
+        <v>1.17</v>
       </c>
       <c r="S11" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -3191,118 +3191,118 @@
         <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="X11" t="n">
         <v>950</v>
       </c>
       <c r="Y11" t="n">
-        <v>950</v>
+        <v>18</v>
       </c>
       <c r="Z11" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AA11" t="n">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="AB11" t="n">
         <v>950</v>
       </c>
       <c r="AC11" t="n">
-        <v>950</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD11" t="n">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="AE11" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AF11" t="n">
-        <v>500</v>
+        <v>8.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="AH11" t="n">
-        <v>950</v>
+        <v>40</v>
       </c>
       <c r="AI11" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AJ11" t="n">
-        <v>900</v>
+        <v>18</v>
       </c>
       <c r="AK11" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AL11" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AM11" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="AN11" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO11" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.24</v>
+        <v>3.35</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.22</v>
+        <v>14.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.23</v>
+        <v>32</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.23</v>
+        <v>4.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.21</v>
+        <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.2</v>
+        <v>4.9</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.22</v>
+        <v>8</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.23</v>
+        <v>5.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.2</v>
+        <v>6.2</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.24</v>
+        <v>28</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.23</v>
+        <v>4.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.23</v>
+        <v>3.7</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.22</v>
+        <v>16</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.23</v>
+        <v>23</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.24</v>
+        <v>4.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.21</v>
+        <v>14</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.55</v>
+        <v>4.6</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,246 +3388,246 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Reynir Sandgeroi</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Augnablik</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="G12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N12" t="n">
+        <v>8</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="R12" t="n">
         <v>2</v>
       </c>
-      <c r="H12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="I12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="S12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="X12" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BF12" t="n">
         <v>4</v>
       </c>
-      <c r="K12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N12" t="n">
-        <v>6</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X12" t="n">
-        <v>34</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>470</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BG12" t="n">
-        <v>5.1</v>
+        <v>2.5</v>
       </c>
       <c r="BH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO12" t="n">
         <v>4.8</v>
       </c>
-      <c r="BI12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>4</v>
-      </c>
       <c r="BP12" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
         <v>5.9</v>
       </c>
       <c r="BR12" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>7.2</v>
+        <v>2.26</v>
       </c>
       <c r="BT12" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="BV12" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.8</v>
+        <v>2.18</v>
       </c>
       <c r="BX12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>8.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="BZ12" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,239 +3642,239 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Kormakur/Hvot</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Leiknir R</t>
+          <t>IF Magni</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.76</v>
+        <v>1.71</v>
       </c>
       <c r="G13" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="H13" t="n">
-        <v>2.42</v>
+        <v>3.85</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="J13" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="K13" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="M13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X13" t="n">
+        <v>38</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP13" t="n">
         <v>5.7</v>
       </c>
-      <c r="O13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X13" t="n">
-        <v>26</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>18</v>
-      </c>
       <c r="AQ13" t="n">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>15</v>
+        <v>5.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>16</v>
+        <v>6.2</v>
       </c>
       <c r="AT13" t="n">
         <v>12</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV13" t="n">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>17</v>
+        <v>5.8</v>
       </c>
       <c r="AX13" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG13" t="n">
         <v>21</v>
       </c>
-      <c r="BB13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>16</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>10</v>
-      </c>
       <c r="BH13" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="BJ13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BL13" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BN13" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="BP13" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="BQ13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW13" t="n">
         <v>6.6</v>
       </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>7</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>17</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BX13" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BY13" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BZ13" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="CA13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
@@ -3896,124 +3896,124 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Leiknir R</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="G14" t="n">
-        <v>3.05</v>
+        <v>2.68</v>
       </c>
       <c r="H14" t="n">
-        <v>2.26</v>
+        <v>2.62</v>
       </c>
       <c r="I14" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S14" t="n">
         <v>2.38</v>
       </c>
-      <c r="J14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N14" t="n">
-        <v>8</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.94</v>
-      </c>
       <c r="T14" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="U14" t="n">
-        <v>3.15</v>
+        <v>2.68</v>
       </c>
       <c r="V14" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="X14" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Y14" t="n">
-        <v>27</v>
+        <v>18.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AA14" t="n">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="AB14" t="n">
-        <v>29</v>
+        <v>17.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AE14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK14" t="n">
         <v>24</v>
       </c>
-      <c r="AF14" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>26</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>27</v>
-      </c>
       <c r="AL14" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AM14" t="n">
-        <v>38</v>
+        <v>200</v>
       </c>
       <c r="AN14" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AP14" t="n">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="AQ14" t="n">
         <v>15.5</v>
@@ -4022,120 +4022,120 @@
         <v>20</v>
       </c>
       <c r="AS14" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AT14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG14" t="n">
         <v>10</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="BH14" t="n">
         <v>4.6</v>
       </c>
-      <c r="AX14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>19</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>16</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BI14" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="BJ14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK14" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BL14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BN14" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="BP14" t="n">
         <v>18.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR14" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BS14" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT14" t="n">
         <v>6.4</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV14" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BX14" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="BY14" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BZ14" t="n">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="CA14" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,36 +4145,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Hviti Riddarinn</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Haukar</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2</v>
+        <v>2.98</v>
       </c>
       <c r="H15" t="n">
-        <v>1.51</v>
+        <v>2.32</v>
       </c>
       <c r="I15" t="n">
-        <v>1.62</v>
+        <v>2.44</v>
       </c>
       <c r="J15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="L15" t="n">
         <v>1.21</v>
@@ -4183,213 +4183,213 @@
         <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="O15" t="n">
         <v>1.12</v>
       </c>
       <c r="P15" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="R15" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="S15" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="T15" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="U15" t="n">
-        <v>2.58</v>
+        <v>3.2</v>
       </c>
       <c r="V15" t="n">
-        <v>2.6</v>
+        <v>1.69</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="X15" t="n">
-        <v>950</v>
+        <v>46</v>
       </c>
       <c r="Y15" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>46</v>
       </c>
-      <c r="Z15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>950</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>180</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>240</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>150</v>
-      </c>
       <c r="AK15" t="n">
-        <v>160</v>
+        <v>26</v>
       </c>
       <c r="AL15" t="n">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="AM15" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AN15" t="n">
-        <v>44</v>
+        <v>13.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="AP15" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>6</v>
+        <v>19.5</v>
       </c>
       <c r="AR15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>16</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH15" t="n">
         <v>5.7</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>5.8</v>
       </c>
       <c r="BI15" t="n">
         <v>4.3</v>
       </c>
       <c r="BJ15" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK15" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BL15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BM15" t="n">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="BN15" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO15" t="n">
         <v>5.2</v>
       </c>
       <c r="BP15" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR15" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS15" t="n">
-        <v>4.1</v>
+        <v>7.8</v>
       </c>
       <c r="BT15" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BU15" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="BV15" t="n">
-        <v>9.4</v>
+        <v>15.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BX15" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BY15" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BZ15" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="CA15" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,251 +4399,251 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CA Ituzaingo</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Real Pilar FC</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.85</v>
+        <v>1.91</v>
       </c>
       <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
         <v>4.6</v>
       </c>
-      <c r="H16" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3.4</v>
-      </c>
       <c r="L16" t="n">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="M16" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>2.68</v>
+        <v>6.2</v>
       </c>
       <c r="O16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T16" t="n">
         <v>1.5</v>
       </c>
-      <c r="P16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S16" t="n">
-        <v>5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.06</v>
-      </c>
       <c r="U16" t="n">
-        <v>1.75</v>
+        <v>2.66</v>
       </c>
       <c r="V16" t="n">
-        <v>1.72</v>
+        <v>1.33</v>
       </c>
       <c r="W16" t="n">
-        <v>1.29</v>
+        <v>1.98</v>
       </c>
       <c r="X16" t="n">
-        <v>9.4</v>
+        <v>32</v>
       </c>
       <c r="Y16" t="n">
-        <v>7.6</v>
+        <v>24</v>
       </c>
       <c r="Z16" t="n">
-        <v>13.5</v>
+        <v>36</v>
       </c>
       <c r="AA16" t="n">
-        <v>34</v>
+        <v>470</v>
       </c>
       <c r="AB16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG16" t="n">
         <v>12</v>
       </c>
-      <c r="AC16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF16" t="n">
+      <c r="AH16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL16" t="n">
         <v>32</v>
       </c>
-      <c r="AG16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>500</v>
-      </c>
       <c r="AM16" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AN16" t="n">
-        <v>500</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO16" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AP16" t="n">
-        <v>4.4</v>
+        <v>13</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.6</v>
+        <v>16</v>
       </c>
       <c r="AS16" t="n">
         <v>6.8</v>
       </c>
       <c r="AT16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG16" t="n">
         <v>5.8</v>
       </c>
-      <c r="AU16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW16" t="n">
+      <c r="BH16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>21</v>
+      </c>
+      <c r="BS16" t="n">
         <v>6.8</v>
       </c>
-      <c r="AX16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA16" t="n">
+      <c r="BT16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW16" t="n">
         <v>7.4</v>
       </c>
-      <c r="BB16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC16" t="n">
+      <c r="BX16" t="n">
+        <v>30</v>
+      </c>
+      <c r="BY16" t="n">
         <v>7.6</v>
       </c>
-      <c r="BD16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>11</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>6</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>19</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BZ16" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,251 +4653,251 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Wanderers (Uru)</t>
+          <t>Hviti Riddarinn</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>Haukar</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.32</v>
+        <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>2.44</v>
+        <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>3.45</v>
+        <v>1.52</v>
       </c>
       <c r="I17" t="n">
-        <v>3.85</v>
+        <v>1.58</v>
       </c>
       <c r="J17" t="n">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.4</v>
+        <v>5.9</v>
       </c>
       <c r="L17" t="n">
-        <v>1.54</v>
+        <v>1.21</v>
       </c>
       <c r="M17" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>2.86</v>
+        <v>8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.49</v>
+        <v>1.12</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6</v>
+        <v>3.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.52</v>
+        <v>1.36</v>
       </c>
       <c r="R17" t="n">
-        <v>1.21</v>
+        <v>1.97</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>1.91</v>
       </c>
       <c r="T17" t="n">
-        <v>2.02</v>
+        <v>1.51</v>
       </c>
       <c r="U17" t="n">
-        <v>1.82</v>
+        <v>2.62</v>
       </c>
       <c r="V17" t="n">
-        <v>1.37</v>
+        <v>2.68</v>
       </c>
       <c r="W17" t="n">
-        <v>1.69</v>
+        <v>1.2</v>
       </c>
       <c r="X17" t="n">
-        <v>9.800000000000001</v>
+        <v>950</v>
       </c>
       <c r="Y17" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>180</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>240</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>160</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR17" t="n">
         <v>11</v>
       </c>
-      <c r="Z17" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>500</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>90</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>70</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR17" t="n">
+      <c r="AS17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU17" t="n">
         <v>10.5</v>
       </c>
-      <c r="AS17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AV17" t="n">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AZ17" t="n">
         <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>28</v>
+        <v>16.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>14.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC17" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE17" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BJ17" t="n">
         <v>9.4</v>
       </c>
-      <c r="BF17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BK17" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>11</v>
+        <v>4.4</v>
       </c>
       <c r="BN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BT17" t="n">
         <v>5.2</v>
       </c>
-      <c r="BO17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS17" t="n">
+      <c r="BU17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BZ17" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BT17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA17" t="n">
-        <v>9.4</v>
+        <v>4.9</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,251 +4907,251 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Plaza Colonia</t>
+          <t>CA Ituzaingo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Huracan del Paso</t>
+          <t>Real Pilar FC</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.84</v>
+        <v>3.85</v>
       </c>
       <c r="G18" t="n">
-        <v>1.98</v>
+        <v>4.4</v>
       </c>
       <c r="H18" t="n">
-        <v>4.8</v>
+        <v>2.22</v>
       </c>
       <c r="I18" t="n">
-        <v>5.8</v>
+        <v>2.42</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="K18" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="L18" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="M18" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="O18" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="P18" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="T18" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U18" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="V18" t="n">
-        <v>1.21</v>
+        <v>1.71</v>
       </c>
       <c r="W18" t="n">
-        <v>2.02</v>
+        <v>1.29</v>
       </c>
       <c r="X18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB18" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="AC18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>900</v>
       </c>
-      <c r="AB18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>700</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>23</v>
-      </c>
       <c r="AK18" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AL18" t="n">
         <v>500</v>
       </c>
       <c r="AM18" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN18" t="n">
-        <v>18.5</v>
+        <v>500</v>
       </c>
       <c r="AO18" t="n">
-        <v>700</v>
+        <v>34</v>
       </c>
       <c r="AP18" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="AR18" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AS18" t="n">
         <v>7.2</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.65</v>
+        <v>9.6</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AW18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>19</v>
+      </c>
+      <c r="BW18" t="n">
         <v>7</v>
       </c>
-      <c r="AX18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT18" t="n">
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BU18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,251 +5161,251 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Talleres (RE)</t>
+          <t>Wanderers (Uru)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Deportivo Merlo</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="G19" t="n">
-        <v>3.05</v>
+        <v>2.44</v>
       </c>
       <c r="H19" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="I19" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="J19" t="n">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="K19" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="L19" t="n">
-        <v>1.79</v>
+        <v>1.56</v>
       </c>
       <c r="M19" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="N19" t="n">
-        <v>2.06</v>
+        <v>2.8</v>
       </c>
       <c r="O19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
         <v>1.8</v>
       </c>
-      <c r="P19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V19" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y19" t="n">
         <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>380</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>22</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA19" t="n">
         <v>9</v>
       </c>
-      <c r="AC19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BX19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BZ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA19" t="n">
-        <v>1.9</v>
-      </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,251 +5415,251 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>Plaza Colonia</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Huracan del Paso</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.36</v>
+        <v>1.88</v>
       </c>
       <c r="G20" t="n">
-        <v>2.46</v>
+        <v>1.97</v>
       </c>
       <c r="H20" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="I20" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="J20" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="L20" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="M20" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="N20" t="n">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="P20" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.72</v>
+        <v>2.28</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="U20" t="n">
         <v>1.81</v>
       </c>
       <c r="V20" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="W20" t="n">
-        <v>1.69</v>
+        <v>2.02</v>
       </c>
       <c r="X20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>700</v>
+      </c>
+      <c r="AP20" t="n">
         <v>8.6</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AQ20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BJ20" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z20" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>75</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY20" t="n">
+      <c r="BK20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
         <v>10.5</v>
       </c>
-      <c r="AZ20" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>28</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>29</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>12</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>17</v>
-      </c>
       <c r="BN20" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="BP20" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="BQ20" t="n">
-        <v>9.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="BT20" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="BZ20" t="n">
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>13.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,498 +5669,1006 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Talleres (RE)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportivo Merlo</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.28</v>
+        <v>2.56</v>
       </c>
       <c r="G21" t="n">
-        <v>2.44</v>
+        <v>3.05</v>
       </c>
       <c r="H21" t="n">
         <v>3.35</v>
       </c>
       <c r="I21" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="J21" t="n">
-        <v>3.2</v>
+        <v>2.46</v>
       </c>
       <c r="K21" t="n">
-        <v>3.65</v>
+        <v>2.76</v>
       </c>
       <c r="L21" t="n">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="M21" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2</v>
+        <v>2.04</v>
       </c>
       <c r="O21" t="n">
-        <v>1.39</v>
+        <v>1.81</v>
       </c>
       <c r="P21" t="n">
-        <v>1.73</v>
+        <v>1.32</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="S21" t="n">
-        <v>4.1</v>
+        <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>1.85</v>
+        <v>1.11</v>
       </c>
       <c r="U21" t="n">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="V21" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W21" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="X21" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.78</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN21" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BP21" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT21" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-05 03:04:35</t>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Operario PR</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>70</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>29</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>65</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>17</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>22</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>13</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>14</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:15:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>San Marcos</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X23" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:15:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Canadian Premier League</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>23:00:00</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Vancouver FC</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Atletico Ottawa</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K22" t="n">
+      <c r="F24" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N24" t="n">
         <v>4.3</v>
       </c>
-      <c r="L22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N22" t="n">
+      <c r="O24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X24" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO24" t="n">
         <v>4.3</v>
       </c>
-      <c r="O22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X22" t="n">
+      <c r="BP24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV24" t="n">
         <v>22</v>
       </c>
-      <c r="Y22" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK22" t="n">
+      <c r="BW24" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX24" t="n">
         <v>32</v>
       </c>
-      <c r="AL22" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO22" t="n">
+      <c r="BY24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BZ24" t="n">
         <v>22</v>
       </c>
-      <c r="AP22" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>9</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>21</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>20</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>30</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>23</v>
-      </c>
-      <c r="CA22" t="n">
+      <c r="CA24" t="n">
         <v>7</v>
       </c>
-      <c r="CB22" t="inlineStr">
-        <is>
-          <t>2026-06-05 03:04:35</t>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:15:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB24"/>
+  <dimension ref="A1:CB25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,154 +857,154 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="G2" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="H2" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="I2" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S2" t="n">
         <v>3.55</v>
       </c>
-      <c r="O2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P2" t="n">
+      <c r="T2" t="n">
         <v>1.89</v>
       </c>
-      <c r="Q2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.87</v>
-      </c>
       <c r="U2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V2" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="W2" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="X2" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL2" t="n">
         <v>38</v>
       </c>
-      <c r="AA2" t="n">
-        <v>180</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI2" t="n">
+      <c r="AM2" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW2" t="n">
         <v>65</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>50</v>
-      </c>
       <c r="AX2" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AY2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BB2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BC2" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BD2" t="n">
         <v>32</v>
@@ -1013,64 +1013,64 @@
         <v>95</v>
       </c>
       <c r="BF2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BG2" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BJ2" t="n">
         <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM2" t="n">
         <v>120</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BO2" t="n">
         <v>4</v>
       </c>
       <c r="BP2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS2" t="n">
         <v>14.5</v>
       </c>
-      <c r="BQ2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>30</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BT2" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU2" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BV2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BW2" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX2" t="n">
         <v>60</v>
       </c>
       <c r="BY2" t="n">
-        <v>55</v>
+        <v>12.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G3" t="n">
         <v>1.52</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.53</v>
       </c>
       <c r="H3" t="n">
         <v>7</v>
@@ -1126,205 +1126,205 @@
         <v>4.9</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="R3" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="S3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W3" t="n">
         <v>2.92</v>
       </c>
-      <c r="T3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.88</v>
-      </c>
       <c r="X3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y3" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="Z3" t="n">
         <v>970</v>
       </c>
       <c r="AA3" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
         <v>950</v>
       </c>
       <c r="AE3" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AF3" t="n">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="AG3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>150</v>
+        <v>960</v>
       </c>
       <c r="AJ3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AK3" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM3" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AO3" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AP3" t="n">
         <v>19.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AR3" t="n">
-        <v>27</v>
+        <v>12.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW3" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB3" t="n">
         <v>12</v>
       </c>
       <c r="BC3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD3" t="n">
-        <v>17.5</v>
+        <v>11</v>
       </c>
       <c r="BE3" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BG3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ3" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BP3" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.2</v>
+        <v>1.05</v>
       </c>
       <c r="BR3" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BT3" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="G4" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.47</v>
@@ -1392,40 +1392,40 @@
         <v>3.45</v>
       </c>
       <c r="O4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P4" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R4" t="n">
         <v>1.31</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V4" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W4" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="X4" t="n">
         <v>12.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z4" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AA4" t="n">
         <v>130</v>
@@ -1434,118 +1434,118 @@
         <v>8</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="AF4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG4" t="n">
         <v>10</v>
       </c>
       <c r="AH4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>22</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>21</v>
       </c>
       <c r="AK4" t="n">
         <v>22</v>
       </c>
       <c r="AL4" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="AM4" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AN4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AO4" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AP4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU4" t="n">
         <v>7.2</v>
       </c>
-      <c r="AU4" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AV4" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="n">
         <v>18.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="BB4" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>11.5</v>
+        <v>36</v>
       </c>
       <c r="BE4" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BF4" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BG4" t="n">
-        <v>13.5</v>
+        <v>60</v>
       </c>
       <c r="BH4" t="n">
         <v>3.15</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BJ4" t="n">
         <v>11</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM4" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO4" t="n">
         <v>3.9</v>
@@ -1554,31 +1554,31 @@
         <v>13.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR4" t="n">
         <v>32</v>
       </c>
       <c r="BS4" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU4" t="n">
         <v>5.5</v>
       </c>
       <c r="BV4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BW4" t="n">
         <v>12.5</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -1619,73 +1619,73 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G5" t="n">
         <v>3.7</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="I5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q5" t="n">
         <v>2.84</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.64</v>
       </c>
       <c r="R5" t="n">
         <v>1.19</v>
       </c>
       <c r="S5" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="V5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W5" t="n">
         <v>1.37</v>
       </c>
       <c r="X5" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="Y5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB5" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>9.6</v>
       </c>
       <c r="AC5" t="n">
         <v>7.2</v>
@@ -1694,16 +1694,16 @@
         <v>14</v>
       </c>
       <c r="AE5" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AF5" t="n">
         <v>23</v>
       </c>
       <c r="AG5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI5" t="n">
         <v>190</v>
@@ -1721,13 +1721,13 @@
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>46</v>
+        <v>600</v>
       </c>
       <c r="AP5" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AQ5" t="n">
         <v>6.6</v>
@@ -1739,13 +1739,13 @@
         <v>27</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AU5" t="n">
         <v>6</v>
       </c>
       <c r="AV5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW5" t="n">
         <v>24</v>
@@ -1754,43 +1754,43 @@
         <v>18</v>
       </c>
       <c r="AY5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ5" t="n">
         <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE5" t="n">
         <v>130</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1799,50 +1799,50 @@
         <v>170</v>
       </c>
       <c r="BN5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BP5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BS5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT5" t="n">
         <v>5.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BV5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BW5" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY5" t="n">
         <v>50</v>
       </c>
       <c r="BZ5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -1873,230 +1873,230 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="G6" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="J6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N6" t="n">
         <v>4.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P6" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="U6" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="V6" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="W6" t="n">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="X6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Y6" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Z6" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AA6" t="n">
         <v>700</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AE6" t="n">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="AF6" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AI6" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="AJ6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK6" t="n">
         <v>16</v>
       </c>
-      <c r="AK6" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AL6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM6" t="n">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN6" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>20</v>
       </c>
-      <c r="AR6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BA6" t="n">
-        <v>29</v>
+        <v>8.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BC6" t="n">
         <v>13.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="BE6" t="n">
-        <v>28</v>
+        <v>8.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="BG6" t="n">
-        <v>9.4</v>
+        <v>15</v>
       </c>
       <c r="BH6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN6" t="n">
         <v>4.2</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>4.5</v>
       </c>
       <c r="BO6" t="n">
         <v>3.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BR6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS6" t="n">
         <v>6.8</v>
       </c>
       <c r="BT6" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BX6" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ6" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -2127,58 +2127,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H7" t="n">
         <v>4.2</v>
       </c>
       <c r="I7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K7" t="n">
         <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M7" t="n">
         <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O7" t="n">
         <v>1.39</v>
       </c>
       <c r="P7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="R7" t="n">
         <v>1.27</v>
       </c>
       <c r="S7" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.92</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.91</v>
       </c>
       <c r="X7" t="n">
         <v>12.5</v>
@@ -2244,10 +2244,10 @@
         <v>14.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU7" t="n">
         <v>6.8</v>
@@ -2259,16 +2259,16 @@
         <v>6.6</v>
       </c>
       <c r="AX7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY7" t="n">
         <v>9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB7" t="n">
         <v>20</v>
@@ -2277,7 +2277,7 @@
         <v>19.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE7" t="n">
         <v>7</v>
@@ -2298,13 +2298,13 @@
         <v>11</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN7" t="n">
         <v>4.7</v>
@@ -2316,13 +2316,13 @@
         <v>15.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BR7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT7" t="n">
         <v>8</v>
@@ -2334,23 +2334,23 @@
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -2384,103 +2384,103 @@
         <v>2.66</v>
       </c>
       <c r="G8" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="H8" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="I8" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J8" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V8" t="n">
         <v>1.46</v>
       </c>
-      <c r="M8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.42</v>
-      </c>
       <c r="W8" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="X8" t="n">
         <v>23</v>
       </c>
       <c r="Y8" t="n">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="Z8" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AA8" t="n">
         <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>42</v>
+        <v>8.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AE8" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AF8" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AG8" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AH8" t="n">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="AI8" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AJ8" t="n">
         <v>900</v>
       </c>
       <c r="AK8" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AL8" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
         <v>600</v>
@@ -2489,79 +2489,79 @@
         <v>600</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.82</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.5</v>
+        <v>6.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.9</v>
+        <v>6.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.5</v>
+        <v>7.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.72</v>
+        <v>6</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.35</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY8" t="n">
-        <v>2.84</v>
+        <v>6.8</v>
       </c>
       <c r="AZ8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH8" t="n">
         <v>3.45</v>
       </c>
-      <c r="BA8" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>3.2</v>
-      </c>
       <c r="BI8" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO8" t="n">
         <v>4.2</v>
@@ -2570,41 +2570,41 @@
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>16</v>
+        <v>6.2</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>18</v>
+        <v>6.4</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>32</v>
+        <v>7.2</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -2635,130 +2635,130 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.64</v>
+        <v>3.15</v>
       </c>
       <c r="G9" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9</v>
+        <v>2.54</v>
       </c>
       <c r="J9" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M9" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="P9" t="n">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="T9" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="U9" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="V9" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="W9" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="X9" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Y9" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AB9" t="n">
         <v>13.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
         <v>28</v>
       </c>
       <c r="AF9" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AG9" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AH9" t="n">
         <v>16</v>
       </c>
       <c r="AI9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>220</v>
+      </c>
+      <c r="AK9" t="n">
         <v>38</v>
       </c>
-      <c r="AJ9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>28</v>
-      </c>
       <c r="AL9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN9" t="n">
         <v>38</v>
       </c>
-      <c r="AM9" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>21</v>
-      </c>
       <c r="AO9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP9" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AT9" t="n">
         <v>11.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AV9" t="n">
         <v>10.5</v>
@@ -2767,98 +2767,98 @@
         <v>17.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA9" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BB9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BG9" t="n">
         <v>18</v>
       </c>
-      <c r="BC9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>16</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BH9" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="BJ9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>24</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>32</v>
+      </c>
+      <c r="BY9" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BK9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>20</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>30</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>20</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>30</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BZ9" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -2889,79 +2889,79 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="G10" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="H10" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M10" t="n">
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="Q10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T10" t="n">
         <v>2.16</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.2</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.62</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W10" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="X10" t="n">
-        <v>90</v>
+        <v>950</v>
       </c>
       <c r="Y10" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.8</v>
+        <v>950</v>
       </c>
       <c r="AC10" t="n">
-        <v>11</v>
+        <v>950</v>
       </c>
       <c r="AD10" t="n">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
@@ -2970,19 +2970,19 @@
         <v>8.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>11.5</v>
+        <v>950</v>
       </c>
       <c r="AH10" t="n">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AK10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL10" t="n">
         <v>60</v>
@@ -2997,122 +2997,122 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.61</v>
+        <v>4.8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.44</v>
+        <v>16.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.42</v>
+        <v>1.89</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.64</v>
+        <v>4.3</v>
       </c>
       <c r="AV10" t="n">
-        <v>6</v>
+        <v>2.96</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.16</v>
+        <v>5.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.4</v>
+        <v>1.88</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.38</v>
+        <v>4.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.43</v>
+        <v>1.83</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BO10" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>20</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>17</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -3143,237 +3143,237 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="H11" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="M11" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.27</v>
       </c>
-      <c r="O11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.17</v>
-      </c>
       <c r="S11" t="n">
-        <v>2.32</v>
+        <v>4.2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.11</v>
+        <v>1.61</v>
       </c>
       <c r="V11" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="W11" t="n">
-        <v>2.42</v>
+        <v>2.74</v>
       </c>
       <c r="X11" t="n">
         <v>950</v>
       </c>
       <c r="Y11" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="Z11" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>700</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>190</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>240</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL11" t="n">
         <v>60</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AM11" t="n">
         <v>300</v>
       </c>
-      <c r="AB11" t="n">
-        <v>950</v>
-      </c>
-      <c r="AC11" t="n">
+      <c r="AN11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>700</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU11" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AD11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>180</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>350</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>350</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AV11" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.5</v>
+        <v>9.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>3.7</v>
+        <v>11.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.6</v>
+        <v>11.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>14</v>
+        <v>5.9</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.04</v>
+        <v>1.84</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.04</v>
+        <v>1.69</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.04</v>
+        <v>1.7</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.04</v>
+        <v>1.6</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.04</v>
+        <v>1.58</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.04</v>
+        <v>1.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,251 +3383,251 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Reynir Sandgeroi</t>
+          <t>Kabylie</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Augnablik</t>
+          <t>Belouizdad</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.97</v>
+        <v>4.5</v>
       </c>
       <c r="G12" t="n">
-        <v>2.18</v>
+        <v>5.3</v>
       </c>
       <c r="H12" t="n">
-        <v>3.1</v>
+        <v>1.89</v>
       </c>
       <c r="I12" t="n">
-        <v>3.65</v>
+        <v>1.99</v>
       </c>
       <c r="J12" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="K12" t="n">
-        <v>5.5</v>
+        <v>3.95</v>
       </c>
       <c r="L12" t="n">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="M12" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>8</v>
+        <v>3.15</v>
       </c>
       <c r="O12" t="n">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="P12" t="n">
-        <v>3.4</v>
+        <v>1.72</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.34</v>
+        <v>2.24</v>
       </c>
       <c r="R12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V12" t="n">
         <v>2</v>
       </c>
-      <c r="S12" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.38</v>
-      </c>
       <c r="W12" t="n">
-        <v>1.84</v>
+        <v>1.25</v>
       </c>
       <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG12" t="n">
         <v>950</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AH12" t="n">
         <v>950</v>
       </c>
-      <c r="Z12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>950</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>970</v>
-      </c>
       <c r="AI12" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AJ12" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.28</v>
+        <v>1.8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.54</v>
+        <v>1.54</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.56</v>
+        <v>1.81</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.32</v>
+        <v>1.71</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.54</v>
+        <v>1.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.2</v>
+        <v>1.56</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.62</v>
+        <v>1.62</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.24</v>
+        <v>1.71</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.4</v>
+        <v>1.75</v>
       </c>
       <c r="AY12" t="n">
-        <v>5.5</v>
+        <v>1.7</v>
       </c>
       <c r="AZ12" t="n">
-        <v>5.5</v>
+        <v>1.71</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.6</v>
+        <v>1.76</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
       <c r="BC12" t="n">
-        <v>3</v>
+        <v>1.81</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.7</v>
+        <v>1.81</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.38</v>
+        <v>1.81</v>
       </c>
       <c r="BF12" t="n">
-        <v>4</v>
+        <v>1.81</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.5</v>
+        <v>1.68</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT12" t="n">
         <v>4.6</v>
       </c>
-      <c r="BJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>1000</v>
-      </c>
       <c r="BU12" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW12" t="n">
-        <v>2.18</v>
+        <v>1.04</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,246 +3642,246 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Kormakur/Hvot</t>
+          <t>Reynir Sandgeroi</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>IF Magni</t>
+          <t>Augnablik</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.71</v>
+        <v>1.96</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="H13" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="I13" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="J13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K13" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="M13" t="n">
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="P13" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="R13" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="T13" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="U13" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="X13" t="n">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="Y13" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="Z13" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AA13" t="n">
         <v>500</v>
       </c>
       <c r="AB13" t="n">
-        <v>17.5</v>
+        <v>950</v>
       </c>
       <c r="AC13" t="n">
-        <v>13</v>
+        <v>500</v>
       </c>
       <c r="AD13" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AE13" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AF13" t="n">
-        <v>17</v>
+        <v>500</v>
       </c>
       <c r="AG13" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH13" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AI13" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AJ13" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AK13" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AL13" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AM13" t="n">
-        <v>55</v>
+        <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>7.6</v>
+        <v>500</v>
       </c>
       <c r="AO13" t="n">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="AP13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>5.7</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AS13" t="n">
+      <c r="BA13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BC13" t="n">
         <v>6.2</v>
       </c>
-      <c r="AT13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>12</v>
-      </c>
       <c r="BD13" t="n">
-        <v>16.5</v>
+        <v>6.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.9</v>
+        <v>3.25</v>
       </c>
       <c r="BF13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO13" t="n">
         <v>4.8</v>
       </c>
-      <c r="BG13" t="n">
-        <v>21</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>70</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>4</v>
-      </c>
       <c r="BP13" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BR13" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BT13" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BV13" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.6</v>
+        <v>2.34</v>
       </c>
       <c r="BX13" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>6.6</v>
+        <v>2.36</v>
       </c>
       <c r="BZ13" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,239 +3896,239 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Kormakur/Hvot</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leiknir R</t>
+          <t>IF Magni</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.56</v>
+        <v>1.7</v>
       </c>
       <c r="G14" t="n">
-        <v>2.68</v>
+        <v>1.88</v>
       </c>
       <c r="H14" t="n">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>2.74</v>
+        <v>4.9</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="K14" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="M14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="P14" t="n">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="R14" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="S14" t="n">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="T14" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="U14" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="V14" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="Y14" t="n">
-        <v>18.5</v>
+        <v>30</v>
       </c>
       <c r="Z14" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="AA14" t="n">
-        <v>120</v>
+        <v>310</v>
       </c>
       <c r="AB14" t="n">
         <v>17.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AD14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT14" t="n">
         <v>13.5</v>
       </c>
-      <c r="AE14" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AP14" t="n">
+      <c r="AU14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>70</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP14" t="n">
         <v>11.5</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT14" t="n">
+      <c r="BQ14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>32</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BZ14" t="n">
         <v>12</v>
       </c>
-      <c r="AU14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>16</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>9</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>26</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>26</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>16.5</v>
-      </c>
       <c r="CA14" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -4159,19 +4159,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="G15" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="H15" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="I15" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K15" t="n">
         <v>4.5</v>
@@ -4189,37 +4189,37 @@
         <v>1.12</v>
       </c>
       <c r="P15" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R15" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="S15" t="n">
         <v>1.94</v>
       </c>
       <c r="T15" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="U15" t="n">
         <v>3.2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="W15" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X15" t="n">
         <v>46</v>
       </c>
       <c r="Y15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA15" t="n">
         <v>34</v>
@@ -4231,7 +4231,7 @@
         <v>13</v>
       </c>
       <c r="AD15" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE15" t="n">
         <v>24</v>
@@ -4243,16 +4243,16 @@
         <v>17</v>
       </c>
       <c r="AH15" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI15" t="n">
         <v>28</v>
       </c>
       <c r="AJ15" t="n">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="AK15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL15" t="n">
         <v>32</v>
@@ -4261,13 +4261,13 @@
         <v>38</v>
       </c>
       <c r="AN15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AO15" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP15" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AQ15" t="n">
         <v>19.5</v>
@@ -4279,13 +4279,13 @@
         <v>16</v>
       </c>
       <c r="AT15" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AU15" t="n">
         <v>10</v>
       </c>
       <c r="AV15" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AW15" t="n">
         <v>18</v>
@@ -4294,95 +4294,95 @@
         <v>14.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ15" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BA15" t="n">
         <v>20</v>
       </c>
       <c r="BB15" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="BC15" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD15" t="n">
         <v>14.5</v>
       </c>
-      <c r="BD15" t="n">
-        <v>19</v>
-      </c>
       <c r="BE15" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="BF15" t="n">
         <v>10</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH15" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL15" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN15" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP15" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR15" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT15" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV15" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX15" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
@@ -4404,246 +4404,246 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Leiknir R</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.91</v>
+        <v>3.05</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="H16" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>2.34</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K16" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M16" t="n">
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="O16" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P16" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="R16" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="S16" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="U16" t="n">
         <v>2.66</v>
       </c>
       <c r="V16" t="n">
-        <v>1.33</v>
+        <v>1.74</v>
       </c>
       <c r="W16" t="n">
-        <v>1.98</v>
+        <v>1.47</v>
       </c>
       <c r="X16" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="Y16" t="n">
-        <v>24</v>
+        <v>15.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>36</v>
+        <v>18.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>470</v>
+        <v>95</v>
       </c>
       <c r="AB16" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AC16" t="n">
         <v>11</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="AF16" t="n">
-        <v>19.5</v>
+        <v>65</v>
       </c>
       <c r="AG16" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="AH16" t="n">
         <v>16</v>
       </c>
       <c r="AI16" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AJ16" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC16" t="n">
         <v>24</v>
       </c>
-      <c r="AK16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU16" t="n">
+      <c r="BD16" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG16" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AV16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BH16" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="BJ16" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK16" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN16" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BO16" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BP16" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BR16" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="BV16" t="n">
-        <v>27</v>
+        <v>16.5</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BX16" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BZ16" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,251 +4653,251 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hviti Riddarinn</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haukar</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>1.92</v>
       </c>
       <c r="G17" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>470</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>20</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>13</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>21</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>30</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>14</v>
+      </c>
+      <c r="CA17" t="n">
         <v>6</v>
       </c>
-      <c r="H17" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="J17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N17" t="n">
-        <v>8</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="V17" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X17" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>100</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>950</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>180</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>240</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>150</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>160</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>5</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>4.9</v>
-      </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,251 +4907,251 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CA Ituzaingo</t>
+          <t>Hviti Riddarinn</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Real Pilar FC</t>
+          <t>Haukar</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="G18" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="H18" t="n">
-        <v>2.22</v>
+        <v>1.52</v>
       </c>
       <c r="I18" t="n">
-        <v>2.42</v>
+        <v>1.58</v>
       </c>
       <c r="J18" t="n">
-        <v>2.94</v>
+        <v>5.4</v>
       </c>
       <c r="K18" t="n">
-        <v>3.2</v>
+        <v>5.9</v>
       </c>
       <c r="L18" t="n">
-        <v>1.56</v>
+        <v>1.21</v>
       </c>
       <c r="M18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="O18" t="n">
         <v>1.12</v>
       </c>
-      <c r="N18" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T18" t="n">
         <v>1.51</v>
       </c>
-      <c r="P18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="U18" t="n">
         <v>2.58</v>
       </c>
-      <c r="R18" t="n">
+      <c r="V18" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.2</v>
       </c>
-      <c r="S18" t="n">
+      <c r="X18" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>180</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>240</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>160</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT18" t="n">
         <v>5.1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>75</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>500</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>4.9</v>
       </c>
       <c r="BU18" t="n">
         <v>3.8</v>
       </c>
       <c r="BV18" t="n">
-        <v>19</v>
+        <v>9.4</v>
       </c>
       <c r="BW18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BX18" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="CA18" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,105 +5161,105 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Wanderers (Uru)</t>
+          <t>CA Ituzaingo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>Real Pilar FC</t>
         </is>
       </c>
       <c r="F19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I19" t="n">
         <v>2.32</v>
       </c>
-      <c r="G19" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="H19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I19" t="n">
-        <v>3.85</v>
-      </c>
       <c r="J19" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K19" t="n">
         <v>3.1</v>
       </c>
-      <c r="K19" t="n">
-        <v>3.35</v>
-      </c>
       <c r="L19" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="M19" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N19" t="n">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="O19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P19" t="n">
         <v>1.51</v>
       </c>
-      <c r="P19" t="n">
-        <v>1.58</v>
-      </c>
       <c r="Q19" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="U19" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="V19" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7</v>
+        <v>1.27</v>
       </c>
       <c r="X19" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y19" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>500</v>
+        <v>13</v>
       </c>
       <c r="AA19" t="n">
-        <v>900</v>
+        <v>32</v>
       </c>
       <c r="AB19" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AC19" t="n">
         <v>7.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>29</v>
+        <v>12.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AF19" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="AG19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH19" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="AI19" t="n">
         <v>500</v>
@@ -5271,141 +5271,141 @@
         <v>500</v>
       </c>
       <c r="AL19" t="n">
-        <v>380</v>
+        <v>500</v>
       </c>
       <c r="AM19" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN19" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO19" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AP19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC19" t="n">
         <v>7.8</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>7.4</v>
       </c>
       <c r="BD19" t="n">
         <v>8</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF19" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BH19" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="BJ19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN19" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="BO19" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BP19" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT19" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="BU19" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="BV19" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BW19" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5420,109 +5420,109 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Plaza Colonia</t>
+          <t>Wanderers (Uru)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Huracan del Paso</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.88</v>
+        <v>2.32</v>
       </c>
       <c r="G20" t="n">
-        <v>1.97</v>
+        <v>2.44</v>
       </c>
       <c r="H20" t="n">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="I20" t="n">
-        <v>5.6</v>
+        <v>3.85</v>
       </c>
       <c r="J20" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K20" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="L20" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="M20" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N20" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="O20" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="P20" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.28</v>
+        <v>2.58</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S20" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U20" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V20" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="W20" t="n">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="X20" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="Z20" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AA20" t="n">
         <v>900</v>
       </c>
       <c r="AB20" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AE20" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="AF20" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="AG20" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AH20" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="AI20" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23</v>
+        <v>900</v>
       </c>
       <c r="AK20" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AL20" t="n">
         <v>500</v>
@@ -5531,135 +5531,135 @@
         <v>580</v>
       </c>
       <c r="AN20" t="n">
-        <v>18</v>
+        <v>600</v>
       </c>
       <c r="AO20" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AP20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW20" t="n">
         <v>8.6</v>
       </c>
-      <c r="AQ20" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>9</v>
-      </c>
       <c r="AX20" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ20" t="n">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="BA20" t="n">
         <v>9</v>
       </c>
       <c r="BB20" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG20" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH20" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="BJ20" t="n">
         <v>11.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN20" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="BP20" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="BQ20" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT20" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BX20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BZ20" t="n">
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,251 +5669,251 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Talleres (RE)</t>
+          <t>Plaza Colonia</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Deportivo Merlo</t>
+          <t>Huracan del Paso</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.56</v>
+        <v>1.87</v>
       </c>
       <c r="G21" t="n">
-        <v>3.05</v>
+        <v>1.98</v>
       </c>
       <c r="H21" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="I21" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="J21" t="n">
-        <v>2.46</v>
+        <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="L21" t="n">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="M21" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="N21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T21" t="n">
         <v>2.04</v>
       </c>
-      <c r="O21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="U21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X21" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>700</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY21" t="n">
         <v>8</v>
       </c>
-      <c r="T21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH21" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN21" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BP21" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5928,246 +5928,246 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>Talleres (RE)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Deportivo Merlo</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="G22" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="H22" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="I22" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="J22" t="n">
-        <v>2.86</v>
+        <v>2.4</v>
       </c>
       <c r="K22" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="L22" t="n">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="M22" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="N22" t="n">
-        <v>2.74</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="P22" t="n">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.72</v>
+        <v>3.65</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="S22" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="T22" t="n">
-        <v>2.1</v>
+        <v>1.11</v>
       </c>
       <c r="U22" t="n">
-        <v>1.81</v>
+        <v>1.11</v>
       </c>
       <c r="V22" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W22" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="X22" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="n">
-        <v>2.72</v>
+        <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.38</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>17</v>
+        <v>1.04</v>
       </c>
       <c r="BN22" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP22" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BT22" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>14</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22" t="n">
         <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,498 +6177,752 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Operario PR</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.28</v>
+        <v>2.54</v>
       </c>
       <c r="G23" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="H23" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="I23" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J23" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="K23" t="n">
-        <v>3.55</v>
+        <v>2.94</v>
       </c>
       <c r="L23" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="M23" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="N23" t="n">
-        <v>3.2</v>
+        <v>2.68</v>
       </c>
       <c r="O23" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="P23" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="S23" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="T23" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="U23" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="V23" t="n">
         <v>1.36</v>
       </c>
       <c r="W23" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="X23" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AA23" t="n">
         <v>80</v>
       </c>
       <c r="AB23" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD23" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE23" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF23" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG23" t="n">
         <v>13</v>
       </c>
       <c r="AH23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI23" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL23" t="n">
         <v>70</v>
       </c>
-      <c r="AJ23" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>55</v>
-      </c>
       <c r="AM23" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="AN23" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AO23" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR23" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.7</v>
+        <v>65</v>
       </c>
       <c r="AT23" t="n">
         <v>6.8</v>
       </c>
       <c r="AU23" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AV23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>36</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>70</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BJ23" t="n">
         <v>11.5</v>
       </c>
-      <c r="AW23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ23" t="n">
+      <c r="BK23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
         <v>14.5</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="BN23" t="n">
         <v>5.2</v>
       </c>
       <c r="BO23" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP23" t="n">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="BQ23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT23" t="n">
         <v>6.6</v>
       </c>
-      <c r="BR23" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS23" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT23" t="n">
-        <v>7</v>
-      </c>
       <c r="BU23" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV23" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW23" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="BZ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-05 05:15:24</t>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>San Marcos</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X24" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:26:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Canadian Premier League</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>23:00:00</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Vancouver FC</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Atletico Ottawa</t>
         </is>
       </c>
-      <c r="F24" t="n">
+      <c r="F25" t="n">
         <v>2.26</v>
       </c>
-      <c r="G24" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="H24" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="I24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="G25" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M25" t="n">
         <v>1.05</v>
       </c>
-      <c r="N24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O24" t="n">
+      <c r="N25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O25" t="n">
         <v>1.27</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P25" t="n">
         <v>2.12</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q25" t="n">
         <v>1.79</v>
       </c>
-      <c r="R24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S24" t="n">
+      <c r="R25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S25" t="n">
         <v>3.05</v>
       </c>
-      <c r="T24" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V24" t="n">
+      <c r="T25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V25" t="n">
         <v>1.01</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W25" t="n">
         <v>1.01</v>
       </c>
-      <c r="X24" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y24" t="n">
+      <c r="X25" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD25" t="n">
         <v>16</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AE25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG25" t="n">
         <v>23</v>
       </c>
-      <c r="AA24" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE24" t="n">
+      <c r="BH25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>24</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX25" t="n">
         <v>34</v>
       </c>
-      <c r="AF24" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB24" t="n">
+      <c r="BY25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BZ25" t="n">
         <v>23</v>
       </c>
-      <c r="BC24" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BI24" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN24" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BO24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP24" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BQ24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR24" t="n">
-        <v>29</v>
-      </c>
-      <c r="BS24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BU24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BV24" t="n">
-        <v>22</v>
-      </c>
-      <c r="BW24" t="n">
+      <c r="CA25" t="n">
         <v>7</v>
       </c>
-      <c r="BX24" t="n">
-        <v>32</v>
-      </c>
-      <c r="BY24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BZ24" t="n">
-        <v>22</v>
-      </c>
-      <c r="CA24" t="n">
-        <v>7</v>
-      </c>
-      <c r="CB24" t="inlineStr">
-        <is>
-          <t>2026-06-05 05:15:24</t>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:26:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB21"/>
+  <dimension ref="A1:CB20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ukrainian Premier League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,244 +843,244 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FK Kudrivka</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Agrobiznes Volochysk</t>
+          <t>MB Rouissat</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="G2" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="H2" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="I2" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1</v>
+        <v>2.84</v>
       </c>
       <c r="K2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="S2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="T2" t="n">
         <v>4.2</v>
       </c>
-      <c r="L2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="U2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>580</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>420</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
         <v>4.3</v>
       </c>
-      <c r="O2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="X2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA2" t="n">
+      <c r="AQ2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>260</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>70</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>280</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>44</v>
+      </c>
+      <c r="BD2" t="n">
         <v>180</v>
       </c>
-      <c r="AB2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>70</v>
-      </c>
-      <c r="BB2" t="n">
+      <c r="BE2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>34</v>
+      </c>
+      <c r="BG2" t="n">
         <v>14</v>
       </c>
-      <c r="BC2" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>80</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>55</v>
-      </c>
       <c r="BH2" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -1102,246 +1102,246 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MB Rouissat</t>
+          <t>ES Setif</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.12</v>
+        <v>8.4</v>
       </c>
       <c r="G3" t="n">
-        <v>2.24</v>
+        <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>3.75</v>
+        <v>1.57</v>
       </c>
       <c r="I3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>350</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>230</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>4.3</v>
       </c>
-      <c r="J3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="X3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Y3" t="n">
+      <c r="AR3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AW3" t="n">
         <v>25</v>
       </c>
-      <c r="Z3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>140</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS3" t="n">
+      <c r="AX3" t="n">
         <v>9.6</v>
       </c>
-      <c r="AT3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>11</v>
-      </c>
       <c r="AY3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB3" t="n">
         <v>9.6</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA3" t="n">
+      <c r="BC3" t="n">
+        <v>50</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>120</v>
+      </c>
+      <c r="BG3" t="n">
         <v>38</v>
       </c>
-      <c r="BB3" t="n">
-        <v>24</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>9</v>
-      </c>
       <c r="BH3" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Paradou</t>
+          <t>FBK Karlstad</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Setif</t>
+          <t>IF Karlstad</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.66</v>
+        <v>3.85</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>2.84</v>
+        <v>2.26</v>
       </c>
       <c r="I4" t="n">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="L4" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="O4" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="P4" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="R4" t="n">
         <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>3.7</v>
+        <v>1.91</v>
       </c>
       <c r="T4" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="U4" t="n">
         <v>2.12</v>
       </c>
       <c r="V4" t="n">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="W4" t="n">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="X4" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE4" t="n">
         <v>23</v>
       </c>
-      <c r="Y4" t="n">
-        <v>500</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>220</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>500</v>
-      </c>
       <c r="AF4" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AG4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AH4" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="AI4" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AJ4" t="n">
         <v>500</v>
       </c>
       <c r="AK4" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AL4" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AM4" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN4" t="n">
         <v>600</v>
       </c>
       <c r="AO4" t="n">
-        <v>600</v>
+        <v>17</v>
       </c>
       <c r="AP4" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AR4" t="n">
         <v>13</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.6</v>
+        <v>23</v>
       </c>
       <c r="AT4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV4" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AU4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AW4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>13.5</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="BA4" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>38</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>30</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>29</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>29</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
         <v>11.5</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="BT4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>16</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>28</v>
+      </c>
+      <c r="BY4" t="n">
         <v>10</v>
       </c>
-      <c r="AZ4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>26</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>25</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,244 +1605,244 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FBK Karlstad</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IF Karlstad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>1.49</v>
       </c>
       <c r="G5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X5" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>170</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>480</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>270</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>240</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>790</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>620</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>80</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>950</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BO5" t="n">
         <v>3.25</v>
       </c>
-      <c r="H5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>85</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>22</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>16</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
+      <c r="BP5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>950</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
         <v>10.5</v>
       </c>
-      <c r="BN5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>23</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>19</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BX5" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BZ5" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -1859,244 +1859,244 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="G6" t="n">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="K6" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="O6" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="P6" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="T6" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="U6" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="V6" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="W6" t="n">
-        <v>2.74</v>
+        <v>3.55</v>
       </c>
       <c r="X6" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="Y6" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>730</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>450</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH6" t="n">
         <v>950</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AI6" t="n">
+        <v>350</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL6" t="n">
         <v>170</v>
       </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>200</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>75</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>500</v>
-      </c>
       <c r="AM6" t="n">
-        <v>790</v>
+        <v>490</v>
       </c>
       <c r="AN6" t="n">
-        <v>29</v>
+        <v>7.8</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="AQ6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>16</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>15</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
         <v>6.8</v>
       </c>
-      <c r="AR6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BN6" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -2118,246 +2118,246 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Kabylie</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.42</v>
+        <v>3.8</v>
       </c>
       <c r="G7" t="n">
-        <v>1.44</v>
+        <v>4.1</v>
       </c>
       <c r="H7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP7" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="I7" t="n">
-        <v>13</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K7" t="n">
+      <c r="AQ7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>19</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT7" t="n">
         <v>4.9</v>
       </c>
-      <c r="L7" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X7" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>28</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>530</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>110</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>260</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>250</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>310</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>510</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY7" t="n">
+      <c r="BU7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>17</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
         <v>10</v>
       </c>
-      <c r="AZ7" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>48</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Kabylie</t>
+          <t>Reynir Sandgeroi</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Belouizdad</t>
+          <t>Augnablik</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1</v>
+        <v>1.77</v>
       </c>
       <c r="G8" t="n">
-        <v>4.3</v>
+        <v>1.89</v>
       </c>
       <c r="H8" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="I8" t="n">
-        <v>2.14</v>
+        <v>4.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.48</v>
+        <v>1.19</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>8.6</v>
       </c>
       <c r="O8" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="P8" t="n">
-        <v>1.75</v>
+        <v>3.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.2</v>
+        <v>1.31</v>
       </c>
       <c r="R8" t="n">
-        <v>1.27</v>
+        <v>2.08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.2</v>
+        <v>1.79</v>
       </c>
       <c r="T8" t="n">
-        <v>1.94</v>
+        <v>1.39</v>
       </c>
       <c r="U8" t="n">
-        <v>1.94</v>
+        <v>3.05</v>
       </c>
       <c r="V8" t="n">
-        <v>1.87</v>
+        <v>1.31</v>
       </c>
       <c r="W8" t="n">
-        <v>1.31</v>
+        <v>2.08</v>
       </c>
       <c r="X8" t="n">
-        <v>13.5</v>
+        <v>950</v>
       </c>
       <c r="Y8" t="n">
-        <v>8</v>
+        <v>950</v>
       </c>
       <c r="Z8" t="n">
-        <v>13</v>
+        <v>500</v>
       </c>
       <c r="AA8" t="n">
-        <v>28</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>16</v>
+        <v>950</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.4</v>
+        <v>500</v>
       </c>
       <c r="AD8" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AE8" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AF8" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AG8" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="AH8" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AI8" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AJ8" t="n">
         <v>900</v>
       </c>
       <c r="AK8" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AL8" t="n">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AM8" t="n">
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>600</v>
+        <v>6.2</v>
       </c>
       <c r="AO8" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AP8" t="n">
-        <v>9.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="AQ8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW8" t="n">
         <v>6.4</v>
       </c>
-      <c r="AR8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AX8" t="n">
-        <v>16.5</v>
+        <v>5.9</v>
       </c>
       <c r="AY8" t="n">
-        <v>15.5</v>
+        <v>5.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.6</v>
+        <v>13</v>
       </c>
       <c r="BB8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD8" t="n">
         <v>5.9</v>
       </c>
-      <c r="BC8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BE8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="BG8" t="n">
         <v>15</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.56</v>
+        <v>4.8</v>
       </c>
       <c r="BJ8" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>13.5</v>
+        <v>3.6</v>
       </c>
       <c r="BN8" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BO8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA8" t="n">
         <v>5</v>
       </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>16</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>0</v>
-      </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,184 +2626,184 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Reynir Sandgeroi</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Augnablik</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="G9" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="H9" t="n">
         <v>3.1</v>
       </c>
       <c r="I9" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K9" t="n">
         <v>4.3</v>
       </c>
-      <c r="K9" t="n">
-        <v>5.1</v>
-      </c>
       <c r="L9" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="M9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="P9" t="n">
-        <v>3.45</v>
+        <v>2.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="R9" t="n">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="S9" t="n">
-        <v>1.83</v>
+        <v>2.34</v>
       </c>
       <c r="T9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.43</v>
       </c>
-      <c r="U9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.4</v>
-      </c>
       <c r="W9" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="X9" t="n">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="Y9" t="n">
-        <v>950</v>
+        <v>20</v>
       </c>
       <c r="Z9" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AA9" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AB9" t="n">
-        <v>950</v>
+        <v>18</v>
       </c>
       <c r="AC9" t="n">
-        <v>500</v>
+        <v>10.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AE9" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AF9" t="n">
-        <v>500</v>
+        <v>19.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AI9" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AJ9" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AK9" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AL9" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AM9" t="n">
-        <v>580</v>
+        <v>55</v>
       </c>
       <c r="AN9" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="AO9" t="n">
-        <v>500</v>
+        <v>18</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.3</v>
+        <v>18</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.26</v>
+        <v>16.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.34</v>
+        <v>22</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.32</v>
+        <v>28</v>
       </c>
       <c r="AT9" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV9" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.34</v>
+        <v>19.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>6.2</v>
+        <v>16.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.7</v>
+        <v>12.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.25</v>
+        <v>21</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.8</v>
+        <v>23</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.4</v>
+        <v>22</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.38</v>
+        <v>23</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.85</v>
+        <v>9.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.15</v>
+        <v>15.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK9" t="n">
         <v>4.9</v>
@@ -2812,53 +2812,53 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ9" t="n">
         <v>6.4</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS9" t="n">
-        <v>2.5</v>
+        <v>7.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU9" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.81</v>
+        <v>7.4</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.98</v>
+        <v>8</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA9" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="G10" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="H10" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="I10" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K10" t="n">
         <v>6.2</v>
@@ -2913,28 +2913,28 @@
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O10" t="n">
         <v>1.12</v>
       </c>
       <c r="P10" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="S10" t="n">
         <v>1.98</v>
       </c>
       <c r="T10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U10" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V10" t="n">
         <v>1.01</v>
@@ -2943,28 +2943,28 @@
         <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Y10" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Z10" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AA10" t="n">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="AB10" t="n">
         <v>16</v>
       </c>
       <c r="AC10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AE10" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AF10" t="n">
         <v>13</v>
@@ -2973,10 +2973,10 @@
         <v>11.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ10" t="n">
         <v>15</v>
@@ -2985,46 +2985,46 @@
         <v>13.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM10" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AN10" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AO10" t="n">
         <v>55</v>
       </c>
       <c r="AP10" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AQ10" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AR10" t="n">
         <v>34</v>
       </c>
       <c r="AS10" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AV10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AW10" t="n">
         <v>46</v>
       </c>
       <c r="AX10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
         <v>18</v>
@@ -3045,25 +3045,25 @@
         <v>26</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="BG10" t="n">
-        <v>40</v>
+        <v>12.5</v>
       </c>
       <c r="BH10" t="n">
         <v>5.6</v>
       </c>
       <c r="BI10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BJ10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM10" t="n">
         <v>9.4</v>
@@ -3072,47 +3072,47 @@
         <v>4.9</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BP10" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BQ10" t="n">
         <v>4.9</v>
       </c>
       <c r="BR10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BS10" t="n">
         <v>6.6</v>
       </c>
       <c r="BT10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY10" t="n">
         <v>8.4</v>
       </c>
       <c r="BZ10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -3134,239 +3134,239 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.92</v>
+        <v>3.2</v>
       </c>
       <c r="G11" t="n">
-        <v>1.99</v>
+        <v>3.4</v>
       </c>
       <c r="H11" t="n">
-        <v>3.75</v>
+        <v>2.12</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>2.22</v>
       </c>
       <c r="J11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K11" t="n">
         <v>4.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="M11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="O11" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="P11" t="n">
-        <v>2.92</v>
+        <v>3.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="R11" t="n">
-        <v>1.71</v>
+        <v>2.06</v>
       </c>
       <c r="S11" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="T11" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="U11" t="n">
-        <v>2.72</v>
+        <v>3.35</v>
       </c>
       <c r="V11" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>1.41</v>
       </c>
       <c r="X11" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="Y11" t="n">
         <v>28</v>
       </c>
       <c r="Z11" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="AA11" t="n">
-        <v>470</v>
+        <v>29</v>
       </c>
       <c r="AB11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>27</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>22</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BX11" t="n">
         <v>17.5</v>
       </c>
-      <c r="AC11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>250</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>20</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>13</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>21</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT11" t="n">
+      <c r="BY11" t="n">
         <v>7.8</v>
       </c>
-      <c r="BU11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>27</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>32</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BZ11" t="n">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="CA11" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="G12" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="H12" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="I12" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="J12" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K12" t="n">
         <v>4.3</v>
@@ -3427,85 +3427,85 @@
         <v>1.18</v>
       </c>
       <c r="P12" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R12" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T12" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="U12" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="V12" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="W12" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="X12" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="Y12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB12" t="n">
         <v>21</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>28</v>
       </c>
       <c r="AC12" t="n">
         <v>10.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AG12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH12" t="n">
         <v>14.5</v>
       </c>
-      <c r="AH12" t="n">
-        <v>15</v>
-      </c>
       <c r="AI12" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AJ12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL12" t="n">
         <v>55</v>
       </c>
-      <c r="AK12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>85</v>
-      </c>
       <c r="AM12" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="AN12" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AO12" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ12" t="n">
         <v>14</v>
@@ -3514,10 +3514,10 @@
         <v>16.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AT12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU12" t="n">
         <v>8.6</v>
@@ -3526,13 +3526,13 @@
         <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX12" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="AY12" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>12.5</v>
@@ -3541,10 +3541,10 @@
         <v>22</v>
       </c>
       <c r="BB12" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BC12" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="BD12" t="n">
         <v>26</v>
@@ -3553,16 +3553,16 @@
         <v>42</v>
       </c>
       <c r="BF12" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ12" t="n">
         <v>8.800000000000001</v>
@@ -3574,60 +3574,60 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BN12" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BO12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BP12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BQ12" t="n">
         <v>6.8</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT12" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BV12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BW12" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY12" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BZ12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,251 +3637,251 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>Hviti Riddarinn</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Haukar</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.2</v>
+        <v>7.4</v>
       </c>
       <c r="G13" t="n">
-        <v>3.35</v>
+        <v>8.6</v>
       </c>
       <c r="H13" t="n">
-        <v>2.12</v>
+        <v>1.37</v>
       </c>
       <c r="I13" t="n">
-        <v>2.22</v>
+        <v>1.41</v>
       </c>
       <c r="J13" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M13" t="n">
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P13" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="R13" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="S13" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="T13" t="n">
-        <v>1.39</v>
+        <v>1.59</v>
       </c>
       <c r="U13" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X13" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>150</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>240</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>210</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG13" t="n">
         <v>3.25</v>
       </c>
-      <c r="V13" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X13" t="n">
-        <v>80</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>38</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>30</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BH13" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BI13" t="n">
         <v>4.4</v>
       </c>
       <c r="BJ13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BV13" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BK13" t="n">
+      <c r="BW13" t="n">
         <v>6</v>
       </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>20</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>22</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BX13" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BY13" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BZ13" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CA13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,251 +3891,251 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Hviti Riddarinn</t>
+          <t>CA Ituzaingo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Haukar</t>
+          <t>Real Pilar FC</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="G14" t="n">
-        <v>8.6</v>
+        <v>4.8</v>
       </c>
       <c r="H14" t="n">
-        <v>1.37</v>
+        <v>2.2</v>
       </c>
       <c r="I14" t="n">
-        <v>1.41</v>
+        <v>2.32</v>
       </c>
       <c r="J14" t="n">
-        <v>6.2</v>
+        <v>2.9</v>
       </c>
       <c r="K14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y14" t="n">
         <v>7.2</v>
       </c>
-      <c r="L14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="P14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="V14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X14" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>100</v>
-      </c>
       <c r="Z14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA14" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="AB14" t="n">
-        <v>950</v>
+        <v>12</v>
       </c>
       <c r="AC14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG14" t="n">
         <v>22</v>
       </c>
-      <c r="AD14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>150</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>950</v>
-      </c>
       <c r="AH14" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AI14" t="n">
-        <v>40</v>
+        <v>460</v>
       </c>
       <c r="AJ14" t="n">
-        <v>240</v>
+        <v>900</v>
       </c>
       <c r="AK14" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AL14" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AM14" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AN14" t="n">
         <v>600</v>
       </c>
       <c r="AO14" t="n">
-        <v>3.65</v>
+        <v>500</v>
       </c>
       <c r="AP14" t="n">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="AQ14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
         <v>11</v>
       </c>
-      <c r="AR14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AV14" t="n">
+      <c r="BN14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>12</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>10</v>
       </c>
       <c r="BT14" t="n">
         <v>4.8</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BV14" t="n">
-        <v>8.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BX14" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BZ14" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,192 +4145,192 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CA Ituzaingo</t>
+          <t>Wanderers (Uru)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Real Pilar FC</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.1</v>
+        <v>2.38</v>
       </c>
       <c r="G15" t="n">
-        <v>4.7</v>
+        <v>2.48</v>
       </c>
       <c r="H15" t="n">
-        <v>2.24</v>
+        <v>3.5</v>
       </c>
       <c r="I15" t="n">
-        <v>2.34</v>
+        <v>3.75</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="K15" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="L15" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="M15" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="N15" t="n">
-        <v>2.58</v>
+        <v>2.84</v>
       </c>
       <c r="O15" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="P15" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S15" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="U15" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="V15" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="X15" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="Z15" t="n">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="AA15" t="n">
-        <v>32</v>
+        <v>900</v>
       </c>
       <c r="AB15" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC15" t="n">
         <v>7.6</v>
       </c>
       <c r="AD15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>240</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG15" t="n">
         <v>12.5</v>
       </c>
-      <c r="AE15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF15" t="n">
+      <c r="AH15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>380</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK15" t="n">
         <v>75</v>
       </c>
-      <c r="AG15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>460</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK15" t="n">
+      <c r="AL15" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN15" t="n">
         <v>500</v>
       </c>
-      <c r="AL15" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN15" t="n">
+      <c r="AO15" t="n">
         <v>600</v>
       </c>
-      <c r="AO15" t="n">
-        <v>500</v>
-      </c>
       <c r="AP15" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AQ15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK15" t="n">
         <v>5.9</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>5.8</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
@@ -4339,57 +4339,57 @@
         <v>11</v>
       </c>
       <c r="BN15" t="n">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BP15" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ15" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BT15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>7</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>9</v>
-      </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,246 +4404,246 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wanderers (Uru)</t>
+          <t>Plaza Colonia</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>Huracan del Paso</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="G16" t="n">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="H16" t="n">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="I16" t="n">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="J16" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="K16" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="L16" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="M16" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="R16" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="T16" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="V16" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="W16" t="n">
-        <v>1.71</v>
+        <v>2.02</v>
       </c>
       <c r="X16" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y16" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AA16" t="n">
         <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE16" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL16" t="n">
         <v>500</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>380</v>
       </c>
       <c r="AM16" t="n">
         <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="AP16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AT16" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>20</v>
       </c>
-      <c r="AX16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>13</v>
-      </c>
       <c r="BA16" t="n">
-        <v>32</v>
+        <v>7.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>28</v>
+        <v>19.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BD16" t="n">
-        <v>25</v>
+        <v>7.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.4</v>
+        <v>16.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>21</v>
+        <v>7.8</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="BJ16" t="n">
         <v>11.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BN16" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="BP16" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BT16" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BZ16" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA16" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,251 +4653,251 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Plaza Colonia</t>
+          <t>Talleres (RE)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Huracan del Paso</t>
+          <t>Deportivo Merlo</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.9</v>
+        <v>2.48</v>
       </c>
       <c r="G17" t="n">
-        <v>1.99</v>
+        <v>3.25</v>
       </c>
       <c r="H17" t="n">
-        <v>4.7</v>
+        <v>3.15</v>
       </c>
       <c r="I17" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J17" t="n">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.6</v>
+        <v>2.76</v>
       </c>
       <c r="L17" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="N17" t="n">
-        <v>2.96</v>
+        <v>2.02</v>
       </c>
       <c r="O17" t="n">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="P17" t="n">
-        <v>1.65</v>
+        <v>1.29</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.36</v>
+        <v>3.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="S17" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1</v>
+        <v>1.11</v>
       </c>
       <c r="U17" t="n">
-        <v>1.8</v>
+        <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="X17" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.48</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN17" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BP17" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT17" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,246 +4912,246 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Talleres (RE)</t>
+          <t>Operario PR</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Deportivo Merlo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="G18" t="n">
-        <v>3.35</v>
+        <v>2.6</v>
       </c>
       <c r="H18" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="I18" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="J18" t="n">
-        <v>2.38</v>
+        <v>2.94</v>
       </c>
       <c r="K18" t="n">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="L18" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="M18" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>2.66</v>
       </c>
       <c r="O18" t="n">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="P18" t="n">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="S18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X18" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB18" t="n">
         <v>7.6</v>
       </c>
-      <c r="T18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1000</v>
-      </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BH18" t="n">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.04</v>
+        <v>17.5</v>
       </c>
       <c r="BN18" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BR18" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BX18" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.04</v>
+        <v>14</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.04</v>
+        <v>14</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,219 +5161,219 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="G19" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="H19" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="I19" t="n">
         <v>3.7</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>2.94</v>
+        <v>3.6</v>
       </c>
       <c r="L19" t="n">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="M19" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>2.66</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="P19" t="n">
-        <v>1.52</v>
+        <v>1.77</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.8</v>
+        <v>2.18</v>
       </c>
       <c r="R19" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="T19" t="n">
-        <v>2.14</v>
+        <v>1.84</v>
       </c>
       <c r="U19" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
         <v>1.37</v>
       </c>
       <c r="W19" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="X19" t="n">
-        <v>8.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="Z19" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AA19" t="n">
         <v>75</v>
       </c>
       <c r="AB19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC19" t="n">
         <v>7.8</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AD19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT19" t="n">
         <v>6.8</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>65</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>70</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>60</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>17</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>36</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>32</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>7</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>48</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>6.4</v>
       </c>
       <c r="BU19" t="n">
         <v>5.7</v>
@@ -5382,30 +5382,30 @@
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX19" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>14</v>
+        <v>9.4</v>
       </c>
       <c r="BZ19" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="CA19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,498 +5415,244 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>23:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Atletico Ottawa</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>2.28</v>
       </c>
       <c r="G20" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H20" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="J20" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="K20" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="M20" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="P20" t="n">
-        <v>1.75</v>
+        <v>2.16</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="S20" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="T20" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="U20" t="n">
-        <v>1.98</v>
+        <v>2.24</v>
       </c>
       <c r="V20" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="Y20" t="n">
         <v>14.5</v>
       </c>
       <c r="Z20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO20" t="n">
         <v>29</v>
       </c>
-      <c r="AA20" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="AP20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT20" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AU20" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW20" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="AX20" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AY20" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA20" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.8</v>
+        <v>26</v>
       </c>
       <c r="BC20" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.3</v>
+        <v>30</v>
       </c>
       <c r="BF20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>22</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP20" t="n">
         <v>17.5</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>18.5</v>
       </c>
       <c r="BQ20" t="n">
         <v>6.4</v>
       </c>
       <c r="BR20" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS20" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT20" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BV20" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW20" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY20" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="CA20" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-05 11:50:17</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>23:00:00</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Vancouver FC</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Atletico Ottawa</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="I21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X21" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>26</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>65</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>23</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>29</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV21" t="n">
-        <v>25</v>
-      </c>
-      <c r="BW21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BX21" t="n">
-        <v>34</v>
-      </c>
-      <c r="BY21" t="n">
-        <v>8</v>
-      </c>
-      <c r="BZ21" t="n">
-        <v>23</v>
-      </c>
-      <c r="CA21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="CB21" t="inlineStr">
-        <is>
-          <t>2026-06-05 11:50:17</t>
+          <t>2026-06-05 14:02:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB11"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,180 +843,180 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Kormakur/Hvot</t>
+          <t>Wanderers (Uru)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>IF Magni</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,102 +1097,102 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Reynir Sandgeroi</t>
+          <t>Plaza Colonia</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Augnablik</t>
+          <t>Huracan del Paso</t>
         </is>
       </c>
       <c r="F3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>11</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O3" t="n">
+        <v>11</v>
+      </c>
+      <c r="P3" t="n">
         <v>1.01</v>
       </c>
-      <c r="G3" t="n">
+      <c r="Q3" t="n">
+        <v>110</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.01</v>
       </c>
-      <c r="H3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>1.64</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>570</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AH3" t="n">
         <v>1000</v>
@@ -1201,7 +1201,7 @@
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>560</v>
       </c>
       <c r="AK3" t="n">
         <v>1000</v>
@@ -1213,64 +1213,64 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.05</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>220</v>
+        <v>1.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>220</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="AS3" t="n">
-        <v>220</v>
+        <v>330</v>
       </c>
       <c r="AT3" t="n">
-        <v>220</v>
+        <v>4.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>220</v>
+        <v>25</v>
       </c>
       <c r="AV3" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AW3" t="n">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.15</v>
+        <v>27</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.15</v>
+        <v>140</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.15</v>
+        <v>22</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.15</v>
+        <v>18</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.15</v>
+        <v>150</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.15</v>
+        <v>170</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.15</v>
+        <v>130</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.15</v>
+        <v>100</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>240</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.02</v>
+        <v>120</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,108 +1351,108 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Hviti Riddarinn</t>
+          <t>Talleres (RE)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Haukar</t>
+          <t>Deportivo Merlo</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>3.1</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="H4" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="I4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.04</v>
       </c>
-      <c r="J4" t="n">
-        <v>26</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.77</v>
-      </c>
       <c r="S4" t="n">
-        <v>2.2</v>
+        <v>21</v>
       </c>
       <c r="T4" t="n">
-        <v>2.68</v>
+        <v>3.75</v>
       </c>
       <c r="U4" t="n">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="V4" t="n">
-        <v>26</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="Z4" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>10.5</v>
+        <v>990</v>
       </c>
       <c r="AE4" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AH4" t="n">
-        <v>55</v>
+        <v>990</v>
       </c>
       <c r="AI4" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
         <v>1000</v>
@@ -1461,141 +1461,141 @@
         <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>460</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
         <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>10</v>
+        <v>3.45</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.4</v>
+        <v>19.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.75</v>
+        <v>14</v>
       </c>
       <c r="AT4" t="n">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="AU4" t="n">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="AV4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>250</v>
+      </c>
+      <c r="BF4" t="n">
         <v>5.8</v>
       </c>
-      <c r="AW4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>42</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>70</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>26</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>46</v>
-      </c>
       <c r="BG4" t="n">
-        <v>3.6</v>
+        <v>23</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>590</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>910</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>690</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>860</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,251 +1605,251 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CA Ituzaingo</t>
+          <t>Operario PR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Pilar FC</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.4</v>
+        <v>2.86</v>
       </c>
       <c r="G5" t="n">
-        <v>4.8</v>
+        <v>2.94</v>
       </c>
       <c r="H5" t="n">
-        <v>2.38</v>
+        <v>3.8</v>
       </c>
       <c r="I5" t="n">
-        <v>2.48</v>
+        <v>3.9</v>
       </c>
       <c r="J5" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="K5" t="n">
-        <v>2.76</v>
+        <v>2.54</v>
       </c>
       <c r="L5" t="n">
-        <v>2.08</v>
+        <v>3.2</v>
       </c>
       <c r="M5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="N5" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="O5" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>780</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>720</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>230</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AX5" t="n">
         <v>15</v>
       </c>
-      <c r="T5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>490</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AH5" t="n">
+      <c r="AY5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>40</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>55</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>70</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>180</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF5" t="n">
         <v>110</v>
       </c>
-      <c r="AI5" t="n">
-        <v>550</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>180</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>190</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>420</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>470</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>44</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>120</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>120</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>140</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>290</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>150</v>
-      </c>
       <c r="BG5" t="n">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="BH5" t="n">
-        <v>1.99</v>
+        <v>1.46</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.89</v>
+        <v>1.41</v>
       </c>
       <c r="BJ5" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="BK5" t="n">
-        <v>20</v>
+        <v>3.15</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>4.8</v>
+        <v>3.15</v>
       </c>
       <c r="BN5" t="n">
-        <v>27</v>
+        <v>800</v>
       </c>
       <c r="BO5" t="n">
-        <v>6.8</v>
+        <v>3.2</v>
       </c>
       <c r="BP5" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>60</v>
+        <v>3.15</v>
       </c>
       <c r="BR5" t="n">
         <v>910</v>
       </c>
       <c r="BS5" t="n">
-        <v>4.7</v>
+        <v>3.15</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.1</v>
+        <v>800</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.95</v>
+        <v>3.15</v>
       </c>
       <c r="BV5" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>28</v>
+        <v>3.15</v>
       </c>
       <c r="BX5" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>4.8</v>
+        <v>3.15</v>
       </c>
       <c r="BZ5" t="n">
-        <v>960</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.8</v>
+        <v>3.15</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wanderers (Uru)</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="G6" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="H6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J6" t="n">
         <v>3.55</v>
       </c>
-      <c r="I6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.2</v>
-      </c>
       <c r="K6" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="M6" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="P6" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.46</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="T6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.02</v>
       </c>
-      <c r="U6" t="n">
-        <v>1.89</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="X6" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="Y6" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA6" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="AB6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC6" t="n">
         <v>8</v>
       </c>
-      <c r="AC6" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AD6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE6" t="n">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="AF6" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AG6" t="n">
         <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AJ6" t="n">
         <v>34</v>
       </c>
       <c r="AK6" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AL6" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="AM6" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AN6" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AO6" t="n">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="AP6" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AR6" t="n">
         <v>20</v>
       </c>
       <c r="AS6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT6" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ6" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>80</v>
+      </c>
+      <c r="BF6" t="n">
         <v>19</v>
       </c>
-      <c r="BA6" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC6" t="n">
+      <c r="BG6" t="n">
         <v>27</v>
       </c>
-      <c r="BD6" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>65</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>23</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>55</v>
-      </c>
       <c r="BH6" t="n">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="BJ6" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR6" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BS6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BT6" t="n">
         <v>6.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BW6" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BX6" t="n">
-        <v>960</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,1260 +2113,244 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>23:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Plaza Colonia</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Huracan del Paso</t>
+          <t>Atletico Ottawa</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1</v>
+        <v>2.46</v>
       </c>
       <c r="H7" t="n">
-        <v>4.2</v>
+        <v>2.86</v>
       </c>
       <c r="I7" t="n">
-        <v>4.7</v>
+        <v>3.05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="K7" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="M7" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.96</v>
+        <v>4.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="P7" t="n">
-        <v>1.64</v>
+        <v>2.18</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.44</v>
+        <v>1.78</v>
       </c>
       <c r="R7" t="n">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>4.7</v>
+        <v>3.05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.06</v>
+        <v>1.68</v>
       </c>
       <c r="U7" t="n">
-        <v>1.86</v>
+        <v>2.28</v>
       </c>
       <c r="V7" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT7" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ7" t="n">
+      <c r="AU7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW7" t="n">
         <v>28</v>
       </c>
-      <c r="AK7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>760</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>70</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>42</v>
-      </c>
       <c r="AX7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY7" t="n">
         <v>10</v>
       </c>
-      <c r="AY7" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AZ7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="BB7" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="BC7" t="n">
         <v>21</v>
       </c>
       <c r="BD7" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BE7" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="BF7" t="n">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.92</v>
+        <v>3.8</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.68</v>
+        <v>2.98</v>
       </c>
       <c r="BJ7" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BK7" t="n">
-        <v>9</v>
+        <v>5.1</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP7" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>12.5</v>
+        <v>6.8</v>
       </c>
       <c r="BR7" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="BS7" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="BT7" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BU7" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BV7" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="BW7" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY7" t="n">
-        <v>65</v>
+        <v>8.4</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA7" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-05 18:26:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Argentinian Primera B Metropolitana</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Talleres (RE)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Deportivo Merlo</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>2026-06-05 18:26:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Brazilian Serie B</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Operario PR</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Juventude</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="X9" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>990</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>50</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>65</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>40</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>65</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>18</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>24</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>70</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>34</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>60</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>2026-06-05 18:26:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Chilean Primera B</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>San Luis</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>San Marcos</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X10" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>25</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>22</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>26</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>2026-06-05 18:26:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>23:00:00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Vancouver FC</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Atletico Ottawa</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="I11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X11" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>44</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>28</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>30</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>13</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>29</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>25</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>36</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>8</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>24</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>2026-06-05 18:26:53</t>
+          <t>2026-06-05 20:39:21</t>
         </is>
       </c>
     </row>
